--- a/edim-ai-blueprint/docs/EDIM_기능정의서.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_기능정의서.xlsx
@@ -1991,7 +1991,7 @@
       </c>
       <c r="J22" s="8" t="inlineStr">
         <is>
-          <t>dwg_file, sys_approval_request</t>
+          <t>doc_control</t>
         </is>
       </c>
       <c r="K22" s="6" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="J23" s="8" t="inlineStr">
         <is>
-          <t>sys_role_permission</t>
+          <t>doc_control, sys_role_permission</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="J24" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>doc_control</t>
         </is>
       </c>
       <c r="K24" s="6" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="J68" s="8" t="inlineStr">
         <is>
-          <t>dwg_revision</t>
+          <t>dwg_supersedure, dwg_revision</t>
         </is>
       </c>
       <c r="K68" s="6" t="inlineStr">
@@ -8575,7 +8575,7 @@
       </c>
       <c r="J139" s="8" t="inlineStr">
         <is>
-          <t>prt_part, com_company</t>
+          <t>prt_supplier_code_map</t>
         </is>
       </c>
       <c r="K139" s="6" t="inlineStr">
@@ -8695,7 +8695,7 @@
       </c>
       <c r="J141" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>erp_warehouse, mat_material</t>
         </is>
       </c>
       <c r="K141" s="6" t="inlineStr">
@@ -8705,7 +8705,7 @@
       </c>
       <c r="L141" s="8" t="inlineStr">
         <is>
-          <t>슬라이드 46 — 상세 테이블 v0.2</t>
+          <t>슬라이드 46</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_기능정의서.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_기능정의서.xlsx
@@ -2604,7 +2604,7 @@
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>match_condition으로 Mother/Child 자릿수 연동</t>
+          <t>Slot 매핑 테이블(slot_map)로 Mother/Child 자릿수 연동</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="J33" s="8" t="inlineStr">
         <is>
-          <t>code_relationship</t>
+          <t>code_relationship, code_relationship_slot_map</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
@@ -10635,7 +10635,7 @@
       </c>
       <c r="J175" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>sys_tenant</t>
         </is>
       </c>
       <c r="K175" s="6" t="inlineStr">

--- a/edim-ai-blueprint/docs/EDIM_기능정의서.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_기능정의서.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="모듈요약" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'기능목록'!$A$1:$L$179</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'기능목록'!$A$1:$M$179</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -738,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L179"/>
+  <dimension ref="A1:M179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -752,7 +752,8 @@
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
     <col width="7" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -813,6 +814,11 @@
       </c>
       <c r="L1" s="5" t="inlineStr">
         <is>
+          <t>작업자</t>
+        </is>
+      </c>
+      <c r="M1" s="5" t="inlineStr">
+        <is>
           <t>비고</t>
         </is>
       </c>
@@ -871,7 +877,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="L2" s="8" t="inlineStr"/>
+      <c r="L2" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="n">
@@ -927,7 +938,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="L3" s="8" t="inlineStr"/>
+      <c r="L3" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M3" s="8" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="n">
@@ -983,7 +999,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="L4" s="8" t="inlineStr"/>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M4" s="8" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
@@ -1035,7 +1056,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="L5" s="8" t="inlineStr"/>
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
@@ -1091,7 +1117,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="L6" s="8" t="inlineStr">
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
         <is>
           <t>개요 §4</t>
         </is>
@@ -1151,7 +1182,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="L7" s="8" t="inlineStr"/>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
@@ -1207,7 +1243,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="L8" s="8" t="inlineStr"/>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
@@ -1263,7 +1304,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="L9" s="8" t="inlineStr">
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M9" s="8" t="inlineStr">
         <is>
           <t>개요 §4</t>
         </is>
@@ -1323,7 +1369,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="L10" s="8" t="inlineStr"/>
+      <c r="L10" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
@@ -1379,7 +1430,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="L11" s="8" t="inlineStr"/>
+      <c r="L11" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
@@ -1431,7 +1487,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L12" s="8" t="inlineStr"/>
+      <c r="L12" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
@@ -1487,7 +1548,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L13" s="8" t="inlineStr"/>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
@@ -1539,7 +1605,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L14" s="8" t="inlineStr"/>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
@@ -1591,7 +1662,12 @@
           <t>P4</t>
         </is>
       </c>
-      <c r="L15" s="8" t="inlineStr"/>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
@@ -1647,7 +1723,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="L16" s="8" t="inlineStr">
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M16" s="8" t="inlineStr">
         <is>
           <t>개요 §4</t>
         </is>
@@ -1703,7 +1784,12 @@
           <t>P4</t>
         </is>
       </c>
-      <c r="L17" s="8" t="inlineStr">
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M17" s="8" t="inlineStr">
         <is>
           <t>슬라이드 57</t>
         </is>
@@ -1763,7 +1849,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L18" s="8" t="inlineStr"/>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
@@ -1819,7 +1910,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L19" s="8" t="inlineStr">
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M19" s="8" t="inlineStr">
         <is>
           <t>슬라이드 57</t>
         </is>
@@ -1879,7 +1975,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L20" s="8" t="inlineStr">
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M20" s="8" t="inlineStr">
         <is>
           <t>슬라이드 57</t>
         </is>
@@ -1939,7 +2040,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L21" s="8" t="inlineStr">
+      <c r="L21" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M21" s="8" t="inlineStr">
         <is>
           <t>슬라이드 57</t>
         </is>
@@ -1999,7 +2105,12 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="L22" s="8" t="inlineStr">
+      <c r="L22" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M22" s="8" t="inlineStr">
         <is>
           <t>슬라이드 58</t>
         </is>
@@ -2059,7 +2170,12 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="L23" s="8" t="inlineStr">
+      <c r="L23" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M23" s="8" t="inlineStr">
         <is>
           <t>슬라이드 58</t>
         </is>
@@ -2119,7 +2235,12 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="L24" s="8" t="inlineStr">
+      <c r="L24" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M24" s="8" t="inlineStr">
         <is>
           <t>슬라이드 4/8</t>
         </is>
@@ -2179,7 +2300,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L25" s="8" t="inlineStr">
+      <c r="L25" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M25" s="8" t="inlineStr">
         <is>
           <t>슬라이드 58 placeholder</t>
         </is>
@@ -2239,7 +2365,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="L26" s="8" t="inlineStr"/>
+      <c r="L26" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M26" s="8" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
@@ -2295,7 +2426,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="L27" s="8" t="inlineStr"/>
+      <c r="L27" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M27" s="8" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
@@ -2351,7 +2487,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="L28" s="8" t="inlineStr"/>
+      <c r="L28" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M28" s="8" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
@@ -2403,7 +2544,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="L29" s="8" t="inlineStr"/>
+      <c r="L29" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M29" s="8" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
@@ -2459,7 +2605,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="L30" s="8" t="inlineStr"/>
+      <c r="L30" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M30" s="8" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
@@ -2515,7 +2666,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="L31" s="8" t="inlineStr"/>
+      <c r="L31" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M31" s="8" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
@@ -2571,7 +2727,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="L32" s="8" t="inlineStr"/>
+      <c r="L32" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M32" s="8" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
@@ -2627,7 +2788,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="L33" s="8" t="inlineStr">
+      <c r="L33" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M33" s="8" t="inlineStr">
         <is>
           <t>관계형 BOM 핵심</t>
         </is>
@@ -2687,7 +2853,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="L34" s="8" t="inlineStr"/>
+      <c r="L34" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M34" s="8" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
@@ -2743,7 +2914,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="L35" s="8" t="inlineStr"/>
+      <c r="L35" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M35" s="8" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
@@ -2799,7 +2975,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L36" s="8" t="inlineStr"/>
+      <c r="L36" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M36" s="8" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
@@ -2855,7 +3036,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L37" s="8" t="inlineStr"/>
+      <c r="L37" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M37" s="8" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
@@ -2911,7 +3097,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="L38" s="8" t="inlineStr"/>
+      <c r="L38" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M38" s="8" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
@@ -2963,7 +3154,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="L39" s="8" t="inlineStr"/>
+      <c r="L39" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M39" s="8" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
@@ -3019,7 +3215,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="L40" s="8" t="inlineStr">
+      <c r="L40" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M40" s="8" t="inlineStr">
         <is>
           <t>슬라이드 33~38 우측판넬</t>
         </is>
@@ -3079,7 +3280,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L41" s="8" t="inlineStr">
+      <c r="L41" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M41" s="8" t="inlineStr">
         <is>
           <t>슬라이드 32</t>
         </is>
@@ -3139,7 +3345,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L42" s="8" t="inlineStr"/>
+      <c r="L42" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M42" s="8" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
@@ -3195,7 +3406,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L43" s="8" t="inlineStr">
+      <c r="L43" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M43" s="8" t="inlineStr">
         <is>
           <t>노트 워크플로우 1</t>
         </is>
@@ -3255,7 +3471,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L44" s="8" t="inlineStr"/>
+      <c r="L44" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M44" s="8" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
@@ -3311,7 +3532,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L45" s="8" t="inlineStr"/>
+      <c r="L45" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M45" s="8" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
@@ -3367,7 +3593,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L46" s="8" t="inlineStr"/>
+      <c r="L46" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M46" s="8" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
@@ -3423,7 +3654,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L47" s="8" t="inlineStr">
+      <c r="L47" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M47" s="8" t="inlineStr">
         <is>
           <t>파라메트릭 핵심</t>
         </is>
@@ -3483,7 +3719,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L48" s="8" t="inlineStr"/>
+      <c r="L48" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M48" s="8" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
@@ -3539,7 +3780,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L49" s="8" t="inlineStr"/>
+      <c r="L49" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M49" s="8" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
@@ -3595,7 +3841,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L50" s="8" t="inlineStr"/>
+      <c r="L50" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M50" s="8" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
@@ -3651,7 +3902,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L51" s="8" t="inlineStr"/>
+      <c r="L51" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M51" s="8" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
@@ -3703,7 +3959,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L52" s="8" t="inlineStr"/>
+      <c r="L52" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M52" s="8" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
@@ -3759,7 +4020,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L53" s="8" t="inlineStr"/>
+      <c r="L53" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M53" s="8" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
@@ -3811,7 +4077,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L54" s="8" t="inlineStr"/>
+      <c r="L54" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M54" s="8" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
@@ -3867,7 +4138,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L55" s="8" t="inlineStr"/>
+      <c r="L55" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M55" s="8" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
@@ -3923,7 +4199,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L56" s="8" t="inlineStr">
+      <c r="L56" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M56" s="8" t="inlineStr">
         <is>
           <t>프로토타입 승계</t>
         </is>
@@ -3979,7 +4260,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L57" s="8" t="inlineStr"/>
+      <c r="L57" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M57" s="8" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
@@ -4035,7 +4321,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L58" s="8" t="inlineStr"/>
+      <c r="L58" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M58" s="8" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
@@ -4091,7 +4382,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L59" s="8" t="inlineStr"/>
+      <c r="L59" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M59" s="8" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
@@ -4143,7 +4439,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L60" s="8" t="inlineStr"/>
+      <c r="L60" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M60" s="8" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
@@ -4199,7 +4500,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L61" s="8" t="inlineStr"/>
+      <c r="L61" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M61" s="8" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
@@ -4255,7 +4561,12 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="L62" s="8" t="inlineStr">
+      <c r="L62" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M62" s="8" t="inlineStr">
         <is>
           <t>슬라이드 45</t>
         </is>
@@ -4315,7 +4626,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L63" s="8" t="inlineStr">
+      <c r="L63" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M63" s="8" t="inlineStr">
         <is>
           <t>슬라이드 41</t>
         </is>
@@ -4375,7 +4691,12 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="L64" s="8" t="inlineStr">
+      <c r="L64" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M64" s="8" t="inlineStr">
         <is>
           <t>슬라이드 44</t>
         </is>
@@ -4435,7 +4756,12 @@
           <t>P4</t>
         </is>
       </c>
-      <c r="L65" s="8" t="inlineStr">
+      <c r="L65" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M65" s="8" t="inlineStr">
         <is>
           <t>슬라이드 63</t>
         </is>
@@ -4495,7 +4821,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L66" s="8" t="inlineStr">
+      <c r="L66" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M66" s="8" t="inlineStr">
         <is>
           <t>슬라이드 61</t>
         </is>
@@ -4555,7 +4886,12 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="L67" s="8" t="inlineStr">
+      <c r="L67" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M67" s="8" t="inlineStr">
         <is>
           <t>슬라이드 5/60 Viewer 탭</t>
         </is>
@@ -4615,7 +4951,12 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="L68" s="8" t="inlineStr">
+      <c r="L68" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M68" s="8" t="inlineStr">
         <is>
           <t>슬라이드 5/60 Viewer 탭</t>
         </is>
@@ -4675,7 +5016,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="L69" s="8" t="inlineStr"/>
+      <c r="L69" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M69" s="8" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="n">
@@ -4731,7 +5077,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="L70" s="8" t="inlineStr"/>
+      <c r="L70" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M70" s="8" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="6" t="n">
@@ -4787,7 +5138,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="L71" s="8" t="inlineStr"/>
+      <c r="L71" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M71" s="8" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n">
@@ -4843,7 +5199,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="L72" s="8" t="inlineStr"/>
+      <c r="L72" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M72" s="8" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="6" t="n">
@@ -4899,7 +5260,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L73" s="8" t="inlineStr"/>
+      <c r="L73" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M73" s="8" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="6" t="n">
@@ -4951,7 +5317,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="L74" s="8" t="inlineStr"/>
+      <c r="L74" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M74" s="8" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="6" t="n">
@@ -5007,7 +5378,12 @@
           <t>P4</t>
         </is>
       </c>
-      <c r="L75" s="8" t="inlineStr"/>
+      <c r="L75" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M75" s="8" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n">
@@ -5063,7 +5439,12 @@
           <t>P4</t>
         </is>
       </c>
-      <c r="L76" s="8" t="inlineStr"/>
+      <c r="L76" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M76" s="8" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="6" t="n">
@@ -5119,7 +5500,12 @@
           <t>P4</t>
         </is>
       </c>
-      <c r="L77" s="8" t="inlineStr"/>
+      <c r="L77" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M77" s="8" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="6" t="n">
@@ -5175,7 +5561,12 @@
           <t>P4</t>
         </is>
       </c>
-      <c r="L78" s="8" t="inlineStr"/>
+      <c r="L78" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M78" s="8" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="6" t="n">
@@ -5231,7 +5622,12 @@
           <t>P4</t>
         </is>
       </c>
-      <c r="L79" s="8" t="inlineStr"/>
+      <c r="L79" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M79" s="8" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="n">
@@ -5287,7 +5683,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L80" s="8" t="inlineStr">
+      <c r="L80" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M80" s="8" t="inlineStr">
         <is>
           <t>엔진은 P1</t>
         </is>
@@ -5343,7 +5744,12 @@
           <t>P4</t>
         </is>
       </c>
-      <c r="L81" s="8" t="inlineStr"/>
+      <c r="L81" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M81" s="8" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="6" t="n">
@@ -5399,7 +5805,12 @@
           <t>P4</t>
         </is>
       </c>
-      <c r="L82" s="8" t="inlineStr">
+      <c r="L82" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M82" s="8" t="inlineStr">
         <is>
           <t>핵심 차별점</t>
         </is>
@@ -5459,7 +5870,12 @@
           <t>P4</t>
         </is>
       </c>
-      <c r="L83" s="8" t="inlineStr"/>
+      <c r="L83" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M83" s="8" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="n">
@@ -5515,7 +5931,12 @@
           <t>P4</t>
         </is>
       </c>
-      <c r="L84" s="8" t="inlineStr"/>
+      <c r="L84" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M84" s="8" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="6" t="n">
@@ -5571,7 +5992,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L85" s="8" t="inlineStr"/>
+      <c r="L85" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M85" s="8" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="6" t="n">
@@ -5627,7 +6053,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L86" s="8" t="inlineStr"/>
+      <c r="L86" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M86" s="8" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="6" t="n">
@@ -5683,7 +6114,12 @@
           <t>P4</t>
         </is>
       </c>
-      <c r="L87" s="8" t="inlineStr"/>
+      <c r="L87" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M87" s="8" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="6" t="n">
@@ -5739,7 +6175,12 @@
           <t>P4</t>
         </is>
       </c>
-      <c r="L88" s="8" t="inlineStr">
+      <c r="L88" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M88" s="8" t="inlineStr">
         <is>
           <t>슬라이드 29</t>
         </is>
@@ -5799,7 +6240,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L89" s="8" t="inlineStr">
+      <c r="L89" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M89" s="8" t="inlineStr">
         <is>
           <t>슬라이드 27 노트</t>
         </is>
@@ -5859,7 +6305,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L90" s="8" t="inlineStr"/>
+      <c r="L90" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M90" s="8" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="6" t="n">
@@ -5915,7 +6366,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L91" s="8" t="inlineStr">
+      <c r="L91" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M91" s="8" t="inlineStr">
         <is>
           <t>노트 워크플로우 2</t>
         </is>
@@ -5975,7 +6431,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L92" s="8" t="inlineStr"/>
+      <c r="L92" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M92" s="8" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="6" t="n">
@@ -6027,7 +6488,12 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="L93" s="8" t="inlineStr"/>
+      <c r="L93" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M93" s="8" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="n">
@@ -6083,7 +6549,12 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="L94" s="8" t="inlineStr"/>
+      <c r="L94" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M94" s="8" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="6" t="n">
@@ -6139,7 +6610,12 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="L95" s="8" t="inlineStr">
+      <c r="L95" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M95" s="8" t="inlineStr">
         <is>
           <t>노트 워크플로우 3</t>
         </is>
@@ -6199,7 +6675,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L96" s="8" t="inlineStr"/>
+      <c r="L96" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M96" s="8" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="6" t="n">
@@ -6255,7 +6736,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L97" s="8" t="inlineStr"/>
+      <c r="L97" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M97" s="8" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="n">
@@ -6311,7 +6797,12 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="L98" s="8" t="inlineStr"/>
+      <c r="L98" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M98" s="8" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="6" t="n">
@@ -6367,7 +6858,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L99" s="8" t="inlineStr"/>
+      <c r="L99" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M99" s="8" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="6" t="n">
@@ -6423,7 +6919,12 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="L100" s="8" t="inlineStr"/>
+      <c r="L100" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M100" s="8" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="6" t="n">
@@ -6475,7 +6976,12 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="L101" s="8" t="inlineStr"/>
+      <c r="L101" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M101" s="8" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="6" t="n">
@@ -6531,7 +7037,12 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="L102" s="8" t="inlineStr"/>
+      <c r="L102" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M102" s="8" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="6" t="n">
@@ -6587,7 +7098,12 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="L103" s="8" t="inlineStr">
+      <c r="L103" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M103" s="8" t="inlineStr">
         <is>
           <t>슬라이드 60</t>
         </is>
@@ -6647,7 +7163,12 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="L104" s="8" t="inlineStr">
+      <c r="L104" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M104" s="8" t="inlineStr">
         <is>
           <t>슬라이드 60</t>
         </is>
@@ -6707,7 +7228,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L105" s="8" t="inlineStr"/>
+      <c r="L105" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M105" s="8" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="6" t="n">
@@ -6763,7 +7289,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L106" s="8" t="inlineStr"/>
+      <c r="L106" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M106" s="8" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="6" t="n">
@@ -6819,7 +7350,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L107" s="8" t="inlineStr">
+      <c r="L107" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M107" s="8" t="inlineStr">
         <is>
           <t>노트 Runtime</t>
         </is>
@@ -6879,7 +7415,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L108" s="8" t="inlineStr"/>
+      <c r="L108" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M108" s="8" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="6" t="n">
@@ -6935,7 +7476,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L109" s="8" t="inlineStr"/>
+      <c r="L109" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M109" s="8" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="6" t="n">
@@ -6987,7 +7533,12 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="L110" s="8" t="inlineStr"/>
+      <c r="L110" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M110" s="8" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="6" t="n">
@@ -7039,7 +7590,12 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="L111" s="8" t="inlineStr"/>
+      <c r="L111" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M111" s="8" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="6" t="n">
@@ -7095,7 +7651,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L112" s="8" t="inlineStr"/>
+      <c r="L112" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M112" s="8" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="6" t="n">
@@ -7147,7 +7708,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L113" s="8" t="inlineStr"/>
+      <c r="L113" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M113" s="8" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="6" t="n">
@@ -7203,7 +7769,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L114" s="8" t="inlineStr">
+      <c r="L114" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M114" s="8" t="inlineStr">
         <is>
           <t>슬라이드 70</t>
         </is>
@@ -7263,7 +7834,12 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="L115" s="8" t="inlineStr"/>
+      <c r="L115" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M115" s="8" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="6" t="n">
@@ -7319,7 +7895,12 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="L116" s="8" t="inlineStr"/>
+      <c r="L116" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M116" s="8" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="6" t="n">
@@ -7371,7 +7952,12 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="L117" s="8" t="inlineStr"/>
+      <c r="L117" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M117" s="8" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="6" t="n">
@@ -7427,7 +8013,12 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="L118" s="8" t="inlineStr"/>
+      <c r="L118" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M118" s="8" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="6" t="n">
@@ -7483,7 +8074,12 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="L119" s="8" t="inlineStr"/>
+      <c r="L119" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M119" s="8" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="6" t="n">
@@ -7539,7 +8135,12 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="L120" s="8" t="inlineStr"/>
+      <c r="L120" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M120" s="8" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="6" t="n">
@@ -7591,7 +8192,12 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="L121" s="8" t="inlineStr"/>
+      <c r="L121" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M121" s="8" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="6" t="n">
@@ -7647,7 +8253,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L122" s="8" t="inlineStr"/>
+      <c r="L122" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M122" s="8" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="6" t="n">
@@ -7703,7 +8314,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L123" s="8" t="inlineStr"/>
+      <c r="L123" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M123" s="8" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="6" t="n">
@@ -7759,7 +8375,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L124" s="8" t="inlineStr"/>
+      <c r="L124" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M124" s="8" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="6" t="n">
@@ -7815,7 +8436,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L125" s="8" t="inlineStr"/>
+      <c r="L125" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M125" s="8" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="6" t="n">
@@ -7871,7 +8497,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L126" s="8" t="inlineStr"/>
+      <c r="L126" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M126" s="8" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="6" t="n">
@@ -7927,7 +8558,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L127" s="8" t="inlineStr"/>
+      <c r="L127" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M127" s="8" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="6" t="n">
@@ -7983,7 +8619,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L128" s="8" t="inlineStr">
+      <c r="L128" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M128" s="8" t="inlineStr">
         <is>
           <t>상세 v0.2</t>
         </is>
@@ -8043,7 +8684,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L129" s="8" t="inlineStr"/>
+      <c r="L129" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M129" s="8" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="6" t="n">
@@ -8095,7 +8741,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L130" s="8" t="inlineStr"/>
+      <c r="L130" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M130" s="8" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="6" t="n">
@@ -8147,7 +8798,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L131" s="8" t="inlineStr"/>
+      <c r="L131" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M131" s="8" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="6" t="n">
@@ -8199,7 +8855,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L132" s="8" t="inlineStr"/>
+      <c r="L132" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M132" s="8" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="6" t="n">
@@ -8251,7 +8912,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L133" s="8" t="inlineStr"/>
+      <c r="L133" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M133" s="8" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="6" t="n">
@@ -8303,7 +8969,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L134" s="8" t="inlineStr"/>
+      <c r="L134" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M134" s="8" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="6" t="n">
@@ -8359,7 +9030,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L135" s="8" t="inlineStr"/>
+      <c r="L135" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M135" s="8" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="6" t="n">
@@ -8411,7 +9087,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L136" s="8" t="inlineStr"/>
+      <c r="L136" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M136" s="8" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="6" t="n">
@@ -8467,7 +9148,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L137" s="8" t="inlineStr"/>
+      <c r="L137" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M137" s="8" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="6" t="n">
@@ -8523,7 +9209,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L138" s="8" t="inlineStr">
+      <c r="L138" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M138" s="8" t="inlineStr">
         <is>
           <t>슬라이드 46</t>
         </is>
@@ -8583,7 +9274,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L139" s="8" t="inlineStr">
+      <c r="L139" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M139" s="8" t="inlineStr">
         <is>
           <t>슬라이드 46</t>
         </is>
@@ -8643,7 +9339,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L140" s="8" t="inlineStr">
+      <c r="L140" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M140" s="8" t="inlineStr">
         <is>
           <t>슬라이드 46</t>
         </is>
@@ -8703,7 +9404,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L141" s="8" t="inlineStr">
+      <c r="L141" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M141" s="8" t="inlineStr">
         <is>
           <t>슬라이드 46</t>
         </is>
@@ -8763,7 +9469,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L142" s="8" t="inlineStr">
+      <c r="L142" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M142" s="8" t="inlineStr">
         <is>
           <t>슬라이드 46</t>
         </is>
@@ -8823,7 +9534,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L143" s="8" t="inlineStr">
+      <c r="L143" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M143" s="8" t="inlineStr">
         <is>
           <t>슬라이드 46</t>
         </is>
@@ -8879,7 +9595,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L144" s="8" t="inlineStr">
+      <c r="L144" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M144" s="8" t="inlineStr">
         <is>
           <t>슬라이드 46</t>
         </is>
@@ -8939,7 +9660,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L145" s="8" t="inlineStr">
+      <c r="L145" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M145" s="8" t="inlineStr">
         <is>
           <t>슬라이드 46</t>
         </is>
@@ -8999,7 +9725,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L146" s="8" t="inlineStr">
+      <c r="L146" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M146" s="8" t="inlineStr">
         <is>
           <t>슬라이드 46</t>
         </is>
@@ -9059,7 +9790,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L147" s="8" t="inlineStr">
+      <c r="L147" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M147" s="8" t="inlineStr">
         <is>
           <t>슬라이드 46</t>
         </is>
@@ -9119,7 +9855,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L148" s="8" t="inlineStr">
+      <c r="L148" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M148" s="8" t="inlineStr">
         <is>
           <t>슬라이드 46</t>
         </is>
@@ -9179,7 +9920,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L149" s="8" t="inlineStr">
+      <c r="L149" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M149" s="8" t="inlineStr">
         <is>
           <t>슬라이드 46</t>
         </is>
@@ -9235,7 +9981,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L150" s="8" t="inlineStr">
+      <c r="L150" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M150" s="8" t="inlineStr">
         <is>
           <t>슬라이드 46</t>
         </is>
@@ -9295,7 +10046,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L151" s="8" t="inlineStr">
+      <c r="L151" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M151" s="8" t="inlineStr">
         <is>
           <t>슬라이드 10/77</t>
         </is>
@@ -9355,7 +10111,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L152" s="8" t="inlineStr">
+      <c r="L152" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M152" s="8" t="inlineStr">
         <is>
           <t>슬라이드 68</t>
         </is>
@@ -9411,7 +10172,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L153" s="8" t="inlineStr">
+      <c r="L153" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M153" s="8" t="inlineStr">
         <is>
           <t>슬라이드 68</t>
         </is>
@@ -9467,7 +10233,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L154" s="8" t="inlineStr">
+      <c r="L154" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M154" s="8" t="inlineStr">
         <is>
           <t>슬라이드 68</t>
         </is>
@@ -9527,7 +10298,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L155" s="8" t="inlineStr">
+      <c r="L155" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M155" s="8" t="inlineStr">
         <is>
           <t>슬라이드 68</t>
         </is>
@@ -9587,7 +10363,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L156" s="8" t="inlineStr">
+      <c r="L156" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M156" s="8" t="inlineStr">
         <is>
           <t>슬라이드 68</t>
         </is>
@@ -9647,7 +10428,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L157" s="8" t="inlineStr">
+      <c r="L157" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M157" s="8" t="inlineStr">
         <is>
           <t>슬라이드 68</t>
         </is>
@@ -9707,7 +10493,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L158" s="8" t="inlineStr">
+      <c r="L158" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M158" s="8" t="inlineStr">
         <is>
           <t>슬라이드 68</t>
         </is>
@@ -9767,7 +10558,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L159" s="8" t="inlineStr"/>
+      <c r="L159" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M159" s="8" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="6" t="n">
@@ -9823,7 +10619,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L160" s="8" t="inlineStr"/>
+      <c r="L160" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M160" s="8" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="6" t="n">
@@ -9879,7 +10680,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L161" s="8" t="inlineStr"/>
+      <c r="L161" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M161" s="8" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="6" t="n">
@@ -9935,7 +10741,12 @@
           <t>P4</t>
         </is>
       </c>
-      <c r="L162" s="8" t="inlineStr"/>
+      <c r="L162" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M162" s="8" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="6" t="n">
@@ -9991,7 +10802,12 @@
           <t>P4</t>
         </is>
       </c>
-      <c r="L163" s="8" t="inlineStr"/>
+      <c r="L163" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M163" s="8" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="6" t="n">
@@ -10043,7 +10859,12 @@
           <t>P4</t>
         </is>
       </c>
-      <c r="L164" s="8" t="inlineStr"/>
+      <c r="L164" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M164" s="8" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="6" t="n">
@@ -10099,7 +10920,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L165" s="8" t="inlineStr"/>
+      <c r="L165" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M165" s="8" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="6" t="n">
@@ -10155,7 +10981,12 @@
           <t>P4</t>
         </is>
       </c>
-      <c r="L166" s="8" t="inlineStr"/>
+      <c r="L166" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M166" s="8" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="6" t="n">
@@ -10211,7 +11042,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L167" s="8" t="inlineStr"/>
+      <c r="L167" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M167" s="8" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="6" t="n">
@@ -10263,7 +11099,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L168" s="8" t="inlineStr"/>
+      <c r="L168" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M168" s="8" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="6" t="n">
@@ -10315,7 +11156,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L169" s="8" t="inlineStr"/>
+      <c r="L169" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M169" s="8" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="6" t="n">
@@ -10371,7 +11217,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L170" s="8" t="inlineStr"/>
+      <c r="L170" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M170" s="8" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="6" t="n">
@@ -10427,7 +11278,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L171" s="8" t="inlineStr"/>
+      <c r="L171" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M171" s="8" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="6" t="n">
@@ -10479,7 +11335,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L172" s="8" t="inlineStr"/>
+      <c r="L172" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M172" s="8" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="6" t="n">
@@ -10531,7 +11392,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L173" s="8" t="inlineStr"/>
+      <c r="L173" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M173" s="8" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="6" t="n">
@@ -10587,7 +11453,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L174" s="8" t="inlineStr">
+      <c r="L174" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M174" s="8" t="inlineStr">
         <is>
           <t>후순위</t>
         </is>
@@ -10643,7 +11514,12 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="L175" s="8" t="inlineStr"/>
+      <c r="L175" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M175" s="8" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="6" t="n">
@@ -10695,7 +11571,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="L176" s="8" t="inlineStr"/>
+      <c r="L176" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M176" s="8" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="6" t="n">
@@ -10747,7 +11628,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L177" s="8" t="inlineStr"/>
+      <c r="L177" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M177" s="8" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="6" t="n">
@@ -10803,7 +11689,12 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="L178" s="8" t="inlineStr"/>
+      <c r="L178" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M178" s="8" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="6" t="n">
@@ -10855,10 +11746,15 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="L179" s="8" t="inlineStr"/>
+      <c r="L179" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M179" s="8" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L179"/>
+  <autoFilter ref="A1:M179"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/edim-ai-blueprint/docs/EDIM_기능정의서.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_기능정의서.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="모듈요약" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'기능목록'!$A$1:$M$179</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'기능목록'!$A$1:$M$180</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -687,7 +687,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>178개</t>
+          <t>179개</t>
         </is>
       </c>
     </row>
@@ -738,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M179"/>
+  <dimension ref="A1:M180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2057,32 +2057,32 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>DOC-001</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>DOC 문서 관리</t>
+          <t>SYS-021</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>SYS 시스템 공통</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>E-1</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>문서 이력·Released Status</t>
+          <t>다국어 지원 (i18n)</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>문서별 Progress(Person/date/Released Status/Approver/App.Date/Version/DOC No.) 관리</t>
+          <t>UI 리소스 4로케일(KO/EN/JA/ZH) 번들, 데이터 라벨 번역(sys_translation), 로케일별 날짜·숫자·통화 포맷, 사용자·테넌트 기본 locale</t>
         </is>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>개정 Version(KD-0.2 등) 자동 증가</t>
+          <t>코드 값은 영문 고정(DB v0.3) — 라벨만 번역, 누락 시 KO 폴백, CJK 폰트 스택</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -2092,17 +2092,17 @@
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>SVC-11, SVC-10</t>
+          <t>FE-01, SVC-01</t>
         </is>
       </c>
       <c r="J22" s="8" t="inlineStr">
         <is>
-          <t>doc_control</t>
+          <t>sys_translation, sys_user</t>
         </is>
       </c>
       <c r="K22" s="6" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="L22" s="6" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="M22" s="8" t="inlineStr">
         <is>
-          <t>슬라이드 58</t>
+          <t>REQ-N-015 확정</t>
         </is>
       </c>
     </row>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>DOC-002</t>
+          <t>DOC-001</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
@@ -2137,32 +2137,32 @@
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>관리 등급(보안 등급)</t>
+          <t>문서 이력·Released Status</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>문서 Management Grade(S-2 등) 설정 — 등급별 열람/출력 통제</t>
+          <t>문서별 Progress(Person/date/Released Status/Approver/App.Date/Version/DOC No.) 관리</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>권한 없는 등급 문서 접근 차단</t>
+          <t>개정 Version(KD-0.2 등) 자동 증가</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>전체</t>
         </is>
       </c>
       <c r="I23" s="8" t="inlineStr">
         <is>
-          <t>SVC-01, SVC-11</t>
+          <t>SVC-11, SVC-10</t>
         </is>
       </c>
       <c r="J23" s="8" t="inlineStr">
         <is>
-          <t>doc_control, sys_role_permission</t>
+          <t>doc_control</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>DOC-003</t>
+          <t>DOC-002</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
@@ -2202,32 +2202,32 @@
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>Document Code 채번</t>
+          <t>관리 등급(보안 등급)</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>문서 코드 자동 생성 (예: EU-3-2020-450-6-21-4-SR-7)</t>
+          <t>문서 Management Grade(S-2 등) 설정 — 등급별 열람/출력 통제</t>
         </is>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>Product Code 기반 규칙 채번</t>
+          <t>권한 없는 등급 문서 접근 차단</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>시스템</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
-          <t>SVC-11</t>
+          <t>SVC-01, SVC-11</t>
         </is>
       </c>
       <c r="J24" s="8" t="inlineStr">
         <is>
-          <t>doc_control</t>
+          <t>doc_control, sys_role_permission</t>
         </is>
       </c>
       <c r="K24" s="6" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="M24" s="8" t="inlineStr">
         <is>
-          <t>슬라이드 4/8</t>
+          <t>슬라이드 58</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>DOC-004</t>
+          <t>DOC-003</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
@@ -2267,22 +2267,22 @@
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>문서 보안 솔루션</t>
+          <t>Document Code 채번</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>Authorization Settings·Security Solution 연계(워터마크·DRM·출력 통제)</t>
+          <t>문서 코드 자동 생성 (예: EU-3-2020-450-6-21-4-SR-7)</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>상세 요건 미정 — 고객 협의</t>
+          <t>Product Code 기반 규칙 채번</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>시스템</t>
         </is>
       </c>
       <c r="I25" s="8" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="J25" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>doc_control</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="L25" s="6" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
-          <t>슬라이드 58 placeholder</t>
+          <t>슬라이드 4/8</t>
         </is>
       </c>
     </row>
@@ -2317,52 +2317,52 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>CODE-001</t>
-        </is>
-      </c>
-      <c r="C26" s="10" t="inlineStr">
-        <is>
-          <t>CODE RCCS 코드 관리</t>
+          <t>DOC-004</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>DOC 문서 관리</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>S-1-1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>코드 그룹 등록</t>
+          <t>문서 보안 솔루션</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
-          <t>Specification 그룹(KOF 등) 생성, Hierarchy 위치 지정</t>
+          <t>Authorization Settings·Security Solution 연계(워터마크·DRM·출력 통제)</t>
         </is>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>group_code 중복 불가, 승인 후 사용</t>
+          <t>상세 요건 미정 — 고객 협의</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="I26" s="8" t="inlineStr">
         <is>
-          <t>SVC-03, FE-02</t>
+          <t>SVC-11</t>
         </is>
       </c>
       <c r="J26" s="8" t="inlineStr">
         <is>
-          <t>code_group</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="L26" s="6" t="inlineStr">
@@ -2370,7 +2370,11 @@
           <t>미정</t>
         </is>
       </c>
-      <c r="M26" s="8" t="inlineStr"/>
+      <c r="M26" s="8" t="inlineStr">
+        <is>
+          <t>슬라이드 58 placeholder</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
@@ -2378,7 +2382,7 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CODE-002</t>
+          <t>CODE-001</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
@@ -2393,17 +2397,17 @@
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>코드 자릿수 정의</t>
+          <t>코드 그룹 등록</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>그룹 내 Item Slot(A:Fan Model, B:Size…) 정의</t>
+          <t>Specification 그룹(KOF 등) 생성, Hierarchy 위치 지정</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>Slot 문자 그룹 내 유일</t>
+          <t>group_code 중복 불가, 승인 후 사용</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
@@ -2413,12 +2417,12 @@
       </c>
       <c r="I27" s="8" t="inlineStr">
         <is>
-          <t>SVC-03</t>
+          <t>SVC-03, FE-02</t>
         </is>
       </c>
       <c r="J27" s="8" t="inlineStr">
         <is>
-          <t>code_item</t>
+          <t>code_group</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
@@ -2439,7 +2443,7 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>CODE-003</t>
+          <t>CODE-002</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
@@ -2454,17 +2458,17 @@
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>자릿수 값 등록</t>
+          <t>코드 자릿수 정의</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>Sub Item List(350/400…, Gal./CU…) 등록</t>
+          <t>그룹 내 Item Slot(A:Fan Model, B:Size…) 정의</t>
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>중복검토 실행 후 승인 요청</t>
+          <t>Slot 문자 그룹 내 유일</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
@@ -2479,7 +2483,7 @@
       </c>
       <c r="J28" s="8" t="inlineStr">
         <is>
-          <t>code_item_value</t>
+          <t>code_item</t>
         </is>
       </c>
       <c r="K28" s="6" t="inlineStr">
@@ -2500,7 +2504,7 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>CODE-004</t>
+          <t>CODE-003</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
@@ -2510,20 +2514,24 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>S-1-2</t>
+          <t>S-1-1</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>Table 참조 값 연결</t>
+          <t>자릿수 값 등록</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>값이 Table 참조인 경우 tbl_data_table 연결</t>
-        </is>
-      </c>
-      <c r="G29" s="8" t="inlineStr"/>
+          <t>Sub Item List(350/400…, Gal./CU…) 등록</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>중복검토 실행 후 승인 요청</t>
+        </is>
+      </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
           <t>SETUP</t>
@@ -2531,7 +2539,7 @@
       </c>
       <c r="I29" s="8" t="inlineStr">
         <is>
-          <t>SVC-03, SVC-05</t>
+          <t>SVC-03</t>
         </is>
       </c>
       <c r="J29" s="8" t="inlineStr">
@@ -2557,7 +2565,7 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>CODE-005</t>
+          <t>CODE-004</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
@@ -2572,19 +2580,15 @@
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>자재·일반구매품 코드 등록</t>
+          <t>Table 참조 값 연결</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>Raw Material/GPI 그룹의 Sub Code 등록 (Motor 등)</t>
-        </is>
-      </c>
-      <c r="G30" s="8" t="inlineStr">
-        <is>
-          <t>가격(G:Price) Slot은 단가 Table 연계</t>
-        </is>
-      </c>
+          <t>값이 Table 참조인 경우 tbl_data_table 연결</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr"/>
       <c r="H30" s="6" t="inlineStr">
         <is>
           <t>SETUP</t>
@@ -2592,12 +2596,12 @@
       </c>
       <c r="I30" s="8" t="inlineStr">
         <is>
-          <t>SVC-03</t>
+          <t>SVC-03, SVC-05</t>
         </is>
       </c>
       <c r="J30" s="8" t="inlineStr">
         <is>
-          <t>code_group, code_item_value</t>
+          <t>code_item_value</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
@@ -2618,7 +2622,7 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>CODE-006</t>
+          <t>CODE-005</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
@@ -2628,22 +2632,22 @@
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>S-1-3</t>
+          <t>S-1-2</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>Product Code 등록</t>
+          <t>자재·일반구매품 코드 등록</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>Main Code(KDCR 3-13) 생성, 설명·Hierarchy 지정</t>
+          <t>Raw Material/GPI 그룹의 Sub Code 등록 (Motor 등)</t>
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>Main Code 중복성 검토 필수</t>
+          <t>가격(G:Price) Slot은 단가 Table 연계</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
@@ -2658,7 +2662,7 @@
       </c>
       <c r="J31" s="8" t="inlineStr">
         <is>
-          <t>product_code</t>
+          <t>code_group, code_item_value</t>
         </is>
       </c>
       <c r="K31" s="6" t="inlineStr">
@@ -2679,7 +2683,7 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>CODE-007</t>
+          <t>CODE-006</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
@@ -2694,17 +2698,17 @@
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>Product Code 자릿수 구성</t>
+          <t>Product Code 등록</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>제품 코드가 사용할 Slot과 값 출처(Sub Code) 연결</t>
+          <t>Main Code(KDCR 3-13) 생성, 설명·Hierarchy 지정</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>Code Hierarchy에서 Item List 탐색·설정 반복</t>
+          <t>Main Code 중복성 검토 필수</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -2719,7 +2723,7 @@
       </c>
       <c r="J32" s="8" t="inlineStr">
         <is>
-          <t>product_code_item</t>
+          <t>product_code</t>
         </is>
       </c>
       <c r="K32" s="6" t="inlineStr">
@@ -2740,7 +2744,7 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>CODE-008</t>
+          <t>CODE-007</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
@@ -2750,22 +2754,22 @@
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>S-1-4</t>
+          <t>S-1-3</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>Code Relationship 설정</t>
+          <t>Product Code 자릿수 구성</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>Mother-Child 관계 + 수량 + Slot 매핑 조건 등록</t>
+          <t>제품 코드가 사용할 Slot과 값 출처(Sub Code) 연결</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>Slot 매핑 테이블(slot_map)로 Mother/Child 자릿수 연동</t>
+          <t>Code Hierarchy에서 Item List 탐색·설정 반복</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
@@ -2780,7 +2784,7 @@
       </c>
       <c r="J33" s="8" t="inlineStr">
         <is>
-          <t>code_relationship, code_relationship_slot_map</t>
+          <t>product_code_item</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
@@ -2793,11 +2797,7 @@
           <t>미정</t>
         </is>
       </c>
-      <c r="M33" s="8" t="inlineStr">
-        <is>
-          <t>관계형 BOM 핵심</t>
-        </is>
-      </c>
+      <c r="M33" s="8" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>CODE-009</t>
+          <t>CODE-008</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
@@ -2820,17 +2820,17 @@
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>Part List Running Test</t>
+          <t>Code Relationship 설정</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>Mother 조합 선택 → 조건 일치 Child 전개 검증</t>
+          <t>Mother-Child 관계 + 수량 + Slot 매핑 조건 등록</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>검증 통과 후 승인 요청 가능</t>
+          <t>Slot 매핑 테이블(slot_map)로 Mother/Child 자릿수 연동</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="J34" s="8" t="inlineStr">
         <is>
-          <t>code_relationship</t>
+          <t>code_relationship, code_relationship_slot_map</t>
         </is>
       </c>
       <c r="K34" s="6" t="inlineStr">
@@ -2858,7 +2858,11 @@
           <t>미정</t>
         </is>
       </c>
-      <c r="M34" s="8" t="inlineStr"/>
+      <c r="M34" s="8" t="inlineStr">
+        <is>
+          <t>관계형 BOM 핵심</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
@@ -2866,7 +2870,7 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>CODE-010</t>
+          <t>CODE-009</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
@@ -2876,37 +2880,37 @@
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>S-1-4</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>BOM 전개</t>
+          <t>Part List Running Test</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>완성품 Code → Code Relationship 재귀 전개 → 전체 Part List</t>
+          <t>Mother 조합 선택 → 조건 일치 Child 전개 검증</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>재귀 CTE, 깊이 제한, 순환 차단</t>
+          <t>검증 통과 후 승인 요청 가능</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>GENERAL↑</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="I35" s="8" t="inlineStr">
         <is>
-          <t>SVC-03, ENG-02</t>
+          <t>SVC-03</t>
         </is>
       </c>
       <c r="J35" s="8" t="inlineStr">
         <is>
-          <t>code_relationship, cpq_selection_item</t>
+          <t>code_relationship</t>
         </is>
       </c>
       <c r="K35" s="6" t="inlineStr">
@@ -2927,7 +2931,7 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>CODE-011</t>
+          <t>CODE-010</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
@@ -2937,42 +2941,42 @@
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>S-1-5</t>
+          <t>D-2</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>Arrangement Code 등록</t>
+          <t>BOM 전개</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>표준 구성 조합(Double Deck 2 등) 등록</t>
+          <t>완성품 Code → Code Relationship 재귀 전개 → 전체 Part List</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>Fan Direction(L0~R270)·설치방식 옵션</t>
+          <t>재귀 CTE, 깊이 제한, 순환 차단</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL↑</t>
         </is>
       </c>
       <c r="I36" s="8" t="inlineStr">
         <is>
-          <t>SVC-03</t>
+          <t>SVC-03, ENG-02</t>
         </is>
       </c>
       <c r="J36" s="8" t="inlineStr">
         <is>
-          <t>arrangement_code</t>
+          <t>code_relationship, cpq_selection_item</t>
         </is>
       </c>
       <c r="K36" s="6" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="L36" s="6" t="inlineStr">
@@ -2988,7 +2992,7 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>CODE-012</t>
+          <t>CODE-011</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
@@ -2998,22 +3002,22 @@
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>S-1-6</t>
+          <t>S-1-5</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>Arrangement 구성 설정</t>
+          <t>Arrangement Code 등록</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>구성 Module 배치·결합조건(Macro) 설정, DWG 연결</t>
+          <t>표준 구성 조합(Double Deck 2 등) 등록</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>결합 조건은 tbx_macro 참조</t>
+          <t>Fan Direction(L0~R270)·설치방식 옵션</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr">
@@ -3023,12 +3027,12 @@
       </c>
       <c r="I37" s="8" t="inlineStr">
         <is>
-          <t>SVC-03, SVC-04</t>
+          <t>SVC-03</t>
         </is>
       </c>
       <c r="J37" s="8" t="inlineStr">
         <is>
-          <t>arrangement_component</t>
+          <t>arrangement_code</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
@@ -3049,7 +3053,7 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>CODE-013</t>
+          <t>CODE-012</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
@@ -3059,42 +3063,42 @@
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>S-1-x</t>
+          <t>S-1-6</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>코드 승인</t>
+          <t>Arrangement 구성 설정</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>코드 자산 승인 워크플로우 (Pending→Approved)</t>
+          <t>구성 Module 배치·결합조건(Macro) 설정, DWG 연결</t>
         </is>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>미승인 코드는 CPQ에서 선택 불가</t>
+          <t>결합 조건은 tbx_macro 참조</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="I38" s="8" t="inlineStr">
         <is>
-          <t>SVC-10</t>
+          <t>SVC-03, SVC-04</t>
         </is>
       </c>
       <c r="J38" s="8" t="inlineStr">
         <is>
-          <t>code_*</t>
+          <t>arrangement_component</t>
         </is>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="L38" s="6" t="inlineStr">
@@ -3110,7 +3114,7 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>CODE-014</t>
+          <t>CODE-013</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
@@ -3125,23 +3129,27 @@
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>등록 Code Table 조회</t>
+          <t>코드 승인</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>그룹별 등록 코드 목록·상세·승인상태 조회</t>
-        </is>
-      </c>
-      <c r="G39" s="8" t="inlineStr"/>
+          <t>코드 자산 승인 워크플로우 (Pending→Approved)</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <t>미승인 코드는 CPQ에서 선택 불가</t>
+        </is>
+      </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="I39" s="8" t="inlineStr">
         <is>
-          <t>SVC-03, FE-02</t>
+          <t>SVC-10</t>
         </is>
       </c>
       <c r="J39" s="8" t="inlineStr">
@@ -3167,7 +3175,7 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>CODE-015</t>
+          <t>CODE-014</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
@@ -3182,32 +3190,28 @@
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>코드 자산 연결</t>
+          <t>등록 Code Table 조회</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>Sub/Product Code에 DWG(2D/3D)·Data Up-Load·Table 연결 관리</t>
-        </is>
-      </c>
-      <c r="G40" s="8" t="inlineStr">
-        <is>
-          <t>우측 판넬에서 코드별 도면/자료 즉시 확인</t>
-        </is>
-      </c>
+          <t>그룹별 등록 코드 목록·상세·승인상태 조회</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="inlineStr"/>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>전체</t>
         </is>
       </c>
       <c r="I40" s="8" t="inlineStr">
         <is>
-          <t>SVC-03, SVC-04, SVC-05</t>
+          <t>SVC-03, FE-02</t>
         </is>
       </c>
       <c r="J40" s="8" t="inlineStr">
         <is>
-          <t>product_code, dwg_file, tbl_data_table</t>
+          <t>code_*</t>
         </is>
       </c>
       <c r="K40" s="6" t="inlineStr">
@@ -3220,11 +3224,7 @@
           <t>미정</t>
         </is>
       </c>
-      <c r="M40" s="8" t="inlineStr">
-        <is>
-          <t>슬라이드 33~38 우측판넬</t>
-        </is>
-      </c>
+      <c r="M40" s="8" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>CODE-016</t>
+          <t>CODE-015</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
@@ -3247,17 +3247,17 @@
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>코드 Excel Import/Export</t>
+          <t>코드 자산 연결</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>Registered Code Table의 값 목록 Excel 일괄 등록/내보내기</t>
+          <t>Sub/Product Code에 DWG(2D/3D)·Data Up-Load·Table 연결 관리</t>
         </is>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>형식 검증 후 반영</t>
+          <t>우측 판넬에서 코드별 도면/자료 즉시 확인</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr">
@@ -3267,17 +3267,17 @@
       </c>
       <c r="I41" s="8" t="inlineStr">
         <is>
-          <t>SVC-03, INT-03</t>
+          <t>SVC-03, SVC-04, SVC-05</t>
         </is>
       </c>
       <c r="J41" s="8" t="inlineStr">
         <is>
-          <t>code_item_value</t>
+          <t>product_code, dwg_file, tbl_data_table</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="L41" s="6" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="M41" s="8" t="inlineStr">
         <is>
-          <t>슬라이드 32</t>
+          <t>슬라이드 33~38 우측판넬</t>
         </is>
       </c>
     </row>
@@ -3297,32 +3297,32 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>DWG-001</t>
-        </is>
-      </c>
-      <c r="C42" s="11" t="inlineStr">
-        <is>
-          <t>DWG 도면·PLM</t>
+          <t>CODE-016</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>CODE RCCS 코드 관리</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>S-4-1-1</t>
+          <t>S-1-x</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>도면 등록</t>
+          <t>코드 Excel Import/Export</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>도면 기본정보(도번·유형·축척·크기) 등록</t>
+          <t>Registered Code Table의 값 목록 Excel 일괄 등록/내보내기</t>
         </is>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>도번 중복 불가, 표준도면은 프로젝트 미연결</t>
+          <t>형식 검증 후 반영</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="I42" s="8" t="inlineStr">
         <is>
-          <t>SVC-04</t>
+          <t>SVC-03, INT-03</t>
         </is>
       </c>
       <c r="J42" s="8" t="inlineStr">
         <is>
-          <t>dwg_drawing</t>
+          <t>code_item_value</t>
         </is>
       </c>
       <c r="K42" s="6" t="inlineStr">
@@ -3350,7 +3350,11 @@
           <t>미정</t>
         </is>
       </c>
-      <c r="M42" s="8" t="inlineStr"/>
+      <c r="M42" s="8" t="inlineStr">
+        <is>
+          <t>슬라이드 32</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
@@ -3358,7 +3362,7 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>DWG-002</t>
+          <t>DWG-001</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
@@ -3373,17 +3377,17 @@
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>부품 호출·배치</t>
+          <t>도면 등록</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>Hierarchy에서 하부 부품 도면 호출, Canvas Drag 배치</t>
+          <t>도면 기본정보(도번·유형·축척·크기) 등록</t>
         </is>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>Block 상태로 호출(기본 치수)</t>
+          <t>도번 중복 불가, 표준도면은 프로젝트 미연결</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
@@ -3393,12 +3397,12 @@
       </c>
       <c r="I43" s="8" t="inlineStr">
         <is>
-          <t>FE-02, SVC-04</t>
+          <t>SVC-04</t>
         </is>
       </c>
       <c r="J43" s="8" t="inlineStr">
         <is>
-          <t>dwg_document</t>
+          <t>dwg_drawing</t>
         </is>
       </c>
       <c r="K43" s="6" t="inlineStr">
@@ -3411,11 +3415,7 @@
           <t>미정</t>
         </is>
       </c>
-      <c r="M43" s="8" t="inlineStr">
-        <is>
-          <t>노트 워크플로우 1</t>
-        </is>
-      </c>
+      <c r="M43" s="8" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>DWG-003</t>
+          <t>DWG-002</t>
         </is>
       </c>
       <c r="C44" s="11" t="inlineStr">
@@ -3433,22 +3433,22 @@
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>E-2</t>
+          <t>S-4-1-1</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>CAD 편집 명령</t>
+          <t>부품 호출·배치</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>복사/이동/반전/연장/삭제/회전, 좌표 이동, 색상·선형식</t>
+          <t>Hierarchy에서 하부 부품 도면 호출, Canvas Drag 배치</t>
         </is>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>CAD와 동일한 명령 Toolbar</t>
+          <t>Block 상태로 호출(기본 치수)</t>
         </is>
       </c>
       <c r="H44" s="6" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="I44" s="8" t="inlineStr">
         <is>
-          <t>FE-02</t>
+          <t>FE-02, SVC-04</t>
         </is>
       </c>
       <c r="J44" s="8" t="inlineStr">
@@ -3476,7 +3476,11 @@
           <t>미정</t>
         </is>
       </c>
-      <c r="M44" s="8" t="inlineStr"/>
+      <c r="M44" s="8" t="inlineStr">
+        <is>
+          <t>노트 워크플로우 1</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
@@ -3484,7 +3488,7 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>DWG-004</t>
+          <t>DWG-003</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
@@ -3499,17 +3503,17 @@
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>선택·스냅</t>
+          <t>CAD 편집 명령</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>1차 블록 선택, 2차 세부(끝점·중앙·모서리·중심) 선택</t>
+          <t>복사/이동/반전/연장/삭제/회전, 좌표 이동, 색상·선형식</t>
         </is>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>정보 선택 시 관계·검증·조립순서 색상 구분</t>
+          <t>CAD와 동일한 명령 Toolbar</t>
         </is>
       </c>
       <c r="H45" s="6" t="inlineStr">
@@ -3524,7 +3528,7 @@
       </c>
       <c r="J45" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>dwg_document</t>
         </is>
       </c>
       <c r="K45" s="6" t="inlineStr">
@@ -3545,7 +3549,7 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>DWG-005</t>
+          <t>DWG-004</t>
         </is>
       </c>
       <c r="C46" s="11" t="inlineStr">
@@ -3555,22 +3559,22 @@
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>S-4-1-1</t>
+          <t>E-2</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>치수선·지시선</t>
+          <t>선택·스냅</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>치수선 삽입, 지시선 자동 번호(A~N) 부여</t>
+          <t>1차 블록 선택, 2차 세부(끝점·중앙·모서리·중심) 선택</t>
         </is>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>번호 임의 변경 시 중복 검사, 치수선 감추기</t>
+          <t>정보 선택 시 관계·검증·조립순서 색상 구분</t>
         </is>
       </c>
       <c r="H46" s="6" t="inlineStr">
@@ -3580,12 +3584,12 @@
       </c>
       <c r="I46" s="8" t="inlineStr">
         <is>
-          <t>FE-02, SVC-04</t>
+          <t>FE-02</t>
         </is>
       </c>
       <c r="J46" s="8" t="inlineStr">
         <is>
-          <t>dwg_dimension</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="6" t="inlineStr">
@@ -3606,7 +3610,7 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>DWG-006</t>
+          <t>DWG-005</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
@@ -3621,17 +3625,17 @@
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>치수 Macro 바인딩</t>
+          <t>치수선·지시선</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>치수마다 Macro 연결 또는 Variant 직접 입력</t>
+          <t>치수선 삽입, 지시선 자동 번호(A~N) 부여</t>
         </is>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>KEY/DETAIL 치수 구분(승인도면용)</t>
+          <t>번호 임의 변경 시 중복 검사, 치수선 감추기</t>
         </is>
       </c>
       <c r="H47" s="6" t="inlineStr">
@@ -3641,12 +3645,12 @@
       </c>
       <c r="I47" s="8" t="inlineStr">
         <is>
-          <t>SVC-04, ENG-01</t>
+          <t>FE-02, SVC-04</t>
         </is>
       </c>
       <c r="J47" s="8" t="inlineStr">
         <is>
-          <t>dwg_dimension, tbx_macro</t>
+          <t>dwg_dimension</t>
         </is>
       </c>
       <c r="K47" s="6" t="inlineStr">
@@ -3659,11 +3663,7 @@
           <t>미정</t>
         </is>
       </c>
-      <c r="M47" s="8" t="inlineStr">
-        <is>
-          <t>파라메트릭 핵심</t>
-        </is>
-      </c>
+      <c r="M47" s="8" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>DWG-007</t>
+          <t>DWG-006</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr">
@@ -3686,17 +3686,17 @@
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>치수·부품 동기화</t>
+          <t>치수 Macro 바인딩</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>입력 치수값에 의한 Parametric Design 반영</t>
+          <t>치수마다 Macro 연결 또는 Variant 직접 입력</t>
         </is>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>치수와 부품 일체화, 항목 선택 시 도면 활성화</t>
+          <t>KEY/DETAIL 치수 구분(승인도면용)</t>
         </is>
       </c>
       <c r="H48" s="6" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="I48" s="8" t="inlineStr">
         <is>
-          <t>FE-02, ENG-03</t>
+          <t>SVC-04, ENG-01</t>
         </is>
       </c>
       <c r="J48" s="8" t="inlineStr">
         <is>
-          <t>dwg_document</t>
+          <t>dwg_dimension, tbx_macro</t>
         </is>
       </c>
       <c r="K48" s="6" t="inlineStr">
@@ -3724,7 +3724,11 @@
           <t>미정</t>
         </is>
       </c>
-      <c r="M48" s="8" t="inlineStr"/>
+      <c r="M48" s="8" t="inlineStr">
+        <is>
+          <t>파라메트릭 핵심</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
@@ -3732,7 +3736,7 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>DWG-008</t>
+          <t>DWG-007</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
@@ -3747,17 +3751,17 @@
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>설계·자료 우선순위</t>
+          <t>치수·부품 동기화</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>Design/Data Priority 설정, 순환 참조 점검</t>
+          <t>입력 치수값에 의한 Parametric Design 반영</t>
         </is>
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>우선순위 불일치 시 경고 제공</t>
+          <t>치수와 부품 일체화, 항목 선택 시 도면 활성화</t>
         </is>
       </c>
       <c r="H49" s="6" t="inlineStr">
@@ -3767,12 +3771,12 @@
       </c>
       <c r="I49" s="8" t="inlineStr">
         <is>
-          <t>SVC-04, ENG-01</t>
+          <t>FE-02, ENG-03</t>
         </is>
       </c>
       <c r="J49" s="8" t="inlineStr">
         <is>
-          <t>dwg_dimension</t>
+          <t>dwg_document</t>
         </is>
       </c>
       <c r="K49" s="6" t="inlineStr">
@@ -3793,7 +3797,7 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>DWG-009</t>
+          <t>DWG-008</t>
         </is>
       </c>
       <c r="C50" s="11" t="inlineStr">
@@ -3803,22 +3807,22 @@
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>E-4</t>
+          <t>S-4-1-1</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>부품 상호관계 설정</t>
+          <t>설계·자료 우선순위</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>Block A/B 선택, 조건1(수직·수평·중심)·조건2(접촉·좌표·각도), 관계값 Macro</t>
+          <t>Design/Data Priority 설정, 순환 참조 점검</t>
         </is>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>관계 진행 우선순위로 데이터 혼선 차단</t>
+          <t>우선순위 불일치 시 경고 제공</t>
         </is>
       </c>
       <c r="H50" s="6" t="inlineStr">
@@ -3828,12 +3832,12 @@
       </c>
       <c r="I50" s="8" t="inlineStr">
         <is>
-          <t>SVC-04</t>
+          <t>SVC-04, ENG-01</t>
         </is>
       </c>
       <c r="J50" s="8" t="inlineStr">
         <is>
-          <t>dwg_part_relation</t>
+          <t>dwg_dimension</t>
         </is>
       </c>
       <c r="K50" s="6" t="inlineStr">
@@ -3854,7 +3858,7 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>DWG-010</t>
+          <t>DWG-009</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
@@ -3869,17 +3873,17 @@
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>설계 검증 규칙</t>
+          <t>부품 상호관계 설정</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>설계 조건 Macro 설정, 불일치 시 경고 문구</t>
+          <t>Block A/B 선택, 조건1(수직·수평·중심)·조건2(접촉·좌표·각도), 관계값 Macro</t>
         </is>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>공학식·Table 활용</t>
+          <t>관계 진행 우선순위로 데이터 혼선 차단</t>
         </is>
       </c>
       <c r="H51" s="6" t="inlineStr">
@@ -3889,12 +3893,12 @@
       </c>
       <c r="I51" s="8" t="inlineStr">
         <is>
-          <t>SVC-04, ENG-01</t>
+          <t>SVC-04</t>
         </is>
       </c>
       <c r="J51" s="8" t="inlineStr">
         <is>
-          <t>dwg_verification</t>
+          <t>dwg_part_relation</t>
         </is>
       </c>
       <c r="K51" s="6" t="inlineStr">
@@ -3915,7 +3919,7 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>DWG-011</t>
+          <t>DWG-010</t>
         </is>
       </c>
       <c r="C52" s="11" t="inlineStr">
@@ -3930,15 +3934,19 @@
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>조립 순서 Set-up</t>
+          <t>설계 검증 규칙</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>조립품 부품에 조립 순서 번호·주의사항 정리</t>
-        </is>
-      </c>
-      <c r="G52" s="8" t="inlineStr"/>
+          <t>설계 조건 Macro 설정, 불일치 시 경고 문구</t>
+        </is>
+      </c>
+      <c r="G52" s="8" t="inlineStr">
+        <is>
+          <t>공학식·Table 활용</t>
+        </is>
+      </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
           <t>SETUP</t>
@@ -3946,12 +3954,12 @@
       </c>
       <c r="I52" s="8" t="inlineStr">
         <is>
-          <t>SVC-04</t>
+          <t>SVC-04, ENG-01</t>
         </is>
       </c>
       <c r="J52" s="8" t="inlineStr">
         <is>
-          <t>dwg_bom</t>
+          <t>dwg_verification</t>
         </is>
       </c>
       <c r="K52" s="6" t="inlineStr">
@@ -3972,7 +3980,7 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>DWG-012</t>
+          <t>DWG-011</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
@@ -3982,24 +3990,20 @@
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>S-4-1-1</t>
+          <t>E-4</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>Block 저장·호출</t>
+          <t>조립 순서 Set-up</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>Block 단위 저장(임시저장→승인→사용), 상위 호출 시 Block 상태</t>
-        </is>
-      </c>
-      <c r="G53" s="8" t="inlineStr">
-        <is>
-          <t>저장 장소 확인 절차</t>
-        </is>
-      </c>
+          <t>조립품 부품에 조립 순서 번호·주의사항 정리</t>
+        </is>
+      </c>
+      <c r="G53" s="8" t="inlineStr"/>
       <c r="H53" s="6" t="inlineStr">
         <is>
           <t>SETUP</t>
@@ -4012,7 +4016,7 @@
       </c>
       <c r="J53" s="8" t="inlineStr">
         <is>
-          <t>dwg_document</t>
+          <t>dwg_bom</t>
         </is>
       </c>
       <c r="K53" s="6" t="inlineStr">
@@ -4033,7 +4037,7 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>DWG-013</t>
+          <t>DWG-012</t>
         </is>
       </c>
       <c r="C54" s="11" t="inlineStr">
@@ -4043,20 +4047,24 @@
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>S-4-1-1</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>도면 개정 관리</t>
+          <t>Block 저장·호출</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>Rev A/B/C 개정, 사유·내용 기록</t>
-        </is>
-      </c>
-      <c r="G54" s="8" t="inlineStr"/>
+          <t>Block 단위 저장(임시저장→승인→사용), 상위 호출 시 Block 상태</t>
+        </is>
+      </c>
+      <c r="G54" s="8" t="inlineStr">
+        <is>
+          <t>저장 장소 확인 절차</t>
+        </is>
+      </c>
       <c r="H54" s="6" t="inlineStr">
         <is>
           <t>SETUP</t>
@@ -4069,7 +4077,7 @@
       </c>
       <c r="J54" s="8" t="inlineStr">
         <is>
-          <t>dwg_revision</t>
+          <t>dwg_document</t>
         </is>
       </c>
       <c r="K54" s="6" t="inlineStr">
@@ -4090,7 +4098,7 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>DWG-014</t>
+          <t>DWG-013</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
@@ -4105,32 +4113,28 @@
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>도면 승인</t>
+          <t>도면 개정 관리</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>작성→검토→승인→발행 단계 관리</t>
-        </is>
-      </c>
-      <c r="G55" s="8" t="inlineStr">
-        <is>
-          <t>슬라이드 26-7 스키마 준용</t>
-        </is>
-      </c>
+          <t>Rev A/B/C 개정, 사유·내용 기록</t>
+        </is>
+      </c>
+      <c r="G55" s="8" t="inlineStr"/>
       <c r="H55" s="6" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="I55" s="8" t="inlineStr">
         <is>
-          <t>SVC-04, SVC-10</t>
+          <t>SVC-04</t>
         </is>
       </c>
       <c r="J55" s="8" t="inlineStr">
         <is>
-          <t>dwg_approval</t>
+          <t>dwg_revision</t>
         </is>
       </c>
       <c r="K55" s="6" t="inlineStr">
@@ -4151,7 +4155,7 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>DWG-015</t>
+          <t>DWG-014</t>
         </is>
       </c>
       <c r="C56" s="11" t="inlineStr">
@@ -4166,32 +4170,32 @@
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>도면 Import</t>
+          <t>도면 승인</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>DXF/DWG/PDF/STEP 업로드 → DrawingDocument 변환</t>
+          <t>작성→검토→승인→발행 단계 관리</t>
         </is>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>DWG는 ODA 변환(INT-04), PDF→DXF 지원</t>
+          <t>슬라이드 26-7 스키마 준용</t>
         </is>
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="I56" s="8" t="inlineStr">
         <is>
-          <t>SVC-04, INT-04</t>
+          <t>SVC-04, SVC-10</t>
         </is>
       </c>
       <c r="J56" s="8" t="inlineStr">
         <is>
-          <t>dwg_file, dwg_document</t>
+          <t>dwg_approval</t>
         </is>
       </c>
       <c r="K56" s="6" t="inlineStr">
@@ -4204,11 +4208,7 @@
           <t>미정</t>
         </is>
       </c>
-      <c r="M56" s="8" t="inlineStr">
-        <is>
-          <t>프로토타입 승계</t>
-        </is>
-      </c>
+      <c r="M56" s="8" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>DWG-016</t>
+          <t>DWG-015</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
@@ -4231,28 +4231,32 @@
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>도면 Export</t>
+          <t>도면 Import</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>DXF(R2010)/PDF 출력</t>
-        </is>
-      </c>
-      <c r="G57" s="8" t="inlineStr"/>
+          <t>DXF/DWG/PDF/STEP 업로드 → DrawingDocument 변환</t>
+        </is>
+      </c>
+      <c r="G57" s="8" t="inlineStr">
+        <is>
+          <t>DWG는 ODA 변환(INT-04), PDF→DXF 지원</t>
+        </is>
+      </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="I57" s="8" t="inlineStr">
         <is>
-          <t>SVC-04, ENG-03</t>
+          <t>SVC-04, INT-04</t>
         </is>
       </c>
       <c r="J57" s="8" t="inlineStr">
         <is>
-          <t>dwg_document</t>
+          <t>dwg_file, dwg_document</t>
         </is>
       </c>
       <c r="K57" s="6" t="inlineStr">
@@ -4265,7 +4269,11 @@
           <t>미정</t>
         </is>
       </c>
-      <c r="M57" s="8" t="inlineStr"/>
+      <c r="M57" s="8" t="inlineStr">
+        <is>
+          <t>프로토타입 승계</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
@@ -4273,7 +4281,7 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>DWG-017</t>
+          <t>DWG-016</t>
         </is>
       </c>
       <c r="C58" s="11" t="inlineStr">
@@ -4288,32 +4296,28 @@
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>부품 마스터</t>
+          <t>도면 Export</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>부품 등록(규격·재질·단위·단중·공급처·표준품)</t>
-        </is>
-      </c>
-      <c r="G58" s="8" t="inlineStr">
-        <is>
-          <t>RCCS Product Code 연결 가능</t>
-        </is>
-      </c>
+          <t>DXF(R2010)/PDF 출력</t>
+        </is>
+      </c>
+      <c r="G58" s="8" t="inlineStr"/>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>전체</t>
         </is>
       </c>
       <c r="I58" s="8" t="inlineStr">
         <is>
-          <t>SVC-04</t>
+          <t>SVC-04, ENG-03</t>
         </is>
       </c>
       <c r="J58" s="8" t="inlineStr">
         <is>
-          <t>prt_part</t>
+          <t>dwg_document</t>
         </is>
       </c>
       <c r="K58" s="6" t="inlineStr">
@@ -4334,7 +4338,7 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>DWG-018</t>
+          <t>DWG-017</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
@@ -4349,17 +4353,17 @@
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>재질 마스터</t>
+          <t>부품 마스터</t>
         </is>
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>재질 코드(SS400 등)·밀도·규격 관리</t>
+          <t>부품 등록(규격·재질·단위·단중·공급처·표준품)</t>
         </is>
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>밀도는 원가 무게 계산 입력</t>
+          <t>RCCS Product Code 연결 가능</t>
         </is>
       </c>
       <c r="H59" s="6" t="inlineStr">
@@ -4374,7 +4378,7 @@
       </c>
       <c r="J59" s="8" t="inlineStr">
         <is>
-          <t>mat_material</t>
+          <t>prt_part</t>
         </is>
       </c>
       <c r="K59" s="6" t="inlineStr">
@@ -4395,7 +4399,7 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>DWG-019</t>
+          <t>DWG-018</t>
         </is>
       </c>
       <c r="C60" s="11" t="inlineStr">
@@ -4410,15 +4414,19 @@
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>도면 BOM 관리</t>
+          <t>재질 마스터</t>
         </is>
       </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>도면 부품 구성표(품번·수량·비고)</t>
-        </is>
-      </c>
-      <c r="G60" s="8" t="inlineStr"/>
+          <t>재질 코드(SS400 등)·밀도·규격 관리</t>
+        </is>
+      </c>
+      <c r="G60" s="8" t="inlineStr">
+        <is>
+          <t>밀도는 원가 무게 계산 입력</t>
+        </is>
+      </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
           <t>SETUP</t>
@@ -4431,7 +4439,7 @@
       </c>
       <c r="J60" s="8" t="inlineStr">
         <is>
-          <t>dwg_bom</t>
+          <t>mat_material</t>
         </is>
       </c>
       <c r="K60" s="6" t="inlineStr">
@@ -4452,7 +4460,7 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>DWG-020</t>
+          <t>DWG-019</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
@@ -4467,32 +4475,28 @@
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>첨부파일 관리</t>
+          <t>도면 BOM 관리</t>
         </is>
       </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>도면별 파일(DWG/PDF/STEP/PNG) 첨부</t>
-        </is>
-      </c>
-      <c r="G61" s="8" t="inlineStr">
-        <is>
-          <t>실체는 Object Storage</t>
-        </is>
-      </c>
+          <t>도면 부품 구성표(품번·수량·비고)</t>
+        </is>
+      </c>
+      <c r="G61" s="8" t="inlineStr"/>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="I61" s="8" t="inlineStr">
         <is>
-          <t>SVC-04, SVC-12</t>
+          <t>SVC-04</t>
         </is>
       </c>
       <c r="J61" s="8" t="inlineStr">
         <is>
-          <t>dwg_file</t>
+          <t>dwg_bom</t>
         </is>
       </c>
       <c r="K61" s="6" t="inlineStr">
@@ -4513,7 +4517,7 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>DWG-021</t>
+          <t>DWG-020</t>
         </is>
       </c>
       <c r="C62" s="11" t="inlineStr">
@@ -4523,42 +4527,42 @@
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>S-4-1-2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>Work Process 공정 데이터</t>
+          <t>첨부파일 관리</t>
         </is>
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>Product Code별 자재/공정/조립 정보(작업장·인원·스킬·시간·창고·최소재고)</t>
+          <t>도면별 파일(DWG/PDF/STEP/PNG) 첨부</t>
         </is>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>제조비 계산 입력</t>
+          <t>실체는 Object Storage</t>
         </is>
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>전체</t>
         </is>
       </c>
       <c r="I62" s="8" t="inlineStr">
         <is>
-          <t>SVC-09</t>
+          <t>SVC-04, SVC-12</t>
         </is>
       </c>
       <c r="J62" s="8" t="inlineStr">
         <is>
-          <t>erp_work_process</t>
+          <t>dwg_file</t>
         </is>
       </c>
       <c r="K62" s="6" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="L62" s="6" t="inlineStr">
@@ -4566,11 +4570,7 @@
           <t>미정</t>
         </is>
       </c>
-      <c r="M62" s="8" t="inlineStr">
-        <is>
-          <t>슬라이드 45</t>
-        </is>
-      </c>
+      <c r="M62" s="8" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>DWG-022</t>
+          <t>DWG-021</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
@@ -4588,22 +4588,22 @@
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>S-4-1-1</t>
+          <t>S-4-1-2</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>도면 Templet 관리</t>
+          <t>Work Process 공정 데이터</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>설정 도면 Templet(도면 Frame·비율·형식) 등록·호출</t>
+          <t>Product Code별 자재/공정/조립 정보(작업장·인원·스킬·시간·창고·최소재고)</t>
         </is>
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>신규 도면은 Templet에서 시작 (Free CAD)</t>
+          <t>제조비 계산 입력</t>
         </is>
       </c>
       <c r="H63" s="6" t="inlineStr">
@@ -4613,17 +4613,17 @@
       </c>
       <c r="I63" s="8" t="inlineStr">
         <is>
-          <t>SVC-04, SVC-06</t>
+          <t>SVC-09</t>
         </is>
       </c>
       <c r="J63" s="8" t="inlineStr">
         <is>
-          <t>tbx_templet</t>
+          <t>erp_work_process</t>
         </is>
       </c>
       <c r="K63" s="6" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="L63" s="6" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="M63" s="8" t="inlineStr">
         <is>
-          <t>슬라이드 41</t>
+          <t>슬라이드 45</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>DWG-023</t>
+          <t>DWG-022</t>
         </is>
       </c>
       <c r="C64" s="11" t="inlineStr">
@@ -4653,22 +4653,22 @@
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>S-4-1-1</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>CAD Mapping</t>
+          <t>도면 Templet 관리</t>
         </is>
       </c>
       <c r="F64" s="8" t="inlineStr">
         <is>
-          <t>도면 항목과 외부 CAD 파일(2D/3D) 매핑 연결</t>
+          <t>설정 도면 Templet(도면 Frame·비율·형식) 등록·호출</t>
         </is>
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>Sub Material/Variant List에 CAD Mapping 체크</t>
+          <t>신규 도면은 Templet에서 시작 (Free CAD)</t>
         </is>
       </c>
       <c r="H64" s="6" t="inlineStr">
@@ -4678,17 +4678,17 @@
       </c>
       <c r="I64" s="8" t="inlineStr">
         <is>
-          <t>SVC-04, INT-04</t>
+          <t>SVC-04, SVC-06</t>
         </is>
       </c>
       <c r="J64" s="8" t="inlineStr">
         <is>
-          <t>dwg_file</t>
+          <t>tbx_templet</t>
         </is>
       </c>
       <c r="K64" s="6" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="L64" s="6" t="inlineStr">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="M64" s="8" t="inlineStr">
         <is>
-          <t>슬라이드 44</t>
+          <t>슬라이드 41</t>
         </is>
       </c>
     </row>
@@ -4708,7 +4708,7 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>DWG-024</t>
+          <t>DWG-023</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
@@ -4718,22 +4718,22 @@
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>E-4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>설계 Simulation</t>
+          <t>CAD Mapping</t>
         </is>
       </c>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>설정된 관계·검증 규칙 기반 도면 동작 시뮬레이션(우측 판넬)</t>
+          <t>도면 항목과 외부 CAD 파일(2D/3D) 매핑 연결</t>
         </is>
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
-          <t>검증 경고 시각화</t>
+          <t>Sub Material/Variant List에 CAD Mapping 체크</t>
         </is>
       </c>
       <c r="H65" s="6" t="inlineStr">
@@ -4743,17 +4743,17 @@
       </c>
       <c r="I65" s="8" t="inlineStr">
         <is>
-          <t>FE-02, ENG-01</t>
+          <t>SVC-04, INT-04</t>
         </is>
       </c>
       <c r="J65" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>dwg_file</t>
         </is>
       </c>
       <c r="K65" s="6" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="L65" s="6" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="M65" s="8" t="inlineStr">
         <is>
-          <t>슬라이드 63</t>
+          <t>슬라이드 44</t>
         </is>
       </c>
     </row>
@@ -4773,7 +4773,7 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>DWG-025</t>
+          <t>DWG-024</t>
         </is>
       </c>
       <c r="C66" s="11" t="inlineStr">
@@ -4783,22 +4783,22 @@
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>E-2</t>
+          <t>E-4</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>측정·특성 도구</t>
+          <t>설계 Simulation</t>
         </is>
       </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
-          <t>치수 측정(수평/수직/정렬/각도/호길이/면적/무게), 특성 변경(색상/투명도/선굵기/레이어), 자르기(Trim), 그룹화/해제, 등각·단면 View</t>
+          <t>설정된 관계·검증 규칙 기반 도면 동작 시뮬레이션(우측 판넬)</t>
         </is>
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>CAD와 동일 형식 명령·단축키(DI/CH/CO/RO/E/TR/REG)</t>
+          <t>검증 경고 시각화</t>
         </is>
       </c>
       <c r="H66" s="6" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="I66" s="8" t="inlineStr">
         <is>
-          <t>FE-02</t>
+          <t>FE-02, ENG-01</t>
         </is>
       </c>
       <c r="J66" s="8" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="K66" s="6" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="L66" s="6" t="inlineStr">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="M66" s="8" t="inlineStr">
         <is>
-          <t>슬라이드 61</t>
+          <t>슬라이드 63</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>DWG-026</t>
+          <t>DWG-025</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
@@ -4853,37 +4853,37 @@
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>Referencers 역참조 조회</t>
+          <t>측정·특성 도구</t>
         </is>
       </c>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>도면/부품의 Where-used — 어느 상위 도면·Arrangement에서 참조되는지 조회</t>
+          <t>치수 측정(수평/수직/정렬/각도/호길이/면적/무게), 특성 변경(색상/투명도/선굵기/레이어), 자르기(Trim), 그룹화/해제, 등각·단면 View</t>
         </is>
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>Viewer 탭: Variants/Viewer/Referencers/Supersedure/Attachment</t>
+          <t>CAD와 동일 형식 명령·단축키(DI/CH/CO/RO/E/TR/REG)</t>
         </is>
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="I67" s="8" t="inlineStr">
         <is>
-          <t>SVC-04</t>
+          <t>FE-02</t>
         </is>
       </c>
       <c r="J67" s="8" t="inlineStr">
         <is>
-          <t>dwg_bom, code_relationship</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="L67" s="6" t="inlineStr">
@@ -4893,7 +4893,7 @@
       </c>
       <c r="M67" s="8" t="inlineStr">
         <is>
-          <t>슬라이드 5/60 Viewer 탭</t>
+          <t>슬라이드 61</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>DWG-027</t>
+          <t>DWG-026</t>
         </is>
       </c>
       <c r="C68" s="11" t="inlineStr">
@@ -4918,22 +4918,22 @@
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>Variants·Supersedure 관리</t>
+          <t>Referencers 역참조 조회</t>
         </is>
       </c>
       <c r="F68" s="8" t="inlineStr">
         <is>
-          <t>도면 변형(Variants) 목록과 대체 관계(Supersedure — 신규정이 구버전 대체) 관리</t>
+          <t>도면/부품의 Where-used — 어느 상위 도면·Arrangement에서 참조되는지 조회</t>
         </is>
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>대체된 도면 사용 시 경고</t>
+          <t>Viewer 탭: Variants/Viewer/Referencers/Supersedure/Attachment</t>
         </is>
       </c>
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>전체</t>
         </is>
       </c>
       <c r="I68" s="8" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="J68" s="8" t="inlineStr">
         <is>
-          <t>dwg_supersedure, dwg_revision</t>
+          <t>dwg_bom, code_relationship</t>
         </is>
       </c>
       <c r="K68" s="6" t="inlineStr">
@@ -4968,32 +4968,32 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>TBL-001</t>
-        </is>
-      </c>
-      <c r="C69" s="12" t="inlineStr">
-        <is>
-          <t>TBL 데이터 Table</t>
+          <t>DWG-027</t>
+        </is>
+      </c>
+      <c r="C69" s="11" t="inlineStr">
+        <is>
+          <t>DWG 도면·PLM</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>E-4</t>
+          <t>E-2</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>Table 정의</t>
+          <t>Variants·Supersedure 관리</t>
         </is>
       </c>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>Variant/Tech/Material Table 생성(열 정의·부서·Hierarchy 주소)</t>
+          <t>도면 변형(Variants) 목록과 대체 관계(Supersedure — 신규정이 구버전 대체) 관리</t>
         </is>
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>DB로서의 명확한 구성 요구, 승인 후 사용</t>
+          <t>대체된 도면 사용 시 경고</t>
         </is>
       </c>
       <c r="H69" s="6" t="inlineStr">
@@ -5003,17 +5003,17 @@
       </c>
       <c r="I69" s="8" t="inlineStr">
         <is>
-          <t>SVC-05</t>
+          <t>SVC-04</t>
         </is>
       </c>
       <c r="J69" s="8" t="inlineStr">
         <is>
-          <t>tbl_data_table</t>
+          <t>dwg_supersedure, dwg_revision</t>
         </is>
       </c>
       <c r="K69" s="6" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="L69" s="6" t="inlineStr">
@@ -5021,7 +5021,11 @@
           <t>미정</t>
         </is>
       </c>
-      <c r="M69" s="8" t="inlineStr"/>
+      <c r="M69" s="8" t="inlineStr">
+        <is>
+          <t>슬라이드 5/60 Viewer 탭</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="n">
@@ -5029,7 +5033,7 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>TBL-002</t>
+          <t>TBL-001</t>
         </is>
       </c>
       <c r="C70" s="12" t="inlineStr">
@@ -5044,17 +5048,17 @@
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>Table 행 편집</t>
+          <t>Table 정의</t>
         </is>
       </c>
       <c r="F70" s="8" t="inlineStr">
         <is>
-          <t>행 추가/편집/일괄 입력 (Key + A~N 값)</t>
+          <t>Variant/Tech/Material Table 생성(열 정의·부서·Hierarchy 주소)</t>
         </is>
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>row_key 유일</t>
+          <t>DB로서의 명확한 구성 요구, 승인 후 사용</t>
         </is>
       </c>
       <c r="H70" s="6" t="inlineStr">
@@ -5069,7 +5073,7 @@
       </c>
       <c r="J70" s="8" t="inlineStr">
         <is>
-          <t>tbl_data_row</t>
+          <t>tbl_data_table</t>
         </is>
       </c>
       <c r="K70" s="6" t="inlineStr">
@@ -5090,7 +5094,7 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>TBL-003</t>
+          <t>TBL-002</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
@@ -5100,22 +5104,22 @@
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>E-4</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>Excel Import</t>
+          <t>Table 행 편집</t>
         </is>
       </c>
       <c r="F71" s="8" t="inlineStr">
         <is>
-          <t>정해진 양식의 Excel에서 Table 행 일괄 등록</t>
+          <t>행 추가/편집/일괄 입력 (Key + A~N 값)</t>
         </is>
       </c>
       <c r="G71" s="8" t="inlineStr">
         <is>
-          <t>Excel 연동 형식 정리(슬라이드 69)</t>
+          <t>row_key 유일</t>
         </is>
       </c>
       <c r="H71" s="6" t="inlineStr">
@@ -5125,7 +5129,7 @@
       </c>
       <c r="I71" s="8" t="inlineStr">
         <is>
-          <t>SVC-05, INT-03</t>
+          <t>SVC-05</t>
         </is>
       </c>
       <c r="J71" s="8" t="inlineStr">
@@ -5151,7 +5155,7 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>TBL-004</t>
+          <t>TBL-003</t>
         </is>
       </c>
       <c r="C72" s="12" t="inlineStr">
@@ -5166,27 +5170,27 @@
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>Table 범위 조회</t>
+          <t>Excel Import</t>
         </is>
       </c>
       <c r="F72" s="8" t="inlineStr">
         <is>
-          <t>Macro 참조용 범위 조회 API(TableN(col,range))</t>
+          <t>정해진 양식의 Excel에서 Table 행 일괄 등록</t>
         </is>
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t>GIN 인덱스, 캐시 적용</t>
+          <t>Excel 연동 형식 정리(슬라이드 69)</t>
         </is>
       </c>
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>시스템</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="I72" s="8" t="inlineStr">
         <is>
-          <t>SVC-05, ENG-01</t>
+          <t>SVC-05, INT-03</t>
         </is>
       </c>
       <c r="J72" s="8" t="inlineStr">
@@ -5212,7 +5216,7 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>TBL-005</t>
+          <t>TBL-004</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
@@ -5222,42 +5226,42 @@
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>E-4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>Data Up-Load</t>
+          <t>Table 범위 조회</t>
         </is>
       </c>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>Data/File/Image 자료 등록(부서·유형·이름·설명)</t>
+          <t>Macro 참조용 범위 조회 API(TableN(col,range))</t>
         </is>
       </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
-          <t>중복검토</t>
+          <t>GIN 인덱스, 캐시 적용</t>
         </is>
       </c>
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>시스템</t>
         </is>
       </c>
       <c r="I73" s="8" t="inlineStr">
         <is>
-          <t>SVC-05, SVC-12</t>
+          <t>SVC-05, ENG-01</t>
         </is>
       </c>
       <c r="J73" s="8" t="inlineStr">
         <is>
-          <t>tbl_data_table, dwg_file</t>
+          <t>tbl_data_row</t>
         </is>
       </c>
       <c r="K73" s="6" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="L73" s="6" t="inlineStr">
@@ -5273,7 +5277,7 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>TBL-006</t>
+          <t>TBL-005</t>
         </is>
       </c>
       <c r="C74" s="12" t="inlineStr">
@@ -5283,38 +5287,42 @@
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>E-4</t>
         </is>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>Table 승인</t>
+          <t>Data Up-Load</t>
         </is>
       </c>
       <c r="F74" s="8" t="inlineStr">
         <is>
-          <t>Table 정의·대량 변경 승인</t>
-        </is>
-      </c>
-      <c r="G74" s="8" t="inlineStr"/>
+          <t>Data/File/Image 자료 등록(부서·유형·이름·설명)</t>
+        </is>
+      </c>
+      <c r="G74" s="8" t="inlineStr">
+        <is>
+          <t>중복검토</t>
+        </is>
+      </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="I74" s="8" t="inlineStr">
         <is>
-          <t>SVC-10</t>
+          <t>SVC-05, SVC-12</t>
         </is>
       </c>
       <c r="J74" s="8" t="inlineStr">
         <is>
-          <t>tbl_data_table</t>
+          <t>tbl_data_table, dwg_file</t>
         </is>
       </c>
       <c r="K74" s="6" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="L74" s="6" t="inlineStr">
@@ -5330,52 +5338,48 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>TBX-001</t>
-        </is>
-      </c>
-      <c r="C75" s="13" t="inlineStr">
-        <is>
-          <t>TBX Toolbox</t>
+          <t>TBL-006</t>
+        </is>
+      </c>
+      <c r="C75" s="12" t="inlineStr">
+        <is>
+          <t>TBL 데이터 Table</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>S-2-1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>UI Designer 위젯 배치</t>
+          <t>Table 승인</t>
         </is>
       </c>
       <c r="F75" s="8" t="inlineStr">
         <is>
-          <t>Widget Palette(Button/Label/Entry/Text/Canvas/Frame/Menu/Combo/Table) Drag&amp;Drop</t>
-        </is>
-      </c>
-      <c r="G75" s="8" t="inlineStr">
-        <is>
-          <t>Qt Designer 방식 폼 빌더</t>
-        </is>
-      </c>
+          <t>Table 정의·대량 변경 승인</t>
+        </is>
+      </c>
+      <c r="G75" s="8" t="inlineStr"/>
       <c r="H75" s="6" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="I75" s="8" t="inlineStr">
         <is>
-          <t>FE-03, SVC-06</t>
+          <t>SVC-10</t>
         </is>
       </c>
       <c r="J75" s="8" t="inlineStr">
         <is>
-          <t>tbx_ui_form</t>
+          <t>tbl_data_table</t>
         </is>
       </c>
       <c r="K75" s="6" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="L75" s="6" t="inlineStr">
@@ -5391,7 +5395,7 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>TBX-002</t>
+          <t>TBX-001</t>
         </is>
       </c>
       <c r="C76" s="13" t="inlineStr">
@@ -5406,17 +5410,17 @@
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>동작 Templet 바인딩</t>
+          <t>UI Designer 위젯 배치</t>
         </is>
       </c>
       <c r="F76" s="8" t="inlineStr">
         <is>
-          <t>위젯별 동작(저장/삭제/복사/등록/찾기)·대상 Data 연결</t>
+          <t>Widget Palette(Button/Label/Entry/Text/Canvas/Frame/Menu/Combo/Table) Drag&amp;Drop</t>
         </is>
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>Set-up 전용 창(Templet)에서 설정</t>
+          <t>Qt Designer 방식 폼 빌더</t>
         </is>
       </c>
       <c r="H76" s="6" t="inlineStr">
@@ -5431,7 +5435,7 @@
       </c>
       <c r="J76" s="8" t="inlineStr">
         <is>
-          <t>tbx_ui_form, tbx_templet</t>
+          <t>tbx_ui_form</t>
         </is>
       </c>
       <c r="K76" s="6" t="inlineStr">
@@ -5452,7 +5456,7 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>TBX-003</t>
+          <t>TBX-002</t>
         </is>
       </c>
       <c r="C77" s="13" t="inlineStr">
@@ -5467,17 +5471,17 @@
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>Form 저장·버전·게시</t>
+          <t>동작 Templet 바인딩</t>
         </is>
       </c>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>layout_def 저장, 버전 관리, 승인 후 게시</t>
+          <t>위젯별 동작(저장/삭제/복사/등록/찾기)·대상 Data 연결</t>
         </is>
       </c>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>게시된 Form은 FE-01 동적 렌더러가 실행</t>
+          <t>Set-up 전용 창(Templet)에서 설정</t>
         </is>
       </c>
       <c r="H77" s="6" t="inlineStr">
@@ -5487,12 +5491,12 @@
       </c>
       <c r="I77" s="8" t="inlineStr">
         <is>
-          <t>SVC-06, SVC-10</t>
+          <t>FE-03, SVC-06</t>
         </is>
       </c>
       <c r="J77" s="8" t="inlineStr">
         <is>
-          <t>tbx_ui_form</t>
+          <t>tbx_ui_form, tbx_templet</t>
         </is>
       </c>
       <c r="K77" s="6" t="inlineStr">
@@ -5513,7 +5517,7 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>TBX-004</t>
+          <t>TBX-003</t>
         </is>
       </c>
       <c r="C78" s="13" t="inlineStr">
@@ -5528,17 +5532,17 @@
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>AI UI 제안</t>
+          <t>Form 저장·버전·게시</t>
         </is>
       </c>
       <c r="F78" s="8" t="inlineStr">
         <is>
-          <t>Application 설명 입력 → 용도/항목/필요 DB Table 정리된 UI 초안</t>
+          <t>layout_def 저장, 버전 관리, 승인 후 게시</t>
         </is>
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
-          <t>제안 후 사용자 Customizing</t>
+          <t>게시된 Form은 FE-01 동적 렌더러가 실행</t>
         </is>
       </c>
       <c r="H78" s="6" t="inlineStr">
@@ -5548,7 +5552,7 @@
       </c>
       <c r="I78" s="8" t="inlineStr">
         <is>
-          <t>AI-04, FE-03</t>
+          <t>SVC-06, SVC-10</t>
         </is>
       </c>
       <c r="J78" s="8" t="inlineStr">
@@ -5574,7 +5578,7 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>TBX-005</t>
+          <t>TBX-004</t>
         </is>
       </c>
       <c r="C79" s="13" t="inlineStr">
@@ -5584,22 +5588,22 @@
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>S-2-2</t>
+          <t>S-2-1</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>Prompt 입력</t>
+          <t>AI UI 제안</t>
         </is>
       </c>
       <c r="F79" s="8" t="inlineStr">
         <is>
-          <t>자연어로 계산 요구 기술</t>
+          <t>Application 설명 입력 → 용도/항목/필요 DB Table 정리된 UI 초안</t>
         </is>
       </c>
       <c r="G79" s="8" t="inlineStr">
         <is>
-          <t>예: SS Fan 샤프트 길이 계산</t>
+          <t>제안 후 사용자 Customizing</t>
         </is>
       </c>
       <c r="H79" s="6" t="inlineStr">
@@ -5609,12 +5613,12 @@
       </c>
       <c r="I79" s="8" t="inlineStr">
         <is>
-          <t>FE-03, AI-03</t>
+          <t>AI-04, FE-03</t>
         </is>
       </c>
       <c r="J79" s="8" t="inlineStr">
         <is>
-          <t>tbx_macro</t>
+          <t>tbx_ui_form</t>
         </is>
       </c>
       <c r="K79" s="6" t="inlineStr">
@@ -5635,7 +5639,7 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>TBX-006</t>
+          <t>TBX-005</t>
         </is>
       </c>
       <c r="C80" s="13" t="inlineStr">
@@ -5650,17 +5654,17 @@
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>Macro 수식 편집</t>
+          <t>Prompt 입력</t>
         </is>
       </c>
       <c r="F80" s="8" t="inlineStr">
         <is>
-          <t>Excel 문법 계산식 작성(TableN/Var/PreC 참조)</t>
+          <t>자연어로 계산 요구 기술</t>
         </is>
       </c>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t>문법 특허 검토 결과 반영</t>
+          <t>예: SS Fan 샤프트 길이 계산</t>
         </is>
       </c>
       <c r="H80" s="6" t="inlineStr">
@@ -5670,7 +5674,7 @@
       </c>
       <c r="I80" s="8" t="inlineStr">
         <is>
-          <t>FE-03, ENG-01</t>
+          <t>FE-03, AI-03</t>
         </is>
       </c>
       <c r="J80" s="8" t="inlineStr">
@@ -5680,7 +5684,7 @@
       </c>
       <c r="K80" s="6" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="L80" s="6" t="inlineStr">
@@ -5688,11 +5692,7 @@
           <t>미정</t>
         </is>
       </c>
-      <c r="M80" s="8" t="inlineStr">
-        <is>
-          <t>엔진은 P1</t>
-        </is>
-      </c>
+      <c r="M80" s="8" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="6" t="n">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>TBX-007</t>
+          <t>TBX-006</t>
         </is>
       </c>
       <c r="C81" s="13" t="inlineStr">
@@ -5715,15 +5715,19 @@
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>Flowchart 편집</t>
+          <t>Macro 수식 편집</t>
         </is>
       </c>
       <c r="F81" s="8" t="inlineStr">
         <is>
-          <t>흐름도 기반 로직 편집</t>
-        </is>
-      </c>
-      <c r="G81" s="8" t="inlineStr"/>
+          <t>Excel 문법 계산식 작성(TableN/Var/PreC 참조)</t>
+        </is>
+      </c>
+      <c r="G81" s="8" t="inlineStr">
+        <is>
+          <t>문법 특허 검토 결과 반영</t>
+        </is>
+      </c>
       <c r="H81" s="6" t="inlineStr">
         <is>
           <t>SETUP</t>
@@ -5731,7 +5735,7 @@
       </c>
       <c r="I81" s="8" t="inlineStr">
         <is>
-          <t>FE-03</t>
+          <t>FE-03, ENG-01</t>
         </is>
       </c>
       <c r="J81" s="8" t="inlineStr">
@@ -5741,7 +5745,7 @@
       </c>
       <c r="K81" s="6" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="L81" s="6" t="inlineStr">
@@ -5749,7 +5753,11 @@
           <t>미정</t>
         </is>
       </c>
-      <c r="M81" s="8" t="inlineStr"/>
+      <c r="M81" s="8" t="inlineStr">
+        <is>
+          <t>엔진은 P1</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="n">
@@ -5757,7 +5765,7 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>TBX-008</t>
+          <t>TBX-007</t>
         </is>
       </c>
       <c r="C82" s="13" t="inlineStr">
@@ -5772,19 +5780,15 @@
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>4-Way Sync 변환</t>
+          <t>Flowchart 편집</t>
         </is>
       </c>
       <c r="F82" s="8" t="inlineStr">
         <is>
-          <t>Prompt↔Macro↔Flowchart↔Coding 실시간 상호 변환</t>
-        </is>
-      </c>
-      <c r="G82" s="8" t="inlineStr">
-        <is>
-          <t>AI 변환, Description 동시 갱신</t>
-        </is>
-      </c>
+          <t>흐름도 기반 로직 편집</t>
+        </is>
+      </c>
+      <c r="G82" s="8" t="inlineStr"/>
       <c r="H82" s="6" t="inlineStr">
         <is>
           <t>SETUP</t>
@@ -5792,7 +5796,7 @@
       </c>
       <c r="I82" s="8" t="inlineStr">
         <is>
-          <t>AI-03, ENG-01</t>
+          <t>FE-03</t>
         </is>
       </c>
       <c r="J82" s="8" t="inlineStr">
@@ -5810,11 +5814,7 @@
           <t>미정</t>
         </is>
       </c>
-      <c r="M82" s="8" t="inlineStr">
-        <is>
-          <t>핵심 차별점</t>
-        </is>
-      </c>
+      <c r="M82" s="8" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="6" t="n">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>TBX-009</t>
+          <t>TBX-008</t>
         </is>
       </c>
       <c r="C83" s="13" t="inlineStr">
@@ -5837,17 +5837,17 @@
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>함수·그래프 마법사</t>
+          <t>4-Way Sync 변환</t>
         </is>
       </c>
       <c r="F83" s="8" t="inlineStr">
         <is>
-          <t>함수 검색/설명/삽입, 그래프 유형 선택 마법사</t>
+          <t>Prompt↔Macro↔Flowchart↔Coding 실시간 상호 변환</t>
         </is>
       </c>
       <c r="G83" s="8" t="inlineStr">
         <is>
-          <t>공학 함수 Templet 포함</t>
+          <t>AI 변환, Description 동시 갱신</t>
         </is>
       </c>
       <c r="H83" s="6" t="inlineStr">
@@ -5857,12 +5857,12 @@
       </c>
       <c r="I83" s="8" t="inlineStr">
         <is>
-          <t>FE-03</t>
+          <t>AI-03, ENG-01</t>
         </is>
       </c>
       <c r="J83" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>tbx_macro</t>
         </is>
       </c>
       <c r="K83" s="6" t="inlineStr">
@@ -5875,7 +5875,11 @@
           <t>미정</t>
         </is>
       </c>
-      <c r="M83" s="8" t="inlineStr"/>
+      <c r="M83" s="8" t="inlineStr">
+        <is>
+          <t>핵심 차별점</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="6" t="n">
@@ -5883,7 +5887,7 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>TBX-010</t>
+          <t>TBX-009</t>
         </is>
       </c>
       <c r="C84" s="13" t="inlineStr">
@@ -5898,17 +5902,17 @@
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>Data Information Call</t>
+          <t>함수·그래프 마법사</t>
         </is>
       </c>
       <c r="F84" s="8" t="inlineStr">
         <is>
-          <t>Enterprise DB(Table/Chart/Formula) 탐색·주소 지정</t>
+          <t>함수 검색/설명/삽입, 그래프 유형 선택 마법사</t>
         </is>
       </c>
       <c r="G84" s="8" t="inlineStr">
         <is>
-          <t>Hierarchy 주소 기반</t>
+          <t>공학 함수 Templet 포함</t>
         </is>
       </c>
       <c r="H84" s="6" t="inlineStr">
@@ -5918,12 +5922,12 @@
       </c>
       <c r="I84" s="8" t="inlineStr">
         <is>
-          <t>FE-03, SVC-05</t>
+          <t>FE-03</t>
         </is>
       </c>
       <c r="J84" s="8" t="inlineStr">
         <is>
-          <t>tbl_data_table</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K84" s="6" t="inlineStr">
@@ -5944,7 +5948,7 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>TBX-011</t>
+          <t>TBX-010</t>
         </is>
       </c>
       <c r="C85" s="13" t="inlineStr">
@@ -5959,17 +5963,17 @@
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>Macro Test Run</t>
+          <t>Data Information Call</t>
         </is>
       </c>
       <c r="F85" s="8" t="inlineStr">
         <is>
-          <t>조건값 입력 → 계산 실행 → 결과 확인</t>
+          <t>Enterprise DB(Table/Chart/Formula) 탐색·주소 지정</t>
         </is>
       </c>
       <c r="G85" s="8" t="inlineStr">
         <is>
-          <t>결과·입력 저장(test_input/result)</t>
+          <t>Hierarchy 주소 기반</t>
         </is>
       </c>
       <c r="H85" s="6" t="inlineStr">
@@ -5979,17 +5983,17 @@
       </c>
       <c r="I85" s="8" t="inlineStr">
         <is>
-          <t>ENG-01</t>
+          <t>FE-03, SVC-05</t>
         </is>
       </c>
       <c r="J85" s="8" t="inlineStr">
         <is>
-          <t>tbx_macro</t>
+          <t>tbl_data_table</t>
         </is>
       </c>
       <c r="K85" s="6" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="L85" s="6" t="inlineStr">
@@ -6005,7 +6009,7 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>TBX-012</t>
+          <t>TBX-011</t>
         </is>
       </c>
       <c r="C86" s="13" t="inlineStr">
@@ -6020,27 +6024,27 @@
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>Macro 승인·버전</t>
+          <t>Macro Test Run</t>
         </is>
       </c>
       <c r="F86" s="8" t="inlineStr">
         <is>
-          <t>생성/편집/삭제의 엄격한 검증·승인 절차, 버전 관리</t>
+          <t>조건값 입력 → 계산 실행 → 결과 확인</t>
         </is>
       </c>
       <c r="G86" s="8" t="inlineStr">
         <is>
-          <t>미승인 Macro는 Run에서 사용 불가</t>
+          <t>결과·입력 저장(test_input/result)</t>
         </is>
       </c>
       <c r="H86" s="6" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="I86" s="8" t="inlineStr">
         <is>
-          <t>SVC-10</t>
+          <t>ENG-01</t>
         </is>
       </c>
       <c r="J86" s="8" t="inlineStr">
@@ -6066,7 +6070,7 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>TBX-013</t>
+          <t>TBX-012</t>
         </is>
       </c>
       <c r="C87" s="13" t="inlineStr">
@@ -6076,42 +6080,42 @@
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>S-2-1</t>
+          <t>S-2-2</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>Templet 관리</t>
+          <t>Macro 승인·버전</t>
         </is>
       </c>
       <c r="F87" s="8" t="inlineStr">
         <is>
-          <t>Command button/Combo/Data Table/Print/Graph Templet 등록·재사용</t>
+          <t>생성/편집/삭제의 엄격한 검증·승인 절차, 버전 관리</t>
         </is>
       </c>
       <c r="G87" s="8" t="inlineStr">
         <is>
-          <t>is_system Templet은 EDIM 제공</t>
+          <t>미승인 Macro는 Run에서 사용 불가</t>
         </is>
       </c>
       <c r="H87" s="6" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="I87" s="8" t="inlineStr">
         <is>
-          <t>SVC-06</t>
+          <t>SVC-10</t>
         </is>
       </c>
       <c r="J87" s="8" t="inlineStr">
         <is>
-          <t>tbx_templet</t>
+          <t>tbx_macro</t>
         </is>
       </c>
       <c r="K87" s="6" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="L87" s="6" t="inlineStr">
@@ -6127,7 +6131,7 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>TBX-014</t>
+          <t>TBX-013</t>
         </is>
       </c>
       <c r="C88" s="13" t="inlineStr">
@@ -6137,37 +6141,37 @@
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>S-2-2</t>
+          <t>S-2-1</t>
         </is>
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>기능 찾기·도움말</t>
+          <t>Templet 관리</t>
         </is>
       </c>
       <c r="F88" s="8" t="inlineStr">
         <is>
-          <t>자연어로 필요 기능/함수 검색(기능 찾기), User Help·Manual 연동</t>
+          <t>Command button/Combo/Data Table/Print/Graph Templet 등록·재사용</t>
         </is>
       </c>
       <c r="G88" s="8" t="inlineStr">
         <is>
-          <t>AI 기반 함수 추천</t>
+          <t>is_system Templet은 EDIM 제공</t>
         </is>
       </c>
       <c r="H88" s="6" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="I88" s="8" t="inlineStr">
         <is>
-          <t>AI-03, FE-03</t>
+          <t>SVC-06</t>
         </is>
       </c>
       <c r="J88" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>tbx_templet</t>
         </is>
       </c>
       <c r="K88" s="6" t="inlineStr">
@@ -6180,11 +6184,7 @@
           <t>미정</t>
         </is>
       </c>
-      <c r="M88" s="8" t="inlineStr">
-        <is>
-          <t>슬라이드 29</t>
-        </is>
-      </c>
+      <c r="M88" s="8" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="6" t="n">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>TBX-015</t>
+          <t>TBX-014</t>
         </is>
       </c>
       <c r="C89" s="13" t="inlineStr">
@@ -6207,17 +6207,17 @@
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>인터넷 검색·AI 질의</t>
+          <t>기능 찾기·도움말</t>
         </is>
       </c>
       <c r="F89" s="8" t="inlineStr">
         <is>
-          <t>Toolbox 내 인터넷 검색 기능, AI 질의응답(내부 자료 검색·응답)</t>
+          <t>자연어로 필요 기능/함수 검색(기능 찾기), User Help·Manual 연동</t>
         </is>
       </c>
       <c r="G89" s="8" t="inlineStr">
         <is>
-          <t>발표자 노트 명시 요건</t>
+          <t>AI 기반 함수 추천</t>
         </is>
       </c>
       <c r="H89" s="6" t="inlineStr">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="I89" s="8" t="inlineStr">
         <is>
-          <t>AI-05, FE-03</t>
+          <t>AI-03, FE-03</t>
         </is>
       </c>
       <c r="J89" s="8" t="inlineStr">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="K89" s="6" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="L89" s="6" t="inlineStr">
@@ -6247,7 +6247,7 @@
       </c>
       <c r="M89" s="8" t="inlineStr">
         <is>
-          <t>슬라이드 27 노트</t>
+          <t>슬라이드 29</t>
         </is>
       </c>
     </row>
@@ -6257,52 +6257,52 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>CPQ-001</t>
-        </is>
-      </c>
-      <c r="C90" s="14" t="inlineStr">
-        <is>
-          <t>CPQ CPQ 제품선정</t>
+          <t>TBX-015</t>
+        </is>
+      </c>
+      <c r="C90" s="13" t="inlineStr">
+        <is>
+          <t>TBX Toolbox</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>C-1</t>
+          <t>S-2-2</t>
         </is>
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>제품 선정 화면</t>
+          <t>인터넷 검색·AI 질의</t>
         </is>
       </c>
       <c r="F90" s="8" t="inlineStr">
         <is>
-          <t>Product Tree에서 제품 선택, Selection 시작</t>
+          <t>Toolbox 내 인터넷 검색 기능, AI 질의응답(내부 자료 검색·응답)</t>
         </is>
       </c>
       <c r="G90" s="8" t="inlineStr">
         <is>
-          <t>승인된 코드만 표시</t>
+          <t>발표자 노트 명시 요건</t>
         </is>
       </c>
       <c r="H90" s="6" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>전체</t>
         </is>
       </c>
       <c r="I90" s="8" t="inlineStr">
         <is>
-          <t>FE-01, SVC-07</t>
+          <t>AI-05, FE-03</t>
         </is>
       </c>
       <c r="J90" s="8" t="inlineStr">
         <is>
-          <t>cpq_selection</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K90" s="6" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="L90" s="6" t="inlineStr">
@@ -6310,7 +6310,11 @@
           <t>미정</t>
         </is>
       </c>
-      <c r="M90" s="8" t="inlineStr"/>
+      <c r="M90" s="8" t="inlineStr">
+        <is>
+          <t>슬라이드 27 노트</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="n">
@@ -6318,7 +6322,7 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>CPQ-002</t>
+          <t>CPQ-001</t>
         </is>
       </c>
       <c r="C91" s="14" t="inlineStr">
@@ -6333,17 +6337,17 @@
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>Arrangement 구성</t>
+          <t>제품 선정 화면</t>
         </is>
       </c>
       <c r="F91" s="8" t="inlineStr">
         <is>
-          <t>모듈 이미지 Drag 조합, 이동/삭제/분할/통합, 치수 DB 표시</t>
+          <t>Product Tree에서 제품 선택, Selection 시작</t>
         </is>
       </c>
       <c r="G91" s="8" t="inlineStr">
         <is>
-          <t>화면·도면 비율 자동 조절, 기준 치수 입력 시 하부 반영</t>
+          <t>승인된 코드만 표시</t>
         </is>
       </c>
       <c r="H91" s="6" t="inlineStr">
@@ -6358,7 +6362,7 @@
       </c>
       <c r="J91" s="8" t="inlineStr">
         <is>
-          <t>cpq_selection, arrangement_*</t>
+          <t>cpq_selection</t>
         </is>
       </c>
       <c r="K91" s="6" t="inlineStr">
@@ -6371,11 +6375,7 @@
           <t>미정</t>
         </is>
       </c>
-      <c r="M91" s="8" t="inlineStr">
-        <is>
-          <t>노트 워크플로우 2</t>
-        </is>
-      </c>
+      <c r="M91" s="8" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="6" t="n">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>CPQ-003</t>
+          <t>CPQ-002</t>
         </is>
       </c>
       <c r="C92" s="14" t="inlineStr">
@@ -6398,17 +6398,17 @@
       </c>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t>사양 입력</t>
+          <t>Arrangement 구성</t>
         </is>
       </c>
       <c r="F92" s="8" t="inlineStr">
         <is>
-          <t>Spec List 입력 Table(풍량·정압·온도 등)</t>
+          <t>모듈 이미지 Drag 조합, 이동/삭제/분할/통합, 치수 DB 표시</t>
         </is>
       </c>
       <c r="G92" s="8" t="inlineStr">
         <is>
-          <t>Slot 값 선택 → 제품 Code 부분 결정</t>
+          <t>화면·도면 비율 자동 조절, 기준 치수 입력 시 하부 반영</t>
         </is>
       </c>
       <c r="H92" s="6" t="inlineStr">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="J92" s="8" t="inlineStr">
         <is>
-          <t>cpq_selection</t>
+          <t>cpq_selection, arrangement_*</t>
         </is>
       </c>
       <c r="K92" s="6" t="inlineStr">
@@ -6436,7 +6436,11 @@
           <t>미정</t>
         </is>
       </c>
-      <c r="M92" s="8" t="inlineStr"/>
+      <c r="M92" s="8" t="inlineStr">
+        <is>
+          <t>노트 워크플로우 2</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="n">
@@ -6444,7 +6448,7 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>CPQ-004</t>
+          <t>CPQ-003</t>
         </is>
       </c>
       <c r="C93" s="14" t="inlineStr">
@@ -6459,15 +6463,19 @@
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>고객 사양 Excel Import</t>
+          <t>사양 입력</t>
         </is>
       </c>
       <c r="F93" s="8" t="inlineStr">
         <is>
-          <t>정해진 Excel 양식 Import → Selection 입력 항 자동 적용</t>
-        </is>
-      </c>
-      <c r="G93" s="8" t="inlineStr"/>
+          <t>Spec List 입력 Table(풍량·정압·온도 등)</t>
+        </is>
+      </c>
+      <c r="G93" s="8" t="inlineStr">
+        <is>
+          <t>Slot 값 선택 → 제품 Code 부분 결정</t>
+        </is>
+      </c>
       <c r="H93" s="6" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -6475,7 +6483,7 @@
       </c>
       <c r="I93" s="8" t="inlineStr">
         <is>
-          <t>INT-03, SVC-07</t>
+          <t>FE-01, SVC-07</t>
         </is>
       </c>
       <c r="J93" s="8" t="inlineStr">
@@ -6485,7 +6493,7 @@
       </c>
       <c r="K93" s="6" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="L93" s="6" t="inlineStr">
@@ -6501,7 +6509,7 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>CPQ-005</t>
+          <t>CPQ-004</t>
         </is>
       </c>
       <c r="C94" s="14" t="inlineStr">
@@ -6511,24 +6519,20 @@
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>C-2</t>
+          <t>C-1</t>
         </is>
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t>기술 데이터 화면</t>
+          <t>고객 사양 Excel Import</t>
         </is>
       </c>
       <c r="F94" s="8" t="inlineStr">
         <is>
-          <t>Fan 선정 상세(Impeller/Motor/Casing 옵션), 성능 곡선, 기술 Table</t>
-        </is>
-      </c>
-      <c r="G94" s="8" t="inlineStr">
-        <is>
-          <t>선정 분류·SL No 관리</t>
-        </is>
-      </c>
+          <t>정해진 Excel 양식 Import → Selection 입력 항 자동 적용</t>
+        </is>
+      </c>
+      <c r="G94" s="8" t="inlineStr"/>
       <c r="H94" s="6" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -6536,12 +6540,12 @@
       </c>
       <c r="I94" s="8" t="inlineStr">
         <is>
-          <t>FE-01, SVC-07</t>
+          <t>INT-03, SVC-07</t>
         </is>
       </c>
       <c r="J94" s="8" t="inlineStr">
         <is>
-          <t>cpq_selection, tbl_*</t>
+          <t>cpq_selection</t>
         </is>
       </c>
       <c r="K94" s="6" t="inlineStr">
@@ -6562,7 +6566,7 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>CPQ-006</t>
+          <t>CPQ-005</t>
         </is>
       </c>
       <c r="C95" s="14" t="inlineStr">
@@ -6572,22 +6576,22 @@
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>C-3</t>
+          <t>C-2</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>Document Template</t>
+          <t>기술 데이터 화면</t>
         </is>
       </c>
       <c r="F95" s="8" t="inlineStr">
         <is>
-          <t>입력값(온도·습도)→Macro 계산→출력값(밀도), 그래프 표시</t>
+          <t>Fan 선정 상세(Impeller/Motor/Casing 옵션), 성능 곡선, 기술 Table</t>
         </is>
       </c>
       <c r="G95" s="8" t="inlineStr">
         <is>
-          <t>그래프 전용 Data Table Templet</t>
+          <t>선정 분류·SL No 관리</t>
         </is>
       </c>
       <c r="H95" s="6" t="inlineStr">
@@ -6597,12 +6601,12 @@
       </c>
       <c r="I95" s="8" t="inlineStr">
         <is>
-          <t>FE-01, ENG-01</t>
+          <t>FE-01, SVC-07</t>
         </is>
       </c>
       <c r="J95" s="8" t="inlineStr">
         <is>
-          <t>tbx_ui_form</t>
+          <t>cpq_selection, tbl_*</t>
         </is>
       </c>
       <c r="K95" s="6" t="inlineStr">
@@ -6615,11 +6619,7 @@
           <t>미정</t>
         </is>
       </c>
-      <c r="M95" s="8" t="inlineStr">
-        <is>
-          <t>노트 워크플로우 3</t>
-        </is>
-      </c>
+      <c r="M95" s="8" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="n">
@@ -6627,7 +6627,7 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>CPQ-007</t>
+          <t>CPQ-006</t>
         </is>
       </c>
       <c r="C96" s="14" t="inlineStr">
@@ -6637,22 +6637,22 @@
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>C-1</t>
+          <t>C-3</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t>완성품 Code 생성</t>
+          <t>Document Template</t>
         </is>
       </c>
       <c r="F96" s="8" t="inlineStr">
         <is>
-          <t>Slot 선택 조합 → Finished Goods Code 확정</t>
+          <t>입력값(온도·습도)→Macro 계산→출력값(밀도), 그래프 표시</t>
         </is>
       </c>
       <c r="G96" s="8" t="inlineStr">
         <is>
-          <t>미완성 Slot 존재 시 확정 불가</t>
+          <t>그래프 전용 Data Table Templet</t>
         </is>
       </c>
       <c r="H96" s="6" t="inlineStr">
@@ -6662,17 +6662,17 @@
       </c>
       <c r="I96" s="8" t="inlineStr">
         <is>
-          <t>SVC-07, SVC-03</t>
+          <t>FE-01, ENG-01</t>
         </is>
       </c>
       <c r="J96" s="8" t="inlineStr">
         <is>
-          <t>cpq_selection</t>
+          <t>tbx_ui_form</t>
         </is>
       </c>
       <c r="K96" s="6" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="L96" s="6" t="inlineStr">
@@ -6680,7 +6680,11 @@
           <t>미정</t>
         </is>
       </c>
-      <c r="M96" s="8" t="inlineStr"/>
+      <c r="M96" s="8" t="inlineStr">
+        <is>
+          <t>노트 워크플로우 3</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="n">
@@ -6688,7 +6692,7 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>CPQ-008</t>
+          <t>CPQ-007</t>
         </is>
       </c>
       <c r="C97" s="14" t="inlineStr">
@@ -6703,17 +6707,17 @@
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>Sub Item List 조회</t>
+          <t>완성품 Code 생성</t>
         </is>
       </c>
       <c r="F97" s="8" t="inlineStr">
         <is>
-          <t>완성품 Code 연결 하위 Code 전개 목록, Click 시 세부 정보</t>
+          <t>Slot 선택 조합 → Finished Goods Code 확정</t>
         </is>
       </c>
       <c r="G97" s="8" t="inlineStr">
         <is>
-          <t>BOM Code Relationship의 Mother 연결 Sub 추출</t>
+          <t>미완성 Slot 존재 시 확정 불가</t>
         </is>
       </c>
       <c r="H97" s="6" t="inlineStr">
@@ -6723,12 +6727,12 @@
       </c>
       <c r="I97" s="8" t="inlineStr">
         <is>
-          <t>SVC-07</t>
+          <t>SVC-07, SVC-03</t>
         </is>
       </c>
       <c r="J97" s="8" t="inlineStr">
         <is>
-          <t>cpq_selection_item</t>
+          <t>cpq_selection</t>
         </is>
       </c>
       <c r="K97" s="6" t="inlineStr">
@@ -6749,7 +6753,7 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>CPQ-009</t>
+          <t>CPQ-008</t>
         </is>
       </c>
       <c r="C98" s="14" t="inlineStr">
@@ -6759,27 +6763,27 @@
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>C-1</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>X-Code 비규격 처리</t>
+          <t>Sub Item List 조회</t>
         </is>
       </c>
       <c r="F98" s="8" t="inlineStr">
         <is>
-          <t>비표준 Option 선택 시 X-Code 표시→검토요청→R&amp;D 신규설계→신규코드 등록→복귀</t>
+          <t>완성품 Code 연결 하위 Code 전개 목록, Click 시 세부 정보</t>
         </is>
       </c>
       <c r="G98" s="8" t="inlineStr">
         <is>
-          <t>X-Code 상태 추적</t>
+          <t>BOM Code Relationship의 Mother 연결 Sub 추출</t>
         </is>
       </c>
       <c r="H98" s="6" t="inlineStr">
         <is>
-          <t>GENERAL/R&amp;D</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="I98" s="8" t="inlineStr">
@@ -6789,12 +6793,12 @@
       </c>
       <c r="J98" s="8" t="inlineStr">
         <is>
-          <t>cpq_selection</t>
+          <t>cpq_selection_item</t>
         </is>
       </c>
       <c r="K98" s="6" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="L98" s="6" t="inlineStr">
@@ -6810,7 +6814,7 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>CPQ-010</t>
+          <t>CPQ-009</t>
         </is>
       </c>
       <c r="C99" s="14" t="inlineStr">
@@ -6820,42 +6824,42 @@
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>C-1</t>
+          <t>D-2</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>DWG View</t>
+          <t>X-Code 비규격 처리</t>
         </is>
       </c>
       <c r="F99" s="8" t="inlineStr">
         <is>
-          <t>선정 제품 도면 확인, 3각법 6면·전체 View</t>
+          <t>비표준 Option 선택 시 X-Code 표시→검토요청→R&amp;D 신규설계→신규코드 등록→복귀</t>
         </is>
       </c>
       <c r="G99" s="8" t="inlineStr">
         <is>
-          <t>SVG 렌더, 팬줌·레이어</t>
+          <t>X-Code 상태 추적</t>
         </is>
       </c>
       <c r="H99" s="6" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GENERAL/R&amp;D</t>
         </is>
       </c>
       <c r="I99" s="8" t="inlineStr">
         <is>
-          <t>FE-01</t>
+          <t>SVC-07</t>
         </is>
       </c>
       <c r="J99" s="8" t="inlineStr">
         <is>
-          <t>dwg_document</t>
+          <t>cpq_selection</t>
         </is>
       </c>
       <c r="K99" s="6" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="L99" s="6" t="inlineStr">
@@ -6871,7 +6875,7 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>CPQ-011</t>
+          <t>CPQ-010</t>
         </is>
       </c>
       <c r="C100" s="14" t="inlineStr">
@@ -6881,42 +6885,42 @@
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>S-3-1</t>
+          <t>C-1</t>
         </is>
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>Selection Set-up</t>
+          <t>DWG View</t>
         </is>
       </c>
       <c r="F100" s="8" t="inlineStr">
         <is>
-          <t>선정 UI 구성 — Product Tree 가져오기, Item Image·Arrangement 정의</t>
+          <t>선정 제품 도면 확인, 3각법 6면·전체 View</t>
         </is>
       </c>
       <c r="G100" s="8" t="inlineStr">
         <is>
-          <t>Call Form으로 구성</t>
+          <t>SVG 렌더, 팬줌·레이어</t>
         </is>
       </c>
       <c r="H100" s="6" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="I100" s="8" t="inlineStr">
         <is>
-          <t>FE-02, SVC-06</t>
+          <t>FE-01</t>
         </is>
       </c>
       <c r="J100" s="8" t="inlineStr">
         <is>
-          <t>tbx_ui_form</t>
+          <t>dwg_document</t>
         </is>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="L100" s="6" t="inlineStr">
@@ -6932,7 +6936,7 @@
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>CPQ-012</t>
+          <t>CPQ-011</t>
         </is>
       </c>
       <c r="C101" s="14" t="inlineStr">
@@ -6942,20 +6946,24 @@
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>S-3-2/3</t>
+          <t>S-3-1</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>Technical·Document Set-up</t>
+          <t>Selection Set-up</t>
         </is>
       </c>
       <c r="F101" s="8" t="inlineStr">
         <is>
-          <t>기술 Data/서류 Form 구성(입출력 항목·그래프 Templet)</t>
-        </is>
-      </c>
-      <c r="G101" s="8" t="inlineStr"/>
+          <t>선정 UI 구성 — Product Tree 가져오기, Item Image·Arrangement 정의</t>
+        </is>
+      </c>
+      <c r="G101" s="8" t="inlineStr">
+        <is>
+          <t>Call Form으로 구성</t>
+        </is>
+      </c>
       <c r="H101" s="6" t="inlineStr">
         <is>
           <t>SETUP</t>
@@ -6989,7 +6997,7 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>CPQ-013</t>
+          <t>CPQ-012</t>
         </is>
       </c>
       <c r="C102" s="14" t="inlineStr">
@@ -6999,24 +7007,20 @@
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>S-3-4</t>
+          <t>S-3-2/3</t>
         </is>
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>Print Set-up</t>
+          <t>Technical·Document Set-up</t>
         </is>
       </c>
       <c r="F102" s="8" t="inlineStr">
         <is>
-          <t>양식 배치·Data 위치·그래프·워터마크·Font·용지·머리글/바닥글·내보내기(PDF/Office)</t>
-        </is>
-      </c>
-      <c r="G102" s="8" t="inlineStr">
-        <is>
-          <t>Print Test 기능</t>
-        </is>
-      </c>
+          <t>기술 Data/서류 Form 구성(입출력 항목·그래프 Templet)</t>
+        </is>
+      </c>
+      <c r="G102" s="8" t="inlineStr"/>
       <c r="H102" s="6" t="inlineStr">
         <is>
           <t>SETUP</t>
@@ -7024,7 +7028,7 @@
       </c>
       <c r="I102" s="8" t="inlineStr">
         <is>
-          <t>FE-02, SVC-11</t>
+          <t>FE-02, SVC-06</t>
         </is>
       </c>
       <c r="J102" s="8" t="inlineStr">
@@ -7050,7 +7054,7 @@
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>CPQ-014</t>
+          <t>CPQ-013</t>
         </is>
       </c>
       <c r="C103" s="14" t="inlineStr">
@@ -7060,22 +7064,22 @@
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>E-2</t>
+          <t>S-3-4</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>Selection Toolbar 구성</t>
+          <t>Print Set-up</t>
         </is>
       </c>
       <c r="F103" s="8" t="inlineStr">
         <is>
-          <t>사용자 명령 버튼 Templet 제작 — Arrangement/Move/Delete/Add/Copy/DWG View, 사양 입력 Combo, 정형화 사양 호출(Excel), 도구 이미지 설정</t>
+          <t>양식 배치·Data 위치·그래프·워터마크·Font·용지·머리글/바닥글·내보내기(PDF/Office)</t>
         </is>
       </c>
       <c r="G103" s="8" t="inlineStr">
         <is>
-          <t>EDIM Toolbar로 제작, 다양한 Macro 준비 필요</t>
+          <t>Print Test 기능</t>
         </is>
       </c>
       <c r="H103" s="6" t="inlineStr">
@@ -7085,12 +7089,12 @@
       </c>
       <c r="I103" s="8" t="inlineStr">
         <is>
-          <t>FE-02, SVC-06</t>
+          <t>FE-02, SVC-11</t>
         </is>
       </c>
       <c r="J103" s="8" t="inlineStr">
         <is>
-          <t>tbx_templet</t>
+          <t>tbx_ui_form</t>
         </is>
       </c>
       <c r="K103" s="6" t="inlineStr">
@@ -7103,11 +7107,7 @@
           <t>미정</t>
         </is>
       </c>
-      <c r="M103" s="8" t="inlineStr">
-        <is>
-          <t>슬라이드 60</t>
-        </is>
-      </c>
+      <c r="M103" s="8" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="6" t="n">
@@ -7115,7 +7115,7 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>CPQ-015</t>
+          <t>CPQ-014</t>
         </is>
       </c>
       <c r="C104" s="14" t="inlineStr">
@@ -7130,17 +7130,17 @@
       </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>Module 이미지 제작</t>
+          <t>Selection Toolbar 구성</t>
         </is>
       </c>
       <c r="F104" s="8" t="inlineStr">
         <is>
-          <t>제품 구성용 Module 그림 제작 도구(그림 제작 Modul) — 저장 이미지 호출·제어</t>
+          <t>사용자 명령 버튼 Templet 제작 — Arrangement/Move/Delete/Add/Copy/DWG View, 사양 입력 Combo, 정형화 사양 호출(Excel), 도구 이미지 설정</t>
         </is>
       </c>
       <c r="G104" s="8" t="inlineStr">
         <is>
-          <t>등록 Arrangement의 구성 제품 호출과 연동</t>
+          <t>EDIM Toolbar로 제작, 다양한 Macro 준비 필요</t>
         </is>
       </c>
       <c r="H104" s="6" t="inlineStr">
@@ -7150,12 +7150,12 @@
       </c>
       <c r="I104" s="8" t="inlineStr">
         <is>
-          <t>FE-02, SVC-04</t>
+          <t>FE-02, SVC-06</t>
         </is>
       </c>
       <c r="J104" s="8" t="inlineStr">
         <is>
-          <t>dwg_document</t>
+          <t>tbx_templet</t>
         </is>
       </c>
       <c r="K104" s="6" t="inlineStr">
@@ -7180,52 +7180,52 @@
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>RUN-001</t>
-        </is>
-      </c>
-      <c r="C105" s="15" t="inlineStr">
-        <is>
-          <t>RUN EDIM Run</t>
+          <t>CPQ-015</t>
+        </is>
+      </c>
+      <c r="C105" s="14" t="inlineStr">
+        <is>
+          <t>CPQ CPQ 제품선정</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>E-2</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>Run 실행 요청</t>
+          <t>Module 이미지 제작</t>
         </is>
       </c>
       <c r="F105" s="8" t="inlineStr">
         <is>
-          <t>Selection에서 BOM/DWG/PRICING/TECH/ALL 실행</t>
+          <t>제품 구성용 Module 그림 제작 도구(그림 제작 Modul) — 저장 이미지 호출·제어</t>
         </is>
       </c>
       <c r="G105" s="8" t="inlineStr">
         <is>
-          <t>비동기 잡 큐, 부분 실행 지원</t>
+          <t>등록 Arrangement의 구성 제품 호출과 연동</t>
         </is>
       </c>
       <c r="H105" s="6" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="I105" s="8" t="inlineStr">
         <is>
-          <t>SVC-07, ENG-02</t>
+          <t>FE-02, SVC-04</t>
         </is>
       </c>
       <c r="J105" s="8" t="inlineStr">
         <is>
-          <t>cpq_run</t>
+          <t>dwg_document</t>
         </is>
       </c>
       <c r="K105" s="6" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="L105" s="6" t="inlineStr">
@@ -7233,7 +7233,11 @@
           <t>미정</t>
         </is>
       </c>
-      <c r="M105" s="8" t="inlineStr"/>
+      <c r="M105" s="8" t="inlineStr">
+        <is>
+          <t>슬라이드 60</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="6" t="n">
@@ -7241,7 +7245,7 @@
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>RUN-002</t>
+          <t>RUN-001</t>
         </is>
       </c>
       <c r="C106" s="15" t="inlineStr">
@@ -7256,32 +7260,32 @@
       </c>
       <c r="E106" s="8" t="inlineStr">
         <is>
-          <t>BOM·Part List 생성</t>
+          <t>Run 실행 요청</t>
         </is>
       </c>
       <c r="F106" s="8" t="inlineStr">
         <is>
-          <t>Main Code 시작 Code Relationship 전개 → BOM 저장</t>
+          <t>Selection에서 BOM/DWG/PRICING/TECH/ALL 실행</t>
         </is>
       </c>
       <c r="G106" s="8" t="inlineStr">
         <is>
-          <t>Project BOM folder 저장</t>
+          <t>비동기 잡 큐, 부분 실행 지원</t>
         </is>
       </c>
       <c r="H106" s="6" t="inlineStr">
         <is>
-          <t>시스템</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="I106" s="8" t="inlineStr">
         <is>
-          <t>ENG-02, SVC-03</t>
+          <t>SVC-07, ENG-02</t>
         </is>
       </c>
       <c r="J106" s="8" t="inlineStr">
         <is>
-          <t>cpq_selection_item, cpq_output</t>
+          <t>cpq_run</t>
         </is>
       </c>
       <c r="K106" s="6" t="inlineStr">
@@ -7302,7 +7306,7 @@
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>RUN-003</t>
+          <t>RUN-002</t>
         </is>
       </c>
       <c r="C107" s="15" t="inlineStr">
@@ -7317,17 +7321,17 @@
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>치수 Macro 일괄 실행</t>
+          <t>BOM·Part List 생성</t>
         </is>
       </c>
       <c r="F107" s="8" t="inlineStr">
         <is>
-          <t>Sub-code 조건별 Macro 계산 → 계산값 Table 생성·저장</t>
+          <t>Main Code 시작 Code Relationship 전개 → BOM 저장</t>
         </is>
       </c>
       <c r="G107" s="8" t="inlineStr">
         <is>
-          <t>우선순위 위상 정렬, 실패 목록 기록</t>
+          <t>Project BOM folder 저장</t>
         </is>
       </c>
       <c r="H107" s="6" t="inlineStr">
@@ -7337,12 +7341,12 @@
       </c>
       <c r="I107" s="8" t="inlineStr">
         <is>
-          <t>ENG-02, ENG-01</t>
+          <t>ENG-02, SVC-03</t>
         </is>
       </c>
       <c r="J107" s="8" t="inlineStr">
         <is>
-          <t>cpq_run.dimension_values</t>
+          <t>cpq_selection_item, cpq_output</t>
         </is>
       </c>
       <c r="K107" s="6" t="inlineStr">
@@ -7355,11 +7359,7 @@
           <t>미정</t>
         </is>
       </c>
-      <c r="M107" s="8" t="inlineStr">
-        <is>
-          <t>노트 Runtime</t>
-        </is>
-      </c>
+      <c r="M107" s="8" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="6" t="n">
@@ -7367,7 +7367,7 @@
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>RUN-004</t>
+          <t>RUN-003</t>
         </is>
       </c>
       <c r="C108" s="15" t="inlineStr">
@@ -7382,17 +7382,17 @@
       </c>
       <c r="E108" s="8" t="inlineStr">
         <is>
-          <t>승인도면 생성</t>
+          <t>치수 Macro 일괄 실행</t>
         </is>
       </c>
       <c r="F108" s="8" t="inlineStr">
         <is>
-          <t>CPQ Main Concept Drawing → 승인도면(CAD, 필요시 PDF)</t>
+          <t>Sub-code 조건별 Macro 계산 → 계산값 Table 생성·저장</t>
         </is>
       </c>
       <c r="G108" s="8" t="inlineStr">
         <is>
-          <t>Project DWG folder 저장</t>
+          <t>우선순위 위상 정렬, 실패 목록 기록</t>
         </is>
       </c>
       <c r="H108" s="6" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="I108" s="8" t="inlineStr">
         <is>
-          <t>ENG-03</t>
+          <t>ENG-02, ENG-01</t>
         </is>
       </c>
       <c r="J108" s="8" t="inlineStr">
         <is>
-          <t>cpq_output, dwg_file</t>
+          <t>cpq_run.dimension_values</t>
         </is>
       </c>
       <c r="K108" s="6" t="inlineStr">
@@ -7420,7 +7420,11 @@
           <t>미정</t>
         </is>
       </c>
-      <c r="M108" s="8" t="inlineStr"/>
+      <c r="M108" s="8" t="inlineStr">
+        <is>
+          <t>노트 Runtime</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="6" t="n">
@@ -7428,7 +7432,7 @@
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>RUN-005</t>
+          <t>RUN-004</t>
         </is>
       </c>
       <c r="C109" s="15" t="inlineStr">
@@ -7443,17 +7447,17 @@
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>제작도면 생성</t>
+          <t>승인도면 생성</t>
         </is>
       </c>
       <c r="F109" s="8" t="inlineStr">
         <is>
-          <t>각 Code 연결 도면의 Macro Run → 치수 반영 도면 추출</t>
+          <t>CPQ Main Concept Drawing → 승인도면(CAD, 필요시 PDF)</t>
         </is>
       </c>
       <c r="G109" s="8" t="inlineStr">
         <is>
-          <t>BOM 관련 내용만 Run 가능</t>
+          <t>Project DWG folder 저장</t>
         </is>
       </c>
       <c r="H109" s="6" t="inlineStr">
@@ -7468,7 +7472,7 @@
       </c>
       <c r="J109" s="8" t="inlineStr">
         <is>
-          <t>cpq_output</t>
+          <t>cpq_output, dwg_file</t>
         </is>
       </c>
       <c r="K109" s="6" t="inlineStr">
@@ -7489,7 +7493,7 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>RUN-006</t>
+          <t>RUN-005</t>
         </is>
       </c>
       <c r="C110" s="15" t="inlineStr">
@@ -7504,15 +7508,19 @@
       </c>
       <c r="E110" s="8" t="inlineStr">
         <is>
-          <t>기술자료 계산·생성</t>
+          <t>제작도면 생성</t>
         </is>
       </c>
       <c r="F110" s="8" t="inlineStr">
         <is>
-          <t>Technical Data Calculation → Project Data folder 저장</t>
-        </is>
-      </c>
-      <c r="G110" s="8" t="inlineStr"/>
+          <t>각 Code 연결 도면의 Macro Run → 치수 반영 도면 추출</t>
+        </is>
+      </c>
+      <c r="G110" s="8" t="inlineStr">
+        <is>
+          <t>BOM 관련 내용만 Run 가능</t>
+        </is>
+      </c>
       <c r="H110" s="6" t="inlineStr">
         <is>
           <t>시스템</t>
@@ -7520,7 +7528,7 @@
       </c>
       <c r="I110" s="8" t="inlineStr">
         <is>
-          <t>ENG-02, ENG-01</t>
+          <t>ENG-03</t>
         </is>
       </c>
       <c r="J110" s="8" t="inlineStr">
@@ -7530,7 +7538,7 @@
       </c>
       <c r="K110" s="6" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="L110" s="6" t="inlineStr">
@@ -7546,7 +7554,7 @@
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>RUN-007</t>
+          <t>RUN-006</t>
         </is>
       </c>
       <c r="C111" s="15" t="inlineStr">
@@ -7561,12 +7569,12 @@
       </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>일반 서류 생성</t>
+          <t>기술자료 계산·생성</t>
         </is>
       </c>
       <c r="F111" s="8" t="inlineStr">
         <is>
-          <t>General Document — 각 Code 연결 서류 계산·생성</t>
+          <t>Technical Data Calculation → Project Data folder 저장</t>
         </is>
       </c>
       <c r="G111" s="8" t="inlineStr"/>
@@ -7577,7 +7585,7 @@
       </c>
       <c r="I111" s="8" t="inlineStr">
         <is>
-          <t>ENG-02, SVC-11</t>
+          <t>ENG-02, ENG-01</t>
         </is>
       </c>
       <c r="J111" s="8" t="inlineStr">
@@ -7603,7 +7611,7 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>RUN-008</t>
+          <t>RUN-007</t>
         </is>
       </c>
       <c r="C112" s="15" t="inlineStr">
@@ -7618,37 +7626,33 @@
       </c>
       <c r="E112" s="8" t="inlineStr">
         <is>
-          <t>Run 상태·오류 조회</t>
+          <t>일반 서류 생성</t>
         </is>
       </c>
       <c r="F112" s="8" t="inlineStr">
         <is>
-          <t>진행률·단계별 상태·Macro 오류/검증 경고 목록</t>
-        </is>
-      </c>
-      <c r="G112" s="8" t="inlineStr">
-        <is>
-          <t>재시도 지원</t>
-        </is>
-      </c>
+          <t>General Document — 각 Code 연결 서류 계산·생성</t>
+        </is>
+      </c>
+      <c r="G112" s="8" t="inlineStr"/>
       <c r="H112" s="6" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>시스템</t>
         </is>
       </c>
       <c r="I112" s="8" t="inlineStr">
         <is>
-          <t>SVC-07</t>
+          <t>ENG-02, SVC-11</t>
         </is>
       </c>
       <c r="J112" s="8" t="inlineStr">
         <is>
-          <t>cpq_run</t>
+          <t>cpq_output</t>
         </is>
       </c>
       <c r="K112" s="6" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="L112" s="6" t="inlineStr">
@@ -7664,7 +7668,7 @@
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>RUN-009</t>
+          <t>RUN-008</t>
         </is>
       </c>
       <c r="C113" s="15" t="inlineStr">
@@ -7679,15 +7683,19 @@
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>산출물 조회</t>
+          <t>Run 상태·오류 조회</t>
         </is>
       </c>
       <c r="F113" s="8" t="inlineStr">
         <is>
-          <t>Project Folder(DWG/Price/Data/BOM)별 산출물 목록·다운로드</t>
-        </is>
-      </c>
-      <c r="G113" s="8" t="inlineStr"/>
+          <t>진행률·단계별 상태·Macro 오류/검증 경고 목록</t>
+        </is>
+      </c>
+      <c r="G113" s="8" t="inlineStr">
+        <is>
+          <t>재시도 지원</t>
+        </is>
+      </c>
       <c r="H113" s="6" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -7695,12 +7703,12 @@
       </c>
       <c r="I113" s="8" t="inlineStr">
         <is>
-          <t>SVC-12</t>
+          <t>SVC-07</t>
         </is>
       </c>
       <c r="J113" s="8" t="inlineStr">
         <is>
-          <t>cpq_output, dwg_file</t>
+          <t>cpq_run</t>
         </is>
       </c>
       <c r="K113" s="6" t="inlineStr">
@@ -7721,7 +7729,7 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>RUN-010</t>
+          <t>RUN-009</t>
         </is>
       </c>
       <c r="C114" s="15" t="inlineStr">
@@ -7731,24 +7739,20 @@
       </c>
       <c r="D114" s="6" t="inlineStr">
         <is>
-          <t>E-4</t>
+          <t>D-2</t>
         </is>
       </c>
       <c r="E114" s="8" t="inlineStr">
         <is>
-          <t>BOM Export·부분 Run</t>
+          <t>산출물 조회</t>
         </is>
       </c>
       <c r="F114" s="8" t="inlineStr">
         <is>
-          <t>BOM 화면의 EBOM Run(BOM만)/EDIM Run(전체)/Export(Excel) 구분 실행</t>
-        </is>
-      </c>
-      <c r="G114" s="8" t="inlineStr">
-        <is>
-          <t>BOM 관련 내용만 Run하는 부분 실행</t>
-        </is>
-      </c>
+          <t>Project Folder(DWG/Price/Data/BOM)별 산출물 목록·다운로드</t>
+        </is>
+      </c>
+      <c r="G114" s="8" t="inlineStr"/>
       <c r="H114" s="6" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -7756,12 +7760,12 @@
       </c>
       <c r="I114" s="8" t="inlineStr">
         <is>
-          <t>ENG-02, INT-03</t>
+          <t>SVC-12</t>
         </is>
       </c>
       <c r="J114" s="8" t="inlineStr">
         <is>
-          <t>cpq_run</t>
+          <t>cpq_output, dwg_file</t>
         </is>
       </c>
       <c r="K114" s="6" t="inlineStr">
@@ -7774,11 +7778,7 @@
           <t>미정</t>
         </is>
       </c>
-      <c r="M114" s="8" t="inlineStr">
-        <is>
-          <t>슬라이드 70</t>
-        </is>
-      </c>
+      <c r="M114" s="8" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="6" t="n">
@@ -7786,52 +7786,52 @@
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>CST-001</t>
-        </is>
-      </c>
-      <c r="C115" s="16" t="inlineStr">
-        <is>
-          <t>CST 원가·견적</t>
+          <t>RUN-010</t>
+        </is>
+      </c>
+      <c r="C115" s="15" t="inlineStr">
+        <is>
+          <t>RUN EDIM Run</t>
         </is>
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>E-4</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>단가 관리</t>
+          <t>BOM Export·부분 Run</t>
         </is>
       </c>
       <c r="F115" s="8" t="inlineStr">
         <is>
-          <t>견적/구매이력/재고단가/견적적용 4종 단가 Table</t>
+          <t>BOM 화면의 EBOM Run(BOM만)/EDIM Run(전체)/Export(Excel) 구분 실행</t>
         </is>
       </c>
       <c r="G115" s="8" t="inlineStr">
         <is>
-          <t>Code·부품 기준, 적용기간 관리</t>
+          <t>BOM 관련 내용만 Run하는 부분 실행</t>
         </is>
       </c>
       <c r="H115" s="6" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="I115" s="8" t="inlineStr">
         <is>
-          <t>SVC-08</t>
+          <t>ENG-02, INT-03</t>
         </is>
       </c>
       <c r="J115" s="8" t="inlineStr">
         <is>
-          <t>cst_price</t>
+          <t>cpq_run</t>
         </is>
       </c>
       <c r="K115" s="6" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="L115" s="6" t="inlineStr">
@@ -7839,7 +7839,11 @@
           <t>미정</t>
         </is>
       </c>
-      <c r="M115" s="8" t="inlineStr"/>
+      <c r="M115" s="8" t="inlineStr">
+        <is>
+          <t>슬라이드 70</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="6" t="n">
@@ -7847,7 +7851,7 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>CST-002</t>
+          <t>CST-001</t>
         </is>
       </c>
       <c r="C116" s="16" t="inlineStr">
@@ -7857,37 +7861,37 @@
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
       <c r="E116" s="8" t="inlineStr">
         <is>
-          <t>자재비 계산</t>
+          <t>단가 관리</t>
         </is>
       </c>
       <c r="F116" s="8" t="inlineStr">
         <is>
-          <t>원자재 정보(면적·무게·부피)×단가 → Material Cost</t>
+          <t>견적/구매이력/재고단가/견적적용 4종 단가 Table</t>
         </is>
       </c>
       <c r="G116" s="8" t="inlineStr">
         <is>
-          <t>밀도(mat_material) 활용</t>
+          <t>Code·부품 기준, 적용기간 관리</t>
         </is>
       </c>
       <c r="H116" s="6" t="inlineStr">
         <is>
-          <t>시스템</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="I116" s="8" t="inlineStr">
         <is>
-          <t>SVC-08, ENG-02</t>
+          <t>SVC-08</t>
         </is>
       </c>
       <c r="J116" s="8" t="inlineStr">
         <is>
-          <t>cst_calc</t>
+          <t>cst_price</t>
         </is>
       </c>
       <c r="K116" s="6" t="inlineStr">
@@ -7908,7 +7912,7 @@
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>CST-003</t>
+          <t>CST-002</t>
         </is>
       </c>
       <c r="C117" s="16" t="inlineStr">
@@ -7923,15 +7927,19 @@
       </c>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>제조비 계산</t>
+          <t>자재비 계산</t>
         </is>
       </c>
       <c r="F117" s="8" t="inlineStr">
         <is>
-          <t>Work Process 제조 정보(시간·임율·장비) → Manufacturing Cost</t>
-        </is>
-      </c>
-      <c r="G117" s="8" t="inlineStr"/>
+          <t>원자재 정보(면적·무게·부피)×단가 → Material Cost</t>
+        </is>
+      </c>
+      <c r="G117" s="8" t="inlineStr">
+        <is>
+          <t>밀도(mat_material) 활용</t>
+        </is>
+      </c>
       <c r="H117" s="6" t="inlineStr">
         <is>
           <t>시스템</t>
@@ -7939,12 +7947,12 @@
       </c>
       <c r="I117" s="8" t="inlineStr">
         <is>
-          <t>SVC-08</t>
+          <t>SVC-08, ENG-02</t>
         </is>
       </c>
       <c r="J117" s="8" t="inlineStr">
         <is>
-          <t>cst_calc, erp_work_process</t>
+          <t>cst_calc</t>
         </is>
       </c>
       <c r="K117" s="6" t="inlineStr">
@@ -7965,7 +7973,7 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>CST-004</t>
+          <t>CST-003</t>
         </is>
       </c>
       <c r="C118" s="16" t="inlineStr">
@@ -7975,24 +7983,20 @@
       </c>
       <c r="D118" s="6" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-4</t>
         </is>
       </c>
       <c r="E118" s="8" t="inlineStr">
         <is>
-          <t>직접비 집계</t>
+          <t>제조비 계산</t>
         </is>
       </c>
       <c r="F118" s="8" t="inlineStr">
         <is>
-          <t>자재비+제조비+기타 직접비 → Direct Cost</t>
-        </is>
-      </c>
-      <c r="G118" s="8" t="inlineStr">
-        <is>
-          <t>Project Price folder 저장</t>
-        </is>
-      </c>
+          <t>Work Process 제조 정보(시간·임율·장비) → Manufacturing Cost</t>
+        </is>
+      </c>
+      <c r="G118" s="8" t="inlineStr"/>
       <c r="H118" s="6" t="inlineStr">
         <is>
           <t>시스템</t>
@@ -8005,7 +8009,7 @@
       </c>
       <c r="J118" s="8" t="inlineStr">
         <is>
-          <t>cst_calc</t>
+          <t>cst_calc, erp_work_process</t>
         </is>
       </c>
       <c r="K118" s="6" t="inlineStr">
@@ -8026,7 +8030,7 @@
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>CST-005</t>
+          <t>CST-004</t>
         </is>
       </c>
       <c r="C119" s="16" t="inlineStr">
@@ -8041,32 +8045,32 @@
       </c>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t>PCR 작성</t>
+          <t>직접비 집계</t>
         </is>
       </c>
       <c r="F119" s="8" t="inlineStr">
         <is>
-          <t>Business Type별 원가 전개(조달·외주·판관비)→ EBIT</t>
+          <t>자재비+제조비+기타 직접비 → Direct Cost</t>
         </is>
       </c>
       <c r="G119" s="8" t="inlineStr">
         <is>
-          <t>Table/Direct 구분 산식</t>
+          <t>Project Price folder 저장</t>
         </is>
       </c>
       <c r="H119" s="6" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>시스템</t>
         </is>
       </c>
       <c r="I119" s="8" t="inlineStr">
         <is>
-          <t>SVC-08, FE-01</t>
+          <t>SVC-08</t>
         </is>
       </c>
       <c r="J119" s="8" t="inlineStr">
         <is>
-          <t>cst_pcr</t>
+          <t>cst_calc</t>
         </is>
       </c>
       <c r="K119" s="6" t="inlineStr">
@@ -8087,7 +8091,7 @@
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>CST-006</t>
+          <t>CST-005</t>
         </is>
       </c>
       <c r="C120" s="16" t="inlineStr">
@@ -8102,17 +8106,17 @@
       </c>
       <c r="E120" s="8" t="inlineStr">
         <is>
-          <t>견적서 생성·출력</t>
+          <t>PCR 작성</t>
         </is>
       </c>
       <c r="F120" s="8" t="inlineStr">
         <is>
-          <t>PCR 기반 견적서(수량·단가·조건) 생성, PDF 출력</t>
+          <t>Business Type별 원가 전개(조달·외주·판관비)→ EBIT</t>
         </is>
       </c>
       <c r="G120" s="8" t="inlineStr">
         <is>
-          <t>VAT·유효기간·납품/지급조건</t>
+          <t>Table/Direct 구분 산식</t>
         </is>
       </c>
       <c r="H120" s="6" t="inlineStr">
@@ -8122,12 +8126,12 @@
       </c>
       <c r="I120" s="8" t="inlineStr">
         <is>
-          <t>SVC-08, SVC-11</t>
+          <t>SVC-08, FE-01</t>
         </is>
       </c>
       <c r="J120" s="8" t="inlineStr">
         <is>
-          <t>cst_quotation</t>
+          <t>cst_pcr</t>
         </is>
       </c>
       <c r="K120" s="6" t="inlineStr">
@@ -8148,7 +8152,7 @@
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>CST-007</t>
+          <t>CST-006</t>
         </is>
       </c>
       <c r="C121" s="16" t="inlineStr">
@@ -8158,20 +8162,24 @@
       </c>
       <c r="D121" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>D-3</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t>견적 이력 관리</t>
+          <t>견적서 생성·출력</t>
         </is>
       </c>
       <c r="F121" s="8" t="inlineStr">
         <is>
-          <t>견적 상태(DRAFT/SENT/ORDERED) 및 이력</t>
-        </is>
-      </c>
-      <c r="G121" s="8" t="inlineStr"/>
+          <t>PCR 기반 견적서(수량·단가·조건) 생성, PDF 출력</t>
+        </is>
+      </c>
+      <c r="G121" s="8" t="inlineStr">
+        <is>
+          <t>VAT·유효기간·납품/지급조건</t>
+        </is>
+      </c>
       <c r="H121" s="6" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -8179,7 +8187,7 @@
       </c>
       <c r="I121" s="8" t="inlineStr">
         <is>
-          <t>SVC-08</t>
+          <t>SVC-08, SVC-11</t>
         </is>
       </c>
       <c r="J121" s="8" t="inlineStr">
@@ -8205,34 +8213,30 @@
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>ERP-001</t>
-        </is>
-      </c>
-      <c r="C122" s="17" t="inlineStr">
-        <is>
-          <t>ERP ERP 업무</t>
+          <t>CST-007</t>
+        </is>
+      </c>
+      <c r="C122" s="16" t="inlineStr">
+        <is>
+          <t>CST 원가·견적</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
         <is>
-          <t>S-3-5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E122" s="8" t="inlineStr">
         <is>
-          <t>프로젝트 등록</t>
+          <t>견적 이력 관리</t>
         </is>
       </c>
       <c r="F122" s="8" t="inlineStr">
         <is>
-          <t>Project No 자동, 영업단계(기술제안~종료), Client·담당자·Pain Point·접수자료</t>
-        </is>
-      </c>
-      <c r="G122" s="8" t="inlineStr">
-        <is>
-          <t>PS 프로세스 시작점</t>
-        </is>
-      </c>
+          <t>견적 상태(DRAFT/SENT/ORDERED) 및 이력</t>
+        </is>
+      </c>
+      <c r="G122" s="8" t="inlineStr"/>
       <c r="H122" s="6" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -8240,17 +8244,17 @@
       </c>
       <c r="I122" s="8" t="inlineStr">
         <is>
-          <t>SVC-09, FE-01</t>
+          <t>SVC-08</t>
         </is>
       </c>
       <c r="J122" s="8" t="inlineStr">
         <is>
-          <t>prj_project</t>
+          <t>cst_quotation</t>
         </is>
       </c>
       <c r="K122" s="6" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="L122" s="6" t="inlineStr">
@@ -8266,7 +8270,7 @@
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>ERP-002</t>
+          <t>ERP-001</t>
         </is>
       </c>
       <c r="C123" s="17" t="inlineStr">
@@ -8276,22 +8280,22 @@
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
-          <t>§11</t>
+          <t>S-3-5</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>프로세스 이벤트 관리</t>
+          <t>프로젝트 등록</t>
         </is>
       </c>
       <c r="F123" s="8" t="inlineStr">
         <is>
-          <t>프로세스 코드별 이벤트 생성·상태 전이(TODO→진행→완료)</t>
+          <t>Project No 자동, 영업단계(기술제안~종료), Client·담당자·Pain Point·접수자료</t>
         </is>
       </c>
       <c r="G123" s="8" t="inlineStr">
         <is>
-          <t>선행 완료 조건 검사</t>
+          <t>PS 프로세스 시작점</t>
         </is>
       </c>
       <c r="H123" s="6" t="inlineStr">
@@ -8301,17 +8305,17 @@
       </c>
       <c r="I123" s="8" t="inlineStr">
         <is>
-          <t>SVC-09</t>
+          <t>SVC-09, FE-01</t>
         </is>
       </c>
       <c r="J123" s="8" t="inlineStr">
         <is>
-          <t>erp_process_event</t>
+          <t>prj_project</t>
         </is>
       </c>
       <c r="K123" s="6" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="L123" s="6" t="inlineStr">
@@ -8327,7 +8331,7 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>ERP-003</t>
+          <t>ERP-002</t>
         </is>
       </c>
       <c r="C124" s="17" t="inlineStr">
@@ -8342,17 +8346,17 @@
       </c>
       <c r="E124" s="8" t="inlineStr">
         <is>
-          <t>부서별 업무함</t>
+          <t>프로세스 이벤트 관리</t>
         </is>
       </c>
       <c r="F124" s="8" t="inlineStr">
         <is>
-          <t>부서·담당자별 To-do/진행/완료 목록</t>
+          <t>프로세스 코드별 이벤트 생성·상태 전이(TODO→진행→완료)</t>
         </is>
       </c>
       <c r="G124" s="8" t="inlineStr">
         <is>
-          <t>이상 경고(기한 초과) 표시</t>
+          <t>선행 완료 조건 검사</t>
         </is>
       </c>
       <c r="H124" s="6" t="inlineStr">
@@ -8362,7 +8366,7 @@
       </c>
       <c r="I124" s="8" t="inlineStr">
         <is>
-          <t>SVC-09, FE-01</t>
+          <t>SVC-09</t>
         </is>
       </c>
       <c r="J124" s="8" t="inlineStr">
@@ -8388,7 +8392,7 @@
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>ERP-004</t>
+          <t>ERP-003</t>
         </is>
       </c>
       <c r="C125" s="17" t="inlineStr">
@@ -8403,27 +8407,27 @@
       </c>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t>영업 프로세스</t>
+          <t>부서별 업무함</t>
         </is>
       </c>
       <c r="F125" s="8" t="inlineStr">
         <is>
-          <t>견적검토(PCR)→견적(QCR)→수주(OR) 흐름 처리</t>
+          <t>부서·담당자별 To-do/진행/완료 목록</t>
         </is>
       </c>
       <c r="G125" s="8" t="inlineStr">
         <is>
-          <t>CPQ·견적 연동</t>
+          <t>이상 경고(기한 초과) 표시</t>
         </is>
       </c>
       <c r="H125" s="6" t="inlineStr">
         <is>
-          <t>영업</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="I125" s="8" t="inlineStr">
         <is>
-          <t>SVC-09</t>
+          <t>SVC-09, FE-01</t>
         </is>
       </c>
       <c r="J125" s="8" t="inlineStr">
@@ -8449,7 +8453,7 @@
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>ERP-005</t>
+          <t>ERP-004</t>
         </is>
       </c>
       <c r="C126" s="17" t="inlineStr">
@@ -8464,22 +8468,22 @@
       </c>
       <c r="E126" s="8" t="inlineStr">
         <is>
-          <t>승인도서·고객승인</t>
+          <t>영업 프로세스</t>
         </is>
       </c>
       <c r="F126" s="8" t="inlineStr">
         <is>
-          <t>AP 생성→APP 고객 승인 처리</t>
+          <t>견적검토(PCR)→견적(QCR)→수주(OR) 흐름 처리</t>
         </is>
       </c>
       <c r="G126" s="8" t="inlineStr">
         <is>
-          <t>산출물(승인도면) 연결</t>
+          <t>CPQ·견적 연동</t>
         </is>
       </c>
       <c r="H126" s="6" t="inlineStr">
         <is>
-          <t>영업/기술</t>
+          <t>영업</t>
         </is>
       </c>
       <c r="I126" s="8" t="inlineStr">
@@ -8510,7 +8514,7 @@
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>ERP-006</t>
+          <t>ERP-005</t>
         </is>
       </c>
       <c r="C127" s="17" t="inlineStr">
@@ -8525,22 +8529,22 @@
       </c>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t>제작 프로세스</t>
+          <t>승인도서·고객승인</t>
         </is>
       </c>
       <c r="F127" s="8" t="inlineStr">
         <is>
-          <t>제작의뢰(MR)→제작점검(MRR)→Part List(PL)→BOM</t>
+          <t>AP 생성→APP 고객 승인 처리</t>
         </is>
       </c>
       <c r="G127" s="8" t="inlineStr">
         <is>
-          <t>EDIM Run 산출물 연동</t>
+          <t>산출물(승인도면) 연결</t>
         </is>
       </c>
       <c r="H127" s="6" t="inlineStr">
         <is>
-          <t>기술</t>
+          <t>영업/기술</t>
         </is>
       </c>
       <c r="I127" s="8" t="inlineStr">
@@ -8571,7 +8575,7 @@
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>ERP-007</t>
+          <t>ERP-006</t>
         </is>
       </c>
       <c r="C128" s="17" t="inlineStr">
@@ -8586,22 +8590,22 @@
       </c>
       <c r="E128" s="8" t="inlineStr">
         <is>
-          <t>자재 프로세스</t>
+          <t>제작 프로세스</t>
         </is>
       </c>
       <c r="F128" s="8" t="inlineStr">
         <is>
-          <t>발주요청(PR)→발주(PO)→입고(MI)→출고(MO)→수령(RM)→검사(ER)</t>
+          <t>제작의뢰(MR)→제작점검(MRR)→Part List(PL)→BOM</t>
         </is>
       </c>
       <c r="G128" s="8" t="inlineStr">
         <is>
-          <t>재고·창고 관리 연계</t>
+          <t>EDIM Run 산출물 연동</t>
         </is>
       </c>
       <c r="H128" s="6" t="inlineStr">
         <is>
-          <t>자재</t>
+          <t>기술</t>
         </is>
       </c>
       <c r="I128" s="8" t="inlineStr">
@@ -8624,11 +8628,7 @@
           <t>미정</t>
         </is>
       </c>
-      <c r="M128" s="8" t="inlineStr">
-        <is>
-          <t>상세 v0.2</t>
-        </is>
-      </c>
+      <c r="M128" s="8" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="6" t="n">
@@ -8636,7 +8636,7 @@
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>ERP-008</t>
+          <t>ERP-007</t>
         </is>
       </c>
       <c r="C129" s="17" t="inlineStr">
@@ -8651,22 +8651,22 @@
       </c>
       <c r="E129" s="8" t="inlineStr">
         <is>
-          <t>생산 프로세스</t>
+          <t>자재 프로세스</t>
         </is>
       </c>
       <c r="F129" s="8" t="inlineStr">
         <is>
-          <t>생산계획(MP)→작업지시(WR)→입고(SFI)→검사(EF)→완료(FF), Stock 생산(SPP)</t>
+          <t>발주요청(PR)→발주(PO)→입고(MI)→출고(MO)→수령(RM)→검사(ER)</t>
         </is>
       </c>
       <c r="G129" s="8" t="inlineStr">
         <is>
-          <t>부적합(NCF) 분기</t>
+          <t>재고·창고 관리 연계</t>
         </is>
       </c>
       <c r="H129" s="6" t="inlineStr">
         <is>
-          <t>생산</t>
+          <t>자재</t>
         </is>
       </c>
       <c r="I129" s="8" t="inlineStr">
@@ -8689,7 +8689,11 @@
           <t>미정</t>
         </is>
       </c>
-      <c r="M129" s="8" t="inlineStr"/>
+      <c r="M129" s="8" t="inlineStr">
+        <is>
+          <t>상세 v0.2</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="6" t="n">
@@ -8697,7 +8701,7 @@
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>ERP-009</t>
+          <t>ERP-008</t>
         </is>
       </c>
       <c r="C130" s="17" t="inlineStr">
@@ -8712,18 +8716,22 @@
       </c>
       <c r="E130" s="8" t="inlineStr">
         <is>
-          <t>출고·납품 프로세스</t>
+          <t>생산 프로세스</t>
         </is>
       </c>
       <c r="F130" s="8" t="inlineStr">
         <is>
-          <t>출고요청(FDR)→고객출고(SFO)→납품(DF)→기성청구(IR)</t>
-        </is>
-      </c>
-      <c r="G130" s="8" t="inlineStr"/>
+          <t>생산계획(MP)→작업지시(WR)→입고(SFI)→검사(EF)→완료(FF), Stock 생산(SPP)</t>
+        </is>
+      </c>
+      <c r="G130" s="8" t="inlineStr">
+        <is>
+          <t>부적합(NCF) 분기</t>
+        </is>
+      </c>
       <c r="H130" s="6" t="inlineStr">
         <is>
-          <t>영업/자재</t>
+          <t>생산</t>
         </is>
       </c>
       <c r="I130" s="8" t="inlineStr">
@@ -8754,7 +8762,7 @@
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>ERP-010</t>
+          <t>ERP-009</t>
         </is>
       </c>
       <c r="C131" s="17" t="inlineStr">
@@ -8769,18 +8777,18 @@
       </c>
       <c r="E131" s="8" t="inlineStr">
         <is>
-          <t>시운전·CS</t>
+          <t>출고·납품 프로세스</t>
         </is>
       </c>
       <c r="F131" s="8" t="inlineStr">
         <is>
-          <t>시운전 요청(CR)→시운전(CF), 인증서 발급</t>
+          <t>출고요청(FDR)→고객출고(SFO)→납품(DF)→기성청구(IR)</t>
         </is>
       </c>
       <c r="G131" s="8" t="inlineStr"/>
       <c r="H131" s="6" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>영업/자재</t>
         </is>
       </c>
       <c r="I131" s="8" t="inlineStr">
@@ -8811,7 +8819,7 @@
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>ERP-011</t>
+          <t>ERP-010</t>
         </is>
       </c>
       <c r="C132" s="17" t="inlineStr">
@@ -8826,18 +8834,18 @@
       </c>
       <c r="E132" s="8" t="inlineStr">
         <is>
-          <t>재무 프로세스</t>
+          <t>시운전·CS</t>
         </is>
       </c>
       <c r="F132" s="8" t="inlineStr">
         <is>
-          <t>세금계산 매입/매출(II/IO), 출금/입금(PA/PI), 정산(RR/RA), 재무관리(FM)</t>
+          <t>시운전 요청(CR)→시운전(CF), 인증서 발급</t>
         </is>
       </c>
       <c r="G132" s="8" t="inlineStr"/>
       <c r="H132" s="6" t="inlineStr">
         <is>
-          <t>재무</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="I132" s="8" t="inlineStr">
@@ -8868,7 +8876,7 @@
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>ERP-012</t>
+          <t>ERP-011</t>
         </is>
       </c>
       <c r="C133" s="17" t="inlineStr">
@@ -8883,18 +8891,18 @@
       </c>
       <c r="E133" s="8" t="inlineStr">
         <is>
-          <t>부적합 처리</t>
+          <t>재무 프로세스</t>
         </is>
       </c>
       <c r="F133" s="8" t="inlineStr">
         <is>
-          <t>NCF 요청·처리, 재작업 요청(WR)</t>
+          <t>세금계산 매입/매출(II/IO), 출금/입금(PA/PI), 정산(RR/RA), 재무관리(FM)</t>
         </is>
       </c>
       <c r="G133" s="8" t="inlineStr"/>
       <c r="H133" s="6" t="inlineStr">
         <is>
-          <t>QC</t>
+          <t>재무</t>
         </is>
       </c>
       <c r="I133" s="8" t="inlineStr">
@@ -8925,7 +8933,7 @@
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>ERP-013</t>
+          <t>ERP-012</t>
         </is>
       </c>
       <c r="C134" s="17" t="inlineStr">
@@ -8940,18 +8948,18 @@
       </c>
       <c r="E134" s="8" t="inlineStr">
         <is>
-          <t>평가</t>
+          <t>부적합 처리</t>
         </is>
       </c>
       <c r="F134" s="8" t="inlineStr">
         <is>
-          <t>업체 평가(CE), Project 평가(PE)</t>
+          <t>NCF 요청·처리, 재작업 요청(WR)</t>
         </is>
       </c>
       <c r="G134" s="8" t="inlineStr"/>
       <c r="H134" s="6" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>QC</t>
         </is>
       </c>
       <c r="I134" s="8" t="inlineStr">
@@ -8961,7 +8969,7 @@
       </c>
       <c r="J134" s="8" t="inlineStr">
         <is>
-          <t>com_company</t>
+          <t>erp_process_event</t>
         </is>
       </c>
       <c r="K134" s="6" t="inlineStr">
@@ -8982,7 +8990,7 @@
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>ERP-014</t>
+          <t>ERP-013</t>
         </is>
       </c>
       <c r="C135" s="17" t="inlineStr">
@@ -8997,32 +9005,28 @@
       </c>
       <c r="E135" s="8" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>평가</t>
         </is>
       </c>
       <c r="F135" s="8" t="inlineStr">
         <is>
-          <t>전후 공정·Project 일정·Event 상황·이상 경고(시간/자금)·손익·자금 흐름</t>
-        </is>
-      </c>
-      <c r="G135" s="8" t="inlineStr">
-        <is>
-          <t>프로젝트별 집계</t>
-        </is>
-      </c>
+          <t>업체 평가(CE), Project 평가(PE)</t>
+        </is>
+      </c>
+      <c r="G135" s="8" t="inlineStr"/>
       <c r="H135" s="6" t="inlineStr">
         <is>
-          <t>ADMIN/경영</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="I135" s="8" t="inlineStr">
         <is>
-          <t>SVC-09, FE-01</t>
+          <t>SVC-09</t>
         </is>
       </c>
       <c r="J135" s="8" t="inlineStr">
         <is>
-          <t>erp_process_event, cst_*</t>
+          <t>com_company</t>
         </is>
       </c>
       <c r="K135" s="6" t="inlineStr">
@@ -9043,7 +9047,7 @@
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>ERP-015</t>
+          <t>ERP-014</t>
         </is>
       </c>
       <c r="C136" s="17" t="inlineStr">
@@ -9053,38 +9057,42 @@
       </c>
       <c r="D136" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>§11</t>
         </is>
       </c>
       <c r="E136" s="8" t="inlineStr">
         <is>
-          <t>회사 마스터</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="F136" s="8" t="inlineStr">
         <is>
-          <t>고객/공급/파트너/은행 등록, 담당자, 평가등급, 지불조건</t>
-        </is>
-      </c>
-      <c r="G136" s="8" t="inlineStr"/>
+          <t>전후 공정·Project 일정·Event 상황·이상 경고(시간/자금)·손익·자금 흐름</t>
+        </is>
+      </c>
+      <c r="G136" s="8" t="inlineStr">
+        <is>
+          <t>프로젝트별 집계</t>
+        </is>
+      </c>
       <c r="H136" s="6" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>ADMIN/경영</t>
         </is>
       </c>
       <c r="I136" s="8" t="inlineStr">
         <is>
-          <t>SVC-09</t>
+          <t>SVC-09, FE-01</t>
         </is>
       </c>
       <c r="J136" s="8" t="inlineStr">
         <is>
-          <t>com_company</t>
+          <t>erp_process_event, cst_*</t>
         </is>
       </c>
       <c r="K136" s="6" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="L136" s="6" t="inlineStr">
@@ -9100,7 +9108,7 @@
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>ERP-016</t>
+          <t>ERP-015</t>
         </is>
       </c>
       <c r="C137" s="17" t="inlineStr">
@@ -9110,24 +9118,20 @@
       </c>
       <c r="D137" s="6" t="inlineStr">
         <is>
-          <t>S-3-5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
         <is>
-          <t>사용자 정의 ERP Toolbar</t>
+          <t>회사 마스터</t>
         </is>
       </c>
       <c r="F137" s="8" t="inlineStr">
         <is>
-          <t>ERP Toolbar 항목 사용자 편집, 권한별 표시</t>
-        </is>
-      </c>
-      <c r="G137" s="8" t="inlineStr">
-        <is>
-          <t>User Customizing ERP</t>
-        </is>
-      </c>
+          <t>고객/공급/파트너/은행 등록, 담당자, 평가등급, 지불조건</t>
+        </is>
+      </c>
+      <c r="G137" s="8" t="inlineStr"/>
       <c r="H137" s="6" t="inlineStr">
         <is>
           <t>SETUP</t>
@@ -9135,17 +9139,17 @@
       </c>
       <c r="I137" s="8" t="inlineStr">
         <is>
-          <t>SVC-06, FE-01</t>
+          <t>SVC-09</t>
         </is>
       </c>
       <c r="J137" s="8" t="inlineStr">
         <is>
-          <t>tbx_ui_form</t>
+          <t>com_company</t>
         </is>
       </c>
       <c r="K137" s="6" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="L137" s="6" t="inlineStr">
@@ -9161,7 +9165,7 @@
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>ERP-017</t>
+          <t>ERP-016</t>
         </is>
       </c>
       <c r="C138" s="17" t="inlineStr">
@@ -9171,37 +9175,37 @@
       </c>
       <c r="D138" s="6" t="inlineStr">
         <is>
-          <t>§11</t>
+          <t>S-3-5</t>
         </is>
       </c>
       <c r="E138" s="8" t="inlineStr">
         <is>
-          <t>구매 조건 관리</t>
+          <t>사용자 정의 ERP Toolbar</t>
         </is>
       </c>
       <c r="F138" s="8" t="inlineStr">
         <is>
-          <t>공급처(국가/본사)·납기·납품조건(EXW/FOB/CIP, 설치/상차/하차)·운송(트럭/배/항공)·지불조건·화폐·물품형식(물건/서비스/인력/협력사)·최소구매수량·인증서·단위(부피/체적/면적/수량)</t>
+          <t>ERP Toolbar 항목 사용자 편집, 권한별 표시</t>
         </is>
       </c>
       <c r="G138" s="8" t="inlineStr">
         <is>
-          <t>Right quality/quantity/time/price/source 원칙</t>
+          <t>User Customizing ERP</t>
         </is>
       </c>
       <c r="H138" s="6" t="inlineStr">
         <is>
-          <t>자재</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="I138" s="8" t="inlineStr">
         <is>
-          <t>SVC-09</t>
+          <t>SVC-06, FE-01</t>
         </is>
       </c>
       <c r="J138" s="8" t="inlineStr">
         <is>
-          <t>com_company, erp_process_event</t>
+          <t>tbx_ui_form</t>
         </is>
       </c>
       <c r="K138" s="6" t="inlineStr">
@@ -9214,11 +9218,7 @@
           <t>미정</t>
         </is>
       </c>
-      <c r="M138" s="8" t="inlineStr">
-        <is>
-          <t>슬라이드 46</t>
-        </is>
-      </c>
+      <c r="M138" s="8" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="6" t="n">
@@ -9226,7 +9226,7 @@
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>ERP-018</t>
+          <t>ERP-017</t>
         </is>
       </c>
       <c r="C139" s="17" t="inlineStr">
@@ -9241,17 +9241,17 @@
       </c>
       <c r="E139" s="8" t="inlineStr">
         <is>
-          <t>제품코드 매핑</t>
+          <t>구매 조건 관리</t>
         </is>
       </c>
       <c r="F139" s="8" t="inlineStr">
         <is>
-          <t>사용자용 코드 ↔ 공급자용 코드 매핑 관리</t>
+          <t>공급처(국가/본사)·납기·납품조건(EXW/FOB/CIP, 설치/상차/하차)·운송(트럭/배/항공)·지불조건·화폐·물품형식(물건/서비스/인력/협력사)·최소구매수량·인증서·단위(부피/체적/면적/수량)</t>
         </is>
       </c>
       <c r="G139" s="8" t="inlineStr">
         <is>
-          <t>발주서에 공급자 코드 표기</t>
+          <t>Right quality/quantity/time/price/source 원칙</t>
         </is>
       </c>
       <c r="H139" s="6" t="inlineStr">
@@ -9261,12 +9261,12 @@
       </c>
       <c r="I139" s="8" t="inlineStr">
         <is>
-          <t>SVC-09, SVC-03</t>
+          <t>SVC-09</t>
         </is>
       </c>
       <c r="J139" s="8" t="inlineStr">
         <is>
-          <t>prt_supplier_code_map</t>
+          <t>com_company, erp_process_event</t>
         </is>
       </c>
       <c r="K139" s="6" t="inlineStr">
@@ -9291,7 +9291,7 @@
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>ERP-019</t>
+          <t>ERP-018</t>
         </is>
       </c>
       <c r="C140" s="17" t="inlineStr">
@@ -9306,17 +9306,17 @@
       </c>
       <c r="E140" s="8" t="inlineStr">
         <is>
-          <t>재고 관리</t>
+          <t>제품코드 매핑</t>
         </is>
       </c>
       <c r="F140" s="8" t="inlineStr">
         <is>
-          <t>적정 재고량, 유통기한 관리</t>
+          <t>사용자용 코드 ↔ 공급자용 코드 매핑 관리</t>
         </is>
       </c>
       <c r="G140" s="8" t="inlineStr">
         <is>
-          <t>최소 재고(min_stock) 경고</t>
+          <t>발주서에 공급자 코드 표기</t>
         </is>
       </c>
       <c r="H140" s="6" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="I140" s="8" t="inlineStr">
         <is>
-          <t>SVC-09</t>
+          <t>SVC-09, SVC-03</t>
         </is>
       </c>
       <c r="J140" s="8" t="inlineStr">
         <is>
-          <t>erp_work_process</t>
+          <t>prt_supplier_code_map</t>
         </is>
       </c>
       <c r="K140" s="6" t="inlineStr">
@@ -9356,7 +9356,7 @@
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>ERP-020</t>
+          <t>ERP-019</t>
         </is>
       </c>
       <c r="C141" s="17" t="inlineStr">
@@ -9371,17 +9371,17 @@
       </c>
       <c r="E141" s="8" t="inlineStr">
         <is>
-          <t>창고 관리</t>
+          <t>재고 관리</t>
         </is>
       </c>
       <c r="F141" s="8" t="inlineStr">
         <is>
-          <t>자재 분류(원자재/가공/구매), 물성 위험등급(액체-독극물/가스-폭발성/고체-판·파이프·개), 저장위치 계층(지역/공장/창고/Storage/Sector), 보관품질(정기점검·유통기한), 입출고 통제·기록</t>
+          <t>적정 재고량, 유통기한 관리</t>
         </is>
       </c>
       <c r="G141" s="8" t="inlineStr">
         <is>
-          <t>위험물 보관 규정 준수</t>
+          <t>최소 재고(min_stock) 경고</t>
         </is>
       </c>
       <c r="H141" s="6" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="J141" s="8" t="inlineStr">
         <is>
-          <t>erp_warehouse, mat_material</t>
+          <t>erp_work_process</t>
         </is>
       </c>
       <c r="K141" s="6" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>ERP-021</t>
+          <t>ERP-020</t>
         </is>
       </c>
       <c r="C142" s="17" t="inlineStr">
@@ -9436,17 +9436,17 @@
       </c>
       <c r="E142" s="8" t="inlineStr">
         <is>
-          <t>재고 단가 관리</t>
+          <t>창고 관리</t>
         </is>
       </c>
       <c r="F142" s="8" t="inlineStr">
         <is>
-          <t>재고 단가 4종 산출 — 최고/최저/평균/최근</t>
+          <t>자재 분류(원자재/가공/구매), 물성 위험등급(액체-독극물/가스-폭발성/고체-판·파이프·개), 저장위치 계층(지역/공장/창고/Storage/Sector), 보관품질(정기점검·유통기한), 입출고 통제·기록</t>
         </is>
       </c>
       <c r="G142" s="8" t="inlineStr">
         <is>
-          <t>cst_price(STOCK) 원천</t>
+          <t>위험물 보관 규정 준수</t>
         </is>
       </c>
       <c r="H142" s="6" t="inlineStr">
@@ -9456,12 +9456,12 @@
       </c>
       <c r="I142" s="8" t="inlineStr">
         <is>
-          <t>SVC-08</t>
+          <t>SVC-09</t>
         </is>
       </c>
       <c r="J142" s="8" t="inlineStr">
         <is>
-          <t>cst_price</t>
+          <t>erp_warehouse, mat_material</t>
         </is>
       </c>
       <c r="K142" s="6" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>ERP-022</t>
+          <t>ERP-021</t>
         </is>
       </c>
       <c r="C143" s="17" t="inlineStr">
@@ -9501,32 +9501,32 @@
       </c>
       <c r="E143" s="8" t="inlineStr">
         <is>
-          <t>MRP 자재 소요 계획</t>
+          <t>재고 단가 관리</t>
         </is>
       </c>
       <c r="F143" s="8" t="inlineStr">
         <is>
-          <t>제품 단위당 BOM 기반 자재 소요량·소요 시기 산출</t>
+          <t>재고 단가 4종 산출 — 최고/최저/평균/최근</t>
         </is>
       </c>
       <c r="G143" s="8" t="inlineStr">
         <is>
-          <t>생산계획 연동</t>
+          <t>cst_price(STOCK) 원천</t>
         </is>
       </c>
       <c r="H143" s="6" t="inlineStr">
         <is>
-          <t>자재/생산</t>
+          <t>자재</t>
         </is>
       </c>
       <c r="I143" s="8" t="inlineStr">
         <is>
-          <t>SVC-09</t>
+          <t>SVC-08</t>
         </is>
       </c>
       <c r="J143" s="8" t="inlineStr">
         <is>
-          <t>erp_process_event</t>
+          <t>cst_price</t>
         </is>
       </c>
       <c r="K143" s="6" t="inlineStr">
@@ -9551,7 +9551,7 @@
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>ERP-023</t>
+          <t>ERP-022</t>
         </is>
       </c>
       <c r="C144" s="17" t="inlineStr">
@@ -9566,18 +9566,22 @@
       </c>
       <c r="E144" s="8" t="inlineStr">
         <is>
-          <t>생산 Scheduling·Capacity</t>
+          <t>MRP 자재 소요 계획</t>
         </is>
       </c>
       <c r="F144" s="8" t="inlineStr">
         <is>
-          <t>주문량·가용 자원 기반 생산 일정, 생산능력(Capacity Planning) 분석</t>
-        </is>
-      </c>
-      <c r="G144" s="8" t="inlineStr"/>
+          <t>제품 단위당 BOM 기반 자재 소요량·소요 시기 산출</t>
+        </is>
+      </c>
+      <c r="G144" s="8" t="inlineStr">
+        <is>
+          <t>생산계획 연동</t>
+        </is>
+      </c>
       <c r="H144" s="6" t="inlineStr">
         <is>
-          <t>생산</t>
+          <t>자재/생산</t>
         </is>
       </c>
       <c r="I144" s="8" t="inlineStr">
@@ -9612,7 +9616,7 @@
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>ERP-024</t>
+          <t>ERP-023</t>
         </is>
       </c>
       <c r="C145" s="17" t="inlineStr">
@@ -9627,19 +9631,15 @@
       </c>
       <c r="E145" s="8" t="inlineStr">
         <is>
-          <t>작업지시 관리</t>
+          <t>생산 Scheduling·Capacity</t>
         </is>
       </c>
       <c r="F145" s="8" t="inlineStr">
         <is>
-          <t>작업 지시서(양식) 발행, 작업 단계별 진행 상황 기록·모니터링</t>
-        </is>
-      </c>
-      <c r="G145" s="8" t="inlineStr">
-        <is>
-          <t>양식은 Print Form 활용</t>
-        </is>
-      </c>
+          <t>주문량·가용 자원 기반 생산 일정, 생산능력(Capacity Planning) 분석</t>
+        </is>
+      </c>
+      <c r="G145" s="8" t="inlineStr"/>
       <c r="H145" s="6" t="inlineStr">
         <is>
           <t>생산</t>
@@ -9647,7 +9647,7 @@
       </c>
       <c r="I145" s="8" t="inlineStr">
         <is>
-          <t>SVC-09, SVC-11</t>
+          <t>SVC-09</t>
         </is>
       </c>
       <c r="J145" s="8" t="inlineStr">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>ERP-025</t>
+          <t>ERP-024</t>
         </is>
       </c>
       <c r="C146" s="17" t="inlineStr">
@@ -9692,17 +9692,17 @@
       </c>
       <c r="E146" s="8" t="inlineStr">
         <is>
-          <t>공정 관리</t>
+          <t>작업지시 관리</t>
         </is>
       </c>
       <c r="F146" s="8" t="inlineStr">
         <is>
-          <t>공정별 데이터 실시간 수집·분석 — 작업장/기계종류/작업인원/필요스킬등급/작업시간/조립공정/전·후공정 DB</t>
+          <t>작업 지시서(양식) 발행, 작업 단계별 진행 상황 기록·모니터링</t>
         </is>
       </c>
       <c r="G146" s="8" t="inlineStr">
         <is>
-          <t>erp_work_process 확장</t>
+          <t>양식은 Print Form 활용</t>
         </is>
       </c>
       <c r="H146" s="6" t="inlineStr">
@@ -9712,12 +9712,12 @@
       </c>
       <c r="I146" s="8" t="inlineStr">
         <is>
-          <t>SVC-09</t>
+          <t>SVC-09, SVC-11</t>
         </is>
       </c>
       <c r="J146" s="8" t="inlineStr">
         <is>
-          <t>erp_work_process</t>
+          <t>erp_process_event</t>
         </is>
       </c>
       <c r="K146" s="6" t="inlineStr">
@@ -9742,7 +9742,7 @@
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>ERP-026</t>
+          <t>ERP-025</t>
         </is>
       </c>
       <c r="C147" s="17" t="inlineStr">
@@ -9757,22 +9757,22 @@
       </c>
       <c r="E147" s="8" t="inlineStr">
         <is>
-          <t>자재흐름·물류 관리</t>
+          <t>공정 관리</t>
         </is>
       </c>
       <c r="F147" s="8" t="inlineStr">
         <is>
-          <t>물류 창고, 물류 방식 관리</t>
+          <t>공정별 데이터 실시간 수집·분석 — 작업장/기계종류/작업인원/필요스킬등급/작업시간/조립공정/전·후공정 DB</t>
         </is>
       </c>
       <c r="G147" s="8" t="inlineStr">
         <is>
-          <t>외주·물류 관리와 연계</t>
+          <t>erp_work_process 확장</t>
         </is>
       </c>
       <c r="H147" s="6" t="inlineStr">
         <is>
-          <t>자재</t>
+          <t>생산</t>
         </is>
       </c>
       <c r="I147" s="8" t="inlineStr">
@@ -9782,7 +9782,7 @@
       </c>
       <c r="J147" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>erp_work_process</t>
         </is>
       </c>
       <c r="K147" s="6" t="inlineStr">
@@ -9807,7 +9807,7 @@
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>ERP-027</t>
+          <t>ERP-026</t>
         </is>
       </c>
       <c r="C148" s="17" t="inlineStr">
@@ -9822,22 +9822,22 @@
       </c>
       <c r="E148" s="8" t="inlineStr">
         <is>
-          <t>품질 관리</t>
+          <t>자재흐름·물류 관리</t>
         </is>
       </c>
       <c r="F148" s="8" t="inlineStr">
         <is>
-          <t>제품 검수, 하자 관리</t>
+          <t>물류 창고, 물류 방식 관리</t>
         </is>
       </c>
       <c r="G148" s="8" t="inlineStr">
         <is>
-          <t>NCF 부적합 프로세스 연동</t>
+          <t>외주·물류 관리와 연계</t>
         </is>
       </c>
       <c r="H148" s="6" t="inlineStr">
         <is>
-          <t>QC</t>
+          <t>자재</t>
         </is>
       </c>
       <c r="I148" s="8" t="inlineStr">
@@ -9847,7 +9847,7 @@
       </c>
       <c r="J148" s="8" t="inlineStr">
         <is>
-          <t>erp_process_event</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K148" s="6" t="inlineStr">
@@ -9872,7 +9872,7 @@
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>ERP-028</t>
+          <t>ERP-027</t>
         </is>
       </c>
       <c r="C149" s="17" t="inlineStr">
@@ -9887,32 +9887,32 @@
       </c>
       <c r="E149" s="8" t="inlineStr">
         <is>
-          <t>원가 DB 관리</t>
+          <t>품질 관리</t>
         </is>
       </c>
       <c r="F149" s="8" t="inlineStr">
         <is>
-          <t>자재 단가 DB, 인건비 DB, 공정비용 DB 유지</t>
+          <t>제품 검수, 하자 관리</t>
         </is>
       </c>
       <c r="G149" s="8" t="inlineStr">
         <is>
-          <t>제조비 계산(CST-003) 원천</t>
+          <t>NCF 부적합 프로세스 연동</t>
         </is>
       </c>
       <c r="H149" s="6" t="inlineStr">
         <is>
-          <t>재무/생산</t>
+          <t>QC</t>
         </is>
       </c>
       <c r="I149" s="8" t="inlineStr">
         <is>
-          <t>SVC-08</t>
+          <t>SVC-09</t>
         </is>
       </c>
       <c r="J149" s="8" t="inlineStr">
         <is>
-          <t>cst_price</t>
+          <t>erp_process_event</t>
         </is>
       </c>
       <c r="K149" s="6" t="inlineStr">
@@ -9937,7 +9937,7 @@
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>ERP-029</t>
+          <t>ERP-028</t>
         </is>
       </c>
       <c r="C150" s="17" t="inlineStr">
@@ -9952,28 +9952,32 @@
       </c>
       <c r="E150" s="8" t="inlineStr">
         <is>
-          <t>불량·대체자재 관리</t>
+          <t>원가 DB 관리</t>
         </is>
       </c>
       <c r="F150" s="8" t="inlineStr">
         <is>
-          <t>불량품·폐품 처리, 자재 표준화·단순화, 대체 자재 연구·적용</t>
-        </is>
-      </c>
-      <c r="G150" s="8" t="inlineStr"/>
+          <t>자재 단가 DB, 인건비 DB, 공정비용 DB 유지</t>
+        </is>
+      </c>
+      <c r="G150" s="8" t="inlineStr">
+        <is>
+          <t>제조비 계산(CST-003) 원천</t>
+        </is>
+      </c>
       <c r="H150" s="6" t="inlineStr">
         <is>
-          <t>자재</t>
+          <t>재무/생산</t>
         </is>
       </c>
       <c r="I150" s="8" t="inlineStr">
         <is>
-          <t>SVC-09</t>
+          <t>SVC-08</t>
         </is>
       </c>
       <c r="J150" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>cst_price</t>
         </is>
       </c>
       <c r="K150" s="6" t="inlineStr">
@@ -9998,7 +10002,7 @@
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>ERP-030</t>
+          <t>ERP-029</t>
         </is>
       </c>
       <c r="C151" s="17" t="inlineStr">
@@ -10013,32 +10017,28 @@
       </c>
       <c r="E151" s="8" t="inlineStr">
         <is>
-          <t>외주 제조 관리</t>
+          <t>불량·대체자재 관리</t>
         </is>
       </c>
       <c r="F151" s="8" t="inlineStr">
         <is>
-          <t>3rd party 제조업체 — 제조 의뢰, 재작업 요청, 인증서 발급</t>
-        </is>
-      </c>
-      <c r="G151" s="8" t="inlineStr">
-        <is>
-          <t>Partner 실시간 Code 연결</t>
-        </is>
-      </c>
+          <t>불량품·폐품 처리, 자재 표준화·단순화, 대체 자재 연구·적용</t>
+        </is>
+      </c>
+      <c r="G151" s="8" t="inlineStr"/>
       <c r="H151" s="6" t="inlineStr">
         <is>
-          <t>생산</t>
+          <t>자재</t>
         </is>
       </c>
       <c r="I151" s="8" t="inlineStr">
         <is>
-          <t>SVC-09, INT-01</t>
+          <t>SVC-09</t>
         </is>
       </c>
       <c r="J151" s="8" t="inlineStr">
         <is>
-          <t>com_company</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K151" s="6" t="inlineStr">
@@ -10053,7 +10053,7 @@
       </c>
       <c r="M151" s="8" t="inlineStr">
         <is>
-          <t>슬라이드 10/77</t>
+          <t>슬라이드 46</t>
         </is>
       </c>
     </row>
@@ -10063,47 +10063,47 @@
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>DUCT-001</t>
-        </is>
-      </c>
-      <c r="C152" s="18" t="inlineStr">
-        <is>
-          <t>DUCT 건축 설비 설계</t>
+          <t>ERP-030</t>
+        </is>
+      </c>
+      <c r="C152" s="17" t="inlineStr">
+        <is>
+          <t>ERP ERP 업무</t>
         </is>
       </c>
       <c r="D152" s="6" t="inlineStr">
         <is>
-          <t>E-4-2</t>
+          <t>§11</t>
         </is>
       </c>
       <c r="E152" s="8" t="inlineStr">
         <is>
-          <t>건축도면 학습</t>
+          <t>외주 제조 관리</t>
         </is>
       </c>
       <c r="F152" s="8" t="inlineStr">
         <is>
-          <t>건축도(램프·빔·소방구역·실 구획) AI 판독 — 설치 불가 지역 구분</t>
+          <t>3rd party 제조업체 — 제조 의뢰, 재작업 요청, 인증서 발급</t>
         </is>
       </c>
       <c r="G152" s="8" t="inlineStr">
         <is>
-          <t>설비(장비 도면·소화 배관·전기)·건축 기호 학습 포함</t>
+          <t>Partner 실시간 Code 연결</t>
         </is>
       </c>
       <c r="H152" s="6" t="inlineStr">
         <is>
-          <t>PLATFORM</t>
+          <t>생산</t>
         </is>
       </c>
       <c r="I152" s="8" t="inlineStr">
         <is>
-          <t>AI-02</t>
+          <t>SVC-09, INT-01</t>
         </is>
       </c>
       <c r="J152" s="8" t="inlineStr">
         <is>
-          <t>(RAG 인덱스)</t>
+          <t>com_company</t>
         </is>
       </c>
       <c r="K152" s="6" t="inlineStr">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="M152" s="8" t="inlineStr">
         <is>
-          <t>슬라이드 68</t>
+          <t>슬라이드 10/77</t>
         </is>
       </c>
     </row>
@@ -10128,7 +10128,7 @@
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>DUCT-002</t>
+          <t>DUCT-001</t>
         </is>
       </c>
       <c r="C153" s="18" t="inlineStr">
@@ -10143,28 +10143,32 @@
       </c>
       <c r="E153" s="8" t="inlineStr">
         <is>
-          <t>건축 도면 호출</t>
+          <t>건축도면 학습</t>
         </is>
       </c>
       <c r="F153" s="8" t="inlineStr">
         <is>
-          <t>층별·대공간 복수 도면 호출, 연결 Point(XYZ) 탐색</t>
-        </is>
-      </c>
-      <c r="G153" s="8" t="inlineStr"/>
+          <t>건축도(램프·빔·소방구역·실 구획) AI 판독 — 설치 불가 지역 구분</t>
+        </is>
+      </c>
+      <c r="G153" s="8" t="inlineStr">
+        <is>
+          <t>설비(장비 도면·소화 배관·전기)·건축 기호 학습 포함</t>
+        </is>
+      </c>
       <c r="H153" s="6" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>PLATFORM</t>
         </is>
       </c>
       <c r="I153" s="8" t="inlineStr">
         <is>
-          <t>SVC-04</t>
+          <t>AI-02</t>
         </is>
       </c>
       <c r="J153" s="8" t="inlineStr">
         <is>
-          <t>dwg_document</t>
+          <t>(RAG 인덱스)</t>
         </is>
       </c>
       <c r="K153" s="6" t="inlineStr">
@@ -10189,7 +10193,7 @@
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>DUCT-003</t>
+          <t>DUCT-002</t>
         </is>
       </c>
       <c r="C154" s="18" t="inlineStr">
@@ -10204,12 +10208,12 @@
       </c>
       <c r="E154" s="8" t="inlineStr">
         <is>
-          <t>Duct 자재 DB</t>
+          <t>건축 도면 호출</t>
         </is>
       </c>
       <c r="F154" s="8" t="inlineStr">
         <is>
-          <t>Duct 종류/손실/무게/Size별 최대길이, Pitting/Hanger/Joint/Insulation, 최대 Sizing·블록화 설계(수동변경·분할합체), 실 용도별 설계기준(풍속), 장비 기초 도면</t>
+          <t>층별·대공간 복수 도면 호출, 연결 Point(XYZ) 탐색</t>
         </is>
       </c>
       <c r="G154" s="8" t="inlineStr"/>
@@ -10220,12 +10224,12 @@
       </c>
       <c r="I154" s="8" t="inlineStr">
         <is>
-          <t>SVC-05</t>
+          <t>SVC-04</t>
         </is>
       </c>
       <c r="J154" s="8" t="inlineStr">
         <is>
-          <t>tbl_data_table</t>
+          <t>dwg_document</t>
         </is>
       </c>
       <c r="K154" s="6" t="inlineStr">
@@ -10250,7 +10254,7 @@
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>DUCT-004</t>
+          <t>DUCT-003</t>
         </is>
       </c>
       <c r="C155" s="18" t="inlineStr">
@@ -10265,27 +10269,23 @@
       </c>
       <c r="E155" s="8" t="inlineStr">
         <is>
-          <t>설비 설계 조건 설정</t>
+          <t>Duct 자재 DB</t>
         </is>
       </c>
       <c r="F155" s="8" t="inlineStr">
         <is>
-          <t>풍량 계산(실별 용도·환기횟수/국소 급배기/임의입력), 장비 리스트 풍량, 건축 정보(층고·보·텍스높이·마감), 용도(급기/배기/순환/국부), 입출구 Point, Diffuser 기준, 출발-종착점(장비↔실 Combo 연결), 공기 조건(GasType·온도·습도·밀도), Point별 유속(Size)/Std 기준, Duct Option(점검구·Turning)</t>
-        </is>
-      </c>
-      <c r="G155" s="8" t="inlineStr">
-        <is>
-          <t>설계 전용 Templet 사용</t>
-        </is>
-      </c>
+          <t>Duct 종류/손실/무게/Size별 최대길이, Pitting/Hanger/Joint/Insulation, 최대 Sizing·블록화 설계(수동변경·분할합체), 실 용도별 설계기준(풍속), 장비 기초 도면</t>
+        </is>
+      </c>
+      <c r="G155" s="8" t="inlineStr"/>
       <c r="H155" s="6" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="I155" s="8" t="inlineStr">
         <is>
-          <t>FE-01, ENG-01</t>
+          <t>SVC-05</t>
         </is>
       </c>
       <c r="J155" s="8" t="inlineStr">
@@ -10315,7 +10315,7 @@
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>DUCT-005</t>
+          <t>DUCT-004</t>
         </is>
       </c>
       <c r="C156" s="18" t="inlineStr">
@@ -10330,17 +10330,17 @@
       </c>
       <c r="E156" s="8" t="inlineStr">
         <is>
-          <t>Duct 자동 배치</t>
+          <t>설비 설계 조건 설정</t>
         </is>
       </c>
       <c r="F156" s="8" t="inlineStr">
         <is>
-          <t>가장 빠른 길 찾기(유체 흐름 고려 설계), Diffuser 자동 배치(위치·수량 조정), 수동 조정(Drag·Click)</t>
+          <t>풍량 계산(실별 용도·환기횟수/국소 급배기/임의입력), 장비 리스트 풍량, 건축 정보(층고·보·텍스높이·마감), 용도(급기/배기/순환/국부), 입출구 Point, Diffuser 기준, 출발-종착점(장비↔실 Combo 연결), 공기 조건(GasType·온도·습도·밀도), Point별 유속(Size)/Std 기준, Duct Option(점검구·Turning)</t>
         </is>
       </c>
       <c r="G156" s="8" t="inlineStr">
         <is>
-          <t>경로 탐색 알고리즘</t>
+          <t>설계 전용 Templet 사용</t>
         </is>
       </c>
       <c r="H156" s="6" t="inlineStr">
@@ -10350,12 +10350,12 @@
       </c>
       <c r="I156" s="8" t="inlineStr">
         <is>
-          <t>ENG-03</t>
+          <t>FE-01, ENG-01</t>
         </is>
       </c>
       <c r="J156" s="8" t="inlineStr">
         <is>
-          <t>dwg_document</t>
+          <t>tbl_data_table</t>
         </is>
       </c>
       <c r="K156" s="6" t="inlineStr">
@@ -10380,7 +10380,7 @@
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>DUCT-006</t>
+          <t>DUCT-005</t>
         </is>
       </c>
       <c r="C157" s="18" t="inlineStr">
@@ -10395,17 +10395,17 @@
       </c>
       <c r="E157" s="8" t="inlineStr">
         <is>
-          <t>설비 기술자료 계산</t>
+          <t>Duct 자동 배치</t>
         </is>
       </c>
       <c r="F157" s="8" t="inlineStr">
         <is>
-          <t>압력 손실/Leak율/온도 변화/결로/하중 계산, 장비 풍량 vs 설계 풍량 비교, 냉난방·배기 자료 기반 장비 선정</t>
+          <t>가장 빠른 길 찾기(유체 흐름 고려 설계), Diffuser 자동 배치(위치·수량 조정), 수동 조정(Drag·Click)</t>
         </is>
       </c>
       <c r="G157" s="8" t="inlineStr">
         <is>
-          <t>공학식 Macro 활용</t>
+          <t>경로 탐색 알고리즘</t>
         </is>
       </c>
       <c r="H157" s="6" t="inlineStr">
@@ -10415,12 +10415,12 @@
       </c>
       <c r="I157" s="8" t="inlineStr">
         <is>
-          <t>ENG-01</t>
+          <t>ENG-03</t>
         </is>
       </c>
       <c r="J157" s="8" t="inlineStr">
         <is>
-          <t>tbx_macro</t>
+          <t>dwg_document</t>
         </is>
       </c>
       <c r="K157" s="6" t="inlineStr">
@@ -10445,7 +10445,7 @@
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>DUCT-007</t>
+          <t>DUCT-006</t>
         </is>
       </c>
       <c r="C158" s="18" t="inlineStr">
@@ -10460,32 +10460,32 @@
       </c>
       <c r="E158" s="8" t="inlineStr">
         <is>
-          <t>설비-EDIM 연결</t>
+          <t>설비 기술자료 계산</t>
         </is>
       </c>
       <c r="F158" s="8" t="inlineStr">
         <is>
-          <t>설계 결과의 EDIM 연동 — 기술(BOM/Code), 제조(최소 스크랩), 자재(구매), 영업(견적)</t>
+          <t>압력 손실/Leak율/온도 변화/결로/하중 계산, 장비 풍량 vs 설계 풍량 비교, 냉난방·배기 자료 기반 장비 선정</t>
         </is>
       </c>
       <c r="G158" s="8" t="inlineStr">
         <is>
-          <t>EDIM Run 파이프라인 재사용</t>
+          <t>공학식 Macro 활용</t>
         </is>
       </c>
       <c r="H158" s="6" t="inlineStr">
         <is>
-          <t>시스템</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="I158" s="8" t="inlineStr">
         <is>
-          <t>ENG-02</t>
+          <t>ENG-01</t>
         </is>
       </c>
       <c r="J158" s="8" t="inlineStr">
         <is>
-          <t>cpq_*</t>
+          <t>tbx_macro</t>
         </is>
       </c>
       <c r="K158" s="6" t="inlineStr">
@@ -10510,47 +10510,47 @@
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>AI-001</t>
-        </is>
-      </c>
-      <c r="C159" s="19" t="inlineStr">
-        <is>
-          <t>AI AI 기능</t>
+          <t>DUCT-007</t>
+        </is>
+      </c>
+      <c r="C159" s="18" t="inlineStr">
+        <is>
+          <t>DUCT 건축 설비 설계</t>
         </is>
       </c>
       <c r="D159" s="6" t="inlineStr">
         <is>
-          <t>§9</t>
+          <t>E-4-2</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
         <is>
-          <t>도면 학습 파이프라인</t>
+          <t>설비-EDIM 연결</t>
         </is>
       </c>
       <c r="F159" s="8" t="inlineStr">
         <is>
-          <t>CAD 변환→추출→구조화→RAG 인덱싱 잡 관리</t>
+          <t>설계 결과의 EDIM 연동 — 기술(BOM/Code), 제조(최소 스크랩), 자재(구매), 영업(견적)</t>
         </is>
       </c>
       <c r="G159" s="8" t="inlineStr">
         <is>
-          <t>Platform 권한 전용, 비용 계측</t>
+          <t>EDIM Run 파이프라인 재사용</t>
         </is>
       </c>
       <c r="H159" s="6" t="inlineStr">
         <is>
-          <t>PLATFORM</t>
+          <t>시스템</t>
         </is>
       </c>
       <c r="I159" s="8" t="inlineStr">
         <is>
-          <t>AI-02, FE-04</t>
+          <t>ENG-02</t>
         </is>
       </c>
       <c r="J159" s="8" t="inlineStr">
         <is>
-          <t>(RAG 인덱스)</t>
+          <t>cpq_*</t>
         </is>
       </c>
       <c r="K159" s="6" t="inlineStr">
@@ -10563,7 +10563,11 @@
           <t>미정</t>
         </is>
       </c>
-      <c r="M159" s="8" t="inlineStr"/>
+      <c r="M159" s="8" t="inlineStr">
+        <is>
+          <t>슬라이드 68</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="6" t="n">
@@ -10571,7 +10575,7 @@
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>AI-002</t>
+          <t>AI-001</t>
         </is>
       </c>
       <c r="C160" s="19" t="inlineStr">
@@ -10586,17 +10590,17 @@
       </c>
       <c r="E160" s="8" t="inlineStr">
         <is>
-          <t>메타데이터 추출</t>
+          <t>도면 학습 파이프라인</t>
         </is>
       </c>
       <c r="F160" s="8" t="inlineStr">
         <is>
-          <t>타이틀블록(도번·Rev·재질·축척)·레이어·블록 속성·BOM 규칙 분류</t>
+          <t>CAD 변환→추출→구조화→RAG 인덱싱 잡 관리</t>
         </is>
       </c>
       <c r="G160" s="8" t="inlineStr">
         <is>
-          <t>난이도 下 — 우선 적용</t>
+          <t>Platform 권한 전용, 비용 계측</t>
         </is>
       </c>
       <c r="H160" s="6" t="inlineStr">
@@ -10606,12 +10610,12 @@
       </c>
       <c r="I160" s="8" t="inlineStr">
         <is>
-          <t>AI-02</t>
+          <t>AI-02, FE-04</t>
         </is>
       </c>
       <c r="J160" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>(RAG 인덱스)</t>
         </is>
       </c>
       <c r="K160" s="6" t="inlineStr">
@@ -10632,7 +10636,7 @@
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>AI-003</t>
+          <t>AI-002</t>
         </is>
       </c>
       <c r="C161" s="19" t="inlineStr">
@@ -10647,17 +10651,17 @@
       </c>
       <c r="E161" s="8" t="inlineStr">
         <is>
-          <t>2D 엔티티 파싱·OCR</t>
+          <t>메타데이터 추출</t>
         </is>
       </c>
       <c r="F161" s="8" t="inlineStr">
         <is>
-          <t>DWG/DXF 엔티티(치수·공차·기호) 추출, 스캔 도면 OCR+도면인식</t>
+          <t>타이틀블록(도번·Rev·재질·축척)·레이어·블록 속성·BOM 규칙 분류</t>
         </is>
       </c>
       <c r="G161" s="8" t="inlineStr">
         <is>
-          <t>도면 표준 상이 시 튜닝</t>
+          <t>난이도 下 — 우선 적용</t>
         </is>
       </c>
       <c r="H161" s="6" t="inlineStr">
@@ -10693,7 +10697,7 @@
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>AI-004</t>
+          <t>AI-003</t>
         </is>
       </c>
       <c r="C162" s="19" t="inlineStr">
@@ -10703,42 +10707,42 @@
       </c>
       <c r="D162" s="6" t="inlineStr">
         <is>
-          <t>S-2-2</t>
+          <t>§9</t>
         </is>
       </c>
       <c r="E162" s="8" t="inlineStr">
         <is>
-          <t>Macro 자동 생성</t>
+          <t>2D 엔티티 파싱·OCR</t>
         </is>
       </c>
       <c r="F162" s="8" t="inlineStr">
         <is>
-          <t>Prompt→Macro/Flowchart/Description/Coding 생성</t>
+          <t>DWG/DXF 엔티티(치수·공차·기호) 추출, 스캔 도면 OCR+도면인식</t>
         </is>
       </c>
       <c r="G162" s="8" t="inlineStr">
         <is>
-          <t>ENG-01 문법 검증 통과 필수</t>
+          <t>도면 표준 상이 시 튜닝</t>
         </is>
       </c>
       <c r="H162" s="6" t="inlineStr">
         <is>
-          <t>SETUP</t>
+          <t>PLATFORM</t>
         </is>
       </c>
       <c r="I162" s="8" t="inlineStr">
         <is>
-          <t>AI-03</t>
+          <t>AI-02</t>
         </is>
       </c>
       <c r="J162" s="8" t="inlineStr">
         <is>
-          <t>tbx_macro</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K162" s="6" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="L162" s="6" t="inlineStr">
@@ -10754,7 +10758,7 @@
       </c>
       <c r="B163" s="6" t="inlineStr">
         <is>
-          <t>AI-005</t>
+          <t>AI-004</t>
         </is>
       </c>
       <c r="C163" s="19" t="inlineStr">
@@ -10769,17 +10773,17 @@
       </c>
       <c r="E163" s="8" t="inlineStr">
         <is>
-          <t>4-Way 상호 변환</t>
+          <t>Macro 자동 생성</t>
         </is>
       </c>
       <c r="F163" s="8" t="inlineStr">
         <is>
-          <t>표현 간(Macro↔Flowchart 등) AI 변환</t>
+          <t>Prompt→Macro/Flowchart/Description/Coding 생성</t>
         </is>
       </c>
       <c r="G163" s="8" t="inlineStr">
         <is>
-          <t>변환 결과 사용자 검토·승인</t>
+          <t>ENG-01 문법 검증 통과 필수</t>
         </is>
       </c>
       <c r="H163" s="6" t="inlineStr">
@@ -10815,7 +10819,7 @@
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>AI-006</t>
+          <t>AI-005</t>
         </is>
       </c>
       <c r="C164" s="19" t="inlineStr">
@@ -10825,20 +10829,24 @@
       </c>
       <c r="D164" s="6" t="inlineStr">
         <is>
-          <t>S-2-1</t>
+          <t>S-2-2</t>
         </is>
       </c>
       <c r="E164" s="8" t="inlineStr">
         <is>
-          <t>UI 자동 제안</t>
+          <t>4-Way 상호 변환</t>
         </is>
       </c>
       <c r="F164" s="8" t="inlineStr">
         <is>
-          <t>설명→용도/항목/필요 DB Table→UI Form 초안</t>
-        </is>
-      </c>
-      <c r="G164" s="8" t="inlineStr"/>
+          <t>표현 간(Macro↔Flowchart 등) AI 변환</t>
+        </is>
+      </c>
+      <c r="G164" s="8" t="inlineStr">
+        <is>
+          <t>변환 결과 사용자 검토·승인</t>
+        </is>
+      </c>
       <c r="H164" s="6" t="inlineStr">
         <is>
           <t>SETUP</t>
@@ -10846,12 +10854,12 @@
       </c>
       <c r="I164" s="8" t="inlineStr">
         <is>
-          <t>AI-04</t>
+          <t>AI-03</t>
         </is>
       </c>
       <c r="J164" s="8" t="inlineStr">
         <is>
-          <t>tbx_ui_form</t>
+          <t>tbx_macro</t>
         </is>
       </c>
       <c r="K164" s="6" t="inlineStr">
@@ -10872,7 +10880,7 @@
       </c>
       <c r="B165" s="6" t="inlineStr">
         <is>
-          <t>AI-007</t>
+          <t>AI-006</t>
         </is>
       </c>
       <c r="C165" s="19" t="inlineStr">
@@ -10882,42 +10890,38 @@
       </c>
       <c r="D165" s="6" t="inlineStr">
         <is>
-          <t>§9</t>
+          <t>S-2-1</t>
         </is>
       </c>
       <c r="E165" s="8" t="inlineStr">
         <is>
-          <t>사내 자료 챗봇</t>
+          <t>UI 자동 제안</t>
         </is>
       </c>
       <c r="F165" s="8" t="inlineStr">
         <is>
-          <t>도면·기술자료·서류 RAG Q&amp;A, ERP 연동 서류 생성 지원</t>
-        </is>
-      </c>
-      <c r="G165" s="8" t="inlineStr">
-        <is>
-          <t>내부 자료 검색·응답용</t>
-        </is>
-      </c>
+          <t>설명→용도/항목/필요 DB Table→UI Form 초안</t>
+        </is>
+      </c>
+      <c r="G165" s="8" t="inlineStr"/>
       <c r="H165" s="6" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>SETUP</t>
         </is>
       </c>
       <c r="I165" s="8" t="inlineStr">
         <is>
-          <t>AI-05</t>
+          <t>AI-04</t>
         </is>
       </c>
       <c r="J165" s="8" t="inlineStr">
         <is>
-          <t>(RAG 인덱스)</t>
+          <t>tbx_ui_form</t>
         </is>
       </c>
       <c r="K165" s="6" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="L165" s="6" t="inlineStr">
@@ -10933,7 +10937,7 @@
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>AI-008</t>
+          <t>AI-007</t>
         </is>
       </c>
       <c r="C166" s="19" t="inlineStr">
@@ -10943,42 +10947,42 @@
       </c>
       <c r="D166" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>§9</t>
         </is>
       </c>
       <c r="E166" s="8" t="inlineStr">
         <is>
-          <t>AI 생성물 승인 게이트</t>
+          <t>사내 자료 챗봇</t>
         </is>
       </c>
       <c r="F166" s="8" t="inlineStr">
         <is>
-          <t>AI 생성 Macro/UI/자료의 검토·승인 절차 강제</t>
+          <t>도면·기술자료·서류 RAG Q&amp;A, ERP 연동 서류 생성 지원</t>
         </is>
       </c>
       <c r="G166" s="8" t="inlineStr">
         <is>
-          <t>미승인 생성물 사용 차단</t>
+          <t>내부 자료 검색·응답용</t>
         </is>
       </c>
       <c r="H166" s="6" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>전체</t>
         </is>
       </c>
       <c r="I166" s="8" t="inlineStr">
         <is>
-          <t>SVC-10</t>
+          <t>AI-05</t>
         </is>
       </c>
       <c r="J166" s="8" t="inlineStr">
         <is>
-          <t>sys_approval_request</t>
+          <t>(RAG 인덱스)</t>
         </is>
       </c>
       <c r="K166" s="6" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="L166" s="6" t="inlineStr">
@@ -10994,52 +10998,52 @@
       </c>
       <c r="B167" s="6" t="inlineStr">
         <is>
-          <t>APP-001</t>
-        </is>
-      </c>
-      <c r="C167" s="7" t="inlineStr">
-        <is>
-          <t>APP 모바일 App</t>
+          <t>AI-008</t>
+        </is>
+      </c>
+      <c r="C167" s="19" t="inlineStr">
+        <is>
+          <t>AI AI 기능</t>
         </is>
       </c>
       <c r="D167" s="6" t="inlineStr">
         <is>
-          <t>§12</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E167" s="8" t="inlineStr">
         <is>
-          <t>QR 정보 열람</t>
+          <t>AI 생성물 승인 게이트</t>
         </is>
       </c>
       <c r="F167" s="8" t="inlineStr">
         <is>
-          <t>QR 스캔→도면/서류/Project History/처리할 업무</t>
+          <t>AI 생성 Macro/UI/자료의 검토·승인 절차 강제</t>
         </is>
       </c>
       <c r="G167" s="8" t="inlineStr">
         <is>
-          <t>권한 검사 후 표시</t>
+          <t>미승인 생성물 사용 차단</t>
         </is>
       </c>
       <c r="H167" s="6" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="I167" s="8" t="inlineStr">
         <is>
-          <t>FE-05, INT-05</t>
+          <t>SVC-10</t>
         </is>
       </c>
       <c r="J167" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>sys_approval_request</t>
         </is>
       </c>
       <c r="K167" s="6" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="L167" s="6" t="inlineStr">
@@ -11055,7 +11059,7 @@
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>APP-002</t>
+          <t>APP-001</t>
         </is>
       </c>
       <c r="C168" s="7" t="inlineStr">
@@ -11070,28 +11074,32 @@
       </c>
       <c r="E168" s="8" t="inlineStr">
         <is>
-          <t>모바일 승인</t>
+          <t>QR 정보 열람</t>
         </is>
       </c>
       <c r="F168" s="8" t="inlineStr">
         <is>
-          <t>업무 승인 처리(승인함·결재)</t>
-        </is>
-      </c>
-      <c r="G168" s="8" t="inlineStr"/>
+          <t>QR 스캔→도면/서류/Project History/처리할 업무</t>
+        </is>
+      </c>
+      <c r="G168" s="8" t="inlineStr">
+        <is>
+          <t>권한 검사 후 표시</t>
+        </is>
+      </c>
       <c r="H168" s="6" t="inlineStr">
         <is>
-          <t>ADMIN↑</t>
+          <t>전체</t>
         </is>
       </c>
       <c r="I168" s="8" t="inlineStr">
         <is>
-          <t>FE-05, SVC-10</t>
+          <t>FE-05, INT-05</t>
         </is>
       </c>
       <c r="J168" s="8" t="inlineStr">
         <is>
-          <t>sys_approval_request</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K168" s="6" t="inlineStr">
@@ -11112,7 +11120,7 @@
       </c>
       <c r="B169" s="6" t="inlineStr">
         <is>
-          <t>APP-003</t>
+          <t>APP-002</t>
         </is>
       </c>
       <c r="C169" s="7" t="inlineStr">
@@ -11127,28 +11135,28 @@
       </c>
       <c r="E169" s="8" t="inlineStr">
         <is>
-          <t>Project 소통</t>
+          <t>모바일 승인</t>
         </is>
       </c>
       <c r="F169" s="8" t="inlineStr">
         <is>
-          <t>Project 중심 대화, History 관리</t>
+          <t>업무 승인 처리(승인함·결재)</t>
         </is>
       </c>
       <c r="G169" s="8" t="inlineStr"/>
       <c r="H169" s="6" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>ADMIN↑</t>
         </is>
       </c>
       <c r="I169" s="8" t="inlineStr">
         <is>
-          <t>FE-05, SVC-13</t>
+          <t>FE-05, SVC-10</t>
         </is>
       </c>
       <c r="J169" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>sys_approval_request</t>
         </is>
       </c>
       <c r="K169" s="6" t="inlineStr">
@@ -11169,7 +11177,7 @@
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>APP-004</t>
+          <t>APP-003</t>
         </is>
       </c>
       <c r="C170" s="7" t="inlineStr">
@@ -11184,32 +11192,28 @@
       </c>
       <c r="E170" s="8" t="inlineStr">
         <is>
-          <t>자재 입출고</t>
+          <t>Project 소통</t>
         </is>
       </c>
       <c r="F170" s="8" t="inlineStr">
         <is>
-          <t>현장 자재 입출고 처리(MI/MO)</t>
-        </is>
-      </c>
-      <c r="G170" s="8" t="inlineStr">
-        <is>
-          <t>QR 기반 자재 식별</t>
-        </is>
-      </c>
+          <t>Project 중심 대화, History 관리</t>
+        </is>
+      </c>
+      <c r="G170" s="8" t="inlineStr"/>
       <c r="H170" s="6" t="inlineStr">
         <is>
-          <t>자재</t>
+          <t>전체</t>
         </is>
       </c>
       <c r="I170" s="8" t="inlineStr">
         <is>
-          <t>FE-05, SVC-09</t>
+          <t>FE-05, SVC-13</t>
         </is>
       </c>
       <c r="J170" s="8" t="inlineStr">
         <is>
-          <t>erp_process_event</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K170" s="6" t="inlineStr">
@@ -11230,7 +11234,7 @@
       </c>
       <c r="B171" s="6" t="inlineStr">
         <is>
-          <t>APP-005</t>
+          <t>APP-004</t>
         </is>
       </c>
       <c r="C171" s="7" t="inlineStr">
@@ -11245,22 +11249,22 @@
       </c>
       <c r="E171" s="8" t="inlineStr">
         <is>
-          <t>검수</t>
+          <t>자재 입출고</t>
         </is>
       </c>
       <c r="F171" s="8" t="inlineStr">
         <is>
-          <t>자재·완성품·설치완료 검수 처리</t>
+          <t>현장 자재 입출고 처리(MI/MO)</t>
         </is>
       </c>
       <c r="G171" s="8" t="inlineStr">
         <is>
-          <t>사진 첨부</t>
+          <t>QR 기반 자재 식별</t>
         </is>
       </c>
       <c r="H171" s="6" t="inlineStr">
         <is>
-          <t>QC</t>
+          <t>자재</t>
         </is>
       </c>
       <c r="I171" s="8" t="inlineStr">
@@ -11291,7 +11295,7 @@
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>APP-006</t>
+          <t>APP-005</t>
         </is>
       </c>
       <c r="C172" s="7" t="inlineStr">
@@ -11306,18 +11310,22 @@
       </c>
       <c r="E172" s="8" t="inlineStr">
         <is>
-          <t>유지보수</t>
+          <t>검수</t>
         </is>
       </c>
       <c r="F172" s="8" t="inlineStr">
         <is>
-          <t>Client 유지보수 접수·처리</t>
-        </is>
-      </c>
-      <c r="G172" s="8" t="inlineStr"/>
+          <t>자재·완성품·설치완료 검수 처리</t>
+        </is>
+      </c>
+      <c r="G172" s="8" t="inlineStr">
+        <is>
+          <t>사진 첨부</t>
+        </is>
+      </c>
       <c r="H172" s="6" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>QC</t>
         </is>
       </c>
       <c r="I172" s="8" t="inlineStr">
@@ -11348,7 +11356,7 @@
       </c>
       <c r="B173" s="6" t="inlineStr">
         <is>
-          <t>APP-007</t>
+          <t>APP-006</t>
         </is>
       </c>
       <c r="C173" s="7" t="inlineStr">
@@ -11363,28 +11371,28 @@
       </c>
       <c r="E173" s="8" t="inlineStr">
         <is>
-          <t>공지·푸시</t>
+          <t>유지보수</t>
         </is>
       </c>
       <c r="F173" s="8" t="inlineStr">
         <is>
-          <t>공지(알림) 수신, 푸시 알림</t>
+          <t>Client 유지보수 접수·처리</t>
         </is>
       </c>
       <c r="G173" s="8" t="inlineStr"/>
       <c r="H173" s="6" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="I173" s="8" t="inlineStr">
         <is>
-          <t>FE-05, SVC-13</t>
+          <t>FE-05, SVC-09</t>
         </is>
       </c>
       <c r="J173" s="8" t="inlineStr">
         <is>
-          <t>sys_notification</t>
+          <t>erp_process_event</t>
         </is>
       </c>
       <c r="K173" s="6" t="inlineStr">
@@ -11405,7 +11413,7 @@
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>APP-008</t>
+          <t>APP-007</t>
         </is>
       </c>
       <c r="C174" s="7" t="inlineStr">
@@ -11420,32 +11428,28 @@
       </c>
       <c r="E174" s="8" t="inlineStr">
         <is>
-          <t>AR 뷰</t>
+          <t>공지·푸시</t>
         </is>
       </c>
       <c r="F174" s="8" t="inlineStr">
         <is>
-          <t>증강현실 — 3D 모델·Digital Twin 데이터 오버레이</t>
-        </is>
-      </c>
-      <c r="G174" s="8" t="inlineStr">
-        <is>
-          <t>INT-02 연계</t>
-        </is>
-      </c>
+          <t>공지(알림) 수신, 푸시 알림</t>
+        </is>
+      </c>
+      <c r="G174" s="8" t="inlineStr"/>
       <c r="H174" s="6" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>전체</t>
         </is>
       </c>
       <c r="I174" s="8" t="inlineStr">
         <is>
-          <t>FE-05, INT-02</t>
+          <t>FE-05, SVC-13</t>
         </is>
       </c>
       <c r="J174" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>sys_notification</t>
         </is>
       </c>
       <c r="K174" s="6" t="inlineStr">
@@ -11458,11 +11462,7 @@
           <t>미정</t>
         </is>
       </c>
-      <c r="M174" s="8" t="inlineStr">
-        <is>
-          <t>후순위</t>
-        </is>
-      </c>
+      <c r="M174" s="8" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="6" t="n">
@@ -11470,48 +11470,52 @@
       </c>
       <c r="B175" s="6" t="inlineStr">
         <is>
-          <t>ADM-001</t>
-        </is>
-      </c>
-      <c r="C175" s="9" t="inlineStr">
-        <is>
-          <t>ADM 관리 콘솔</t>
+          <t>APP-008</t>
+        </is>
+      </c>
+      <c r="C175" s="7" t="inlineStr">
+        <is>
+          <t>APP 모바일 App</t>
         </is>
       </c>
       <c r="D175" s="6" t="inlineStr">
         <is>
+          <t>§12</t>
+        </is>
+      </c>
+      <c r="E175" s="8" t="inlineStr">
+        <is>
+          <t>AR 뷰</t>
+        </is>
+      </c>
+      <c r="F175" s="8" t="inlineStr">
+        <is>
+          <t>증강현실 — 3D 모델·Digital Twin 데이터 오버레이</t>
+        </is>
+      </c>
+      <c r="G175" s="8" t="inlineStr">
+        <is>
+          <t>INT-02 연계</t>
+        </is>
+      </c>
+      <c r="H175" s="6" t="inlineStr">
+        <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="I175" s="8" t="inlineStr">
+        <is>
+          <t>FE-05, INT-02</t>
+        </is>
+      </c>
+      <c r="J175" s="8" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E175" s="8" t="inlineStr">
-        <is>
-          <t>테넌트 관리</t>
-        </is>
-      </c>
-      <c r="F175" s="8" t="inlineStr">
-        <is>
-          <t>테넌트 생성·설정·상태, 요금제(SaaS)</t>
-        </is>
-      </c>
-      <c r="G175" s="8" t="inlineStr"/>
-      <c r="H175" s="6" t="inlineStr">
-        <is>
-          <t>PLATFORM</t>
-        </is>
-      </c>
-      <c r="I175" s="8" t="inlineStr">
-        <is>
-          <t>FE-04</t>
-        </is>
-      </c>
-      <c r="J175" s="8" t="inlineStr">
-        <is>
-          <t>sys_tenant</t>
-        </is>
-      </c>
       <c r="K175" s="6" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="L175" s="6" t="inlineStr">
@@ -11519,7 +11523,11 @@
           <t>미정</t>
         </is>
       </c>
-      <c r="M175" s="8" t="inlineStr"/>
+      <c r="M175" s="8" t="inlineStr">
+        <is>
+          <t>후순위</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="6" t="n">
@@ -11527,7 +11535,7 @@
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>ADM-002</t>
+          <t>ADM-001</t>
         </is>
       </c>
       <c r="C176" s="9" t="inlineStr">
@@ -11542,33 +11550,33 @@
       </c>
       <c r="E176" s="8" t="inlineStr">
         <is>
-          <t>사용자·권한 관리 UI</t>
+          <t>테넌트 관리</t>
         </is>
       </c>
       <c r="F176" s="8" t="inlineStr">
         <is>
-          <t>SYS-003~005의 관리 화면</t>
+          <t>테넌트 생성·설정·상태, 요금제(SaaS)</t>
         </is>
       </c>
       <c r="G176" s="8" t="inlineStr"/>
       <c r="H176" s="6" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>PLATFORM</t>
         </is>
       </c>
       <c r="I176" s="8" t="inlineStr">
         <is>
-          <t>FE-04, SVC-01</t>
+          <t>FE-04</t>
         </is>
       </c>
       <c r="J176" s="8" t="inlineStr">
         <is>
-          <t>sys_*</t>
+          <t>sys_tenant</t>
         </is>
       </c>
       <c r="K176" s="6" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="L176" s="6" t="inlineStr">
@@ -11584,7 +11592,7 @@
       </c>
       <c r="B177" s="6" t="inlineStr">
         <is>
-          <t>ADM-003</t>
+          <t>ADM-002</t>
         </is>
       </c>
       <c r="C177" s="9" t="inlineStr">
@@ -11599,12 +11607,12 @@
       </c>
       <c r="E177" s="8" t="inlineStr">
         <is>
-          <t>승인 관리</t>
+          <t>사용자·권한 관리 UI</t>
         </is>
       </c>
       <c r="F177" s="8" t="inlineStr">
         <is>
-          <t>승인 요청 일괄 처리·위임·규칙</t>
+          <t>SYS-003~005의 관리 화면</t>
         </is>
       </c>
       <c r="G177" s="8" t="inlineStr"/>
@@ -11615,17 +11623,17 @@
       </c>
       <c r="I177" s="8" t="inlineStr">
         <is>
-          <t>FE-04, SVC-10</t>
+          <t>FE-04, SVC-01</t>
         </is>
       </c>
       <c r="J177" s="8" t="inlineStr">
         <is>
-          <t>sys_approval_request</t>
+          <t>sys_*</t>
         </is>
       </c>
       <c r="K177" s="6" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="L177" s="6" t="inlineStr">
@@ -11641,7 +11649,7 @@
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>ADM-004</t>
+          <t>ADM-003</t>
         </is>
       </c>
       <c r="C178" s="9" t="inlineStr">
@@ -11656,37 +11664,33 @@
       </c>
       <c r="E178" s="8" t="inlineStr">
         <is>
-          <t>AI 학습 관리</t>
+          <t>승인 관리</t>
         </is>
       </c>
       <c r="F178" s="8" t="inlineStr">
         <is>
-          <t>학습 데이터 등록, 파이프라인 실행·품질 확인</t>
-        </is>
-      </c>
-      <c r="G178" s="8" t="inlineStr">
-        <is>
-          <t>Platform 전용</t>
-        </is>
-      </c>
+          <t>승인 요청 일괄 처리·위임·규칙</t>
+        </is>
+      </c>
+      <c r="G178" s="8" t="inlineStr"/>
       <c r="H178" s="6" t="inlineStr">
         <is>
-          <t>PLATFORM</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="I178" s="8" t="inlineStr">
         <is>
-          <t>FE-04, AI-02</t>
+          <t>FE-04, SVC-10</t>
         </is>
       </c>
       <c r="J178" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>sys_approval_request</t>
         </is>
       </c>
       <c r="K178" s="6" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="L178" s="6" t="inlineStr">
@@ -11702,59 +11706,120 @@
       </c>
       <c r="B179" s="6" t="inlineStr">
         <is>
+          <t>ADM-004</t>
+        </is>
+      </c>
+      <c r="C179" s="9" t="inlineStr">
+        <is>
+          <t>ADM 관리 콘솔</t>
+        </is>
+      </c>
+      <c r="D179" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E179" s="8" t="inlineStr">
+        <is>
+          <t>AI 학습 관리</t>
+        </is>
+      </c>
+      <c r="F179" s="8" t="inlineStr">
+        <is>
+          <t>학습 데이터 등록, 파이프라인 실행·품질 확인</t>
+        </is>
+      </c>
+      <c r="G179" s="8" t="inlineStr">
+        <is>
+          <t>Platform 전용</t>
+        </is>
+      </c>
+      <c r="H179" s="6" t="inlineStr">
+        <is>
+          <t>PLATFORM</t>
+        </is>
+      </c>
+      <c r="I179" s="8" t="inlineStr">
+        <is>
+          <t>FE-04, AI-02</t>
+        </is>
+      </c>
+      <c r="J179" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K179" s="6" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="L179" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M179" s="8" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="6" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" s="6" t="inlineStr">
+        <is>
           <t>ADM-005</t>
         </is>
       </c>
-      <c r="C179" s="9" t="inlineStr">
+      <c r="C180" s="9" t="inlineStr">
         <is>
           <t>ADM 관리 콘솔</t>
         </is>
       </c>
-      <c r="D179" s="6" t="inlineStr">
+      <c r="D180" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E179" s="8" t="inlineStr">
+      <c r="E180" s="8" t="inlineStr">
         <is>
           <t>감사·사용량</t>
         </is>
       </c>
-      <c r="F179" s="8" t="inlineStr">
+      <c r="F180" s="8" t="inlineStr">
         <is>
           <t>감사 로그, API 사용량, AI 토큰 비용 조회</t>
         </is>
       </c>
-      <c r="G179" s="8" t="inlineStr"/>
-      <c r="H179" s="6" t="inlineStr">
+      <c r="G180" s="8" t="inlineStr"/>
+      <c r="H180" s="6" t="inlineStr">
         <is>
           <t>PLATFORM/ADMIN</t>
         </is>
       </c>
-      <c r="I179" s="8" t="inlineStr">
+      <c r="I180" s="8" t="inlineStr">
         <is>
           <t>FE-04, INF-07</t>
         </is>
       </c>
-      <c r="J179" s="8" t="inlineStr">
+      <c r="J180" s="8" t="inlineStr">
         <is>
           <t>sys_history</t>
         </is>
       </c>
-      <c r="K179" s="6" t="inlineStr">
+      <c r="K180" s="6" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="L179" s="6" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="M179" s="8" t="inlineStr"/>
+      <c r="L180" s="6" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="M180" s="8" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M179"/>
+  <autoFilter ref="A1:M180"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11832,13 +11897,13 @@
         </is>
       </c>
       <c r="C2" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" s="6" t="n">
         <v>11</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" s="6" t="inlineStr"/>
       <c r="G2" s="6" t="n">
@@ -12170,13 +12235,13 @@
       </c>
       <c r="B16" s="32" t="inlineStr"/>
       <c r="C16" s="32" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D16" s="32" t="n">
         <v>30</v>
       </c>
       <c r="E16" s="32" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F16" s="32" t="n">
         <v>27</v>
